--- a/tables/Flexible CUE/Local_estpar_protection_True_vo_False_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_estpar_protection_True_vo_False_CUE_True.xlsx
@@ -588,46 +588,46 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301524983055982</v>
+        <v>0.230173922345163</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2004351542868739</v>
+        <v>0.2038584361609218</v>
       </c>
       <c r="M2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.404174468294835</v>
       </c>
       <c r="N2" t="n">
-        <v>4.387911232949087</v>
+        <v>4.431700328899079</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002717398397123686</v>
+        <v>0.002691167565226858</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002695905549460506</v>
+        <v>0.002705328869841683</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007355187754656232</v>
+        <v>0.0007388555130337309</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009888449793967859</v>
+        <v>0.0009972553073629008</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006220274351503275</v>
+        <v>0.0006271730006101701</v>
       </c>
       <c r="T2" t="n">
-        <v>0.008539704523570085</v>
+        <v>0.008429000661916652</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006138284466882004</v>
+        <v>0.006114632638712192</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001639549244280104</v>
+        <v>0.001650796340018038</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001881410351950529</v>
+        <v>0.001951147053555535</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001504408134152127</v>
+        <v>0.001511764627242887</v>
       </c>
     </row>
     <row r="3">
@@ -668,46 +668,46 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1187964952926874</v>
+        <v>0.1194156710580432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.140436197290562</v>
+        <v>0.1413287515195503</v>
       </c>
       <c r="M3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.321674553984673</v>
       </c>
       <c r="N3" t="n">
-        <v>4.32308953591069</v>
+        <v>4.331611202164182</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002996162794990883</v>
+        <v>0.00297629722833991</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001653591100189854</v>
+        <v>0.001658051600468724</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006103443773176312</v>
+        <v>0.0006110701801911452</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005413878418296291</v>
+        <v>0.0005416627933942327</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003064220418450668</v>
+        <v>0.0003075901248437788</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01078674174866509</v>
+        <v>0.01069902560507406</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003585187711933679</v>
+        <v>0.003595712092669254</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001341004458719694</v>
+        <v>0.001344252488470284</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001129411456084894</v>
+        <v>0.001154851164725616</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001106049525880969</v>
+        <v>0.001101890743741658</v>
       </c>
     </row>
     <row r="4">
@@ -748,46 +748,46 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4340590818808676</v>
+        <v>0.4194869788621236</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2180319877736369</v>
+        <v>0.2269943105173577</v>
       </c>
       <c r="M4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.305760853918062</v>
       </c>
       <c r="N4" t="n">
-        <v>4.430209765323307</v>
+        <v>4.566683054074947</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00290987938753536</v>
+        <v>0.002736524493574656</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00235832699055376</v>
+        <v>0.002303342962690763</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000307185078341158</v>
+        <v>0.0003126631300834826</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001137168520350855</v>
+        <v>0.001177590037346351</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002850797324776311</v>
+        <v>0.0002881513962370256</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008823714810689285</v>
+        <v>0.008055813858564654</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00639830572315583</v>
+        <v>0.006067675723701741</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001268318672874809</v>
+        <v>0.001290341320083157</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001981990064079153</v>
+        <v>0.002155228545424732</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001587379928260273</v>
+        <v>0.001631635945398531</v>
       </c>
     </row>
     <row r="5">
@@ -828,46 +828,46 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851828485504524</v>
+        <v>0.1836362466865699</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2253085691290141</v>
+        <v>0.2222504432753144</v>
       </c>
       <c r="M5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.304261087108948</v>
       </c>
       <c r="N5" t="n">
-        <v>4.405410527363491</v>
+        <v>4.346505225166321</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002413379219659122</v>
+        <v>0.002405050948081549</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002195760627346779</v>
+        <v>0.002171415004770004</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008487975598333455</v>
+        <v>0.0008481916127724251</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000836387684696339</v>
+        <v>0.000831983808958567</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001160666699367369</v>
+        <v>0.001154948362134588</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007434203588245981</v>
+        <v>0.007421336883031586</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004395229647166385</v>
+        <v>0.004364053333945715</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00191038063112518</v>
+        <v>0.001913631676307882</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001620863636046333</v>
+        <v>0.001657997414157822</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002491277051910093</v>
+        <v>0.002462008849885081</v>
       </c>
     </row>
     <row r="6">
@@ -908,46 +908,46 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1720532088902192</v>
+        <v>0.1696931496494424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.204638966287349</v>
+        <v>0.202075292835271</v>
       </c>
       <c r="M6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.366354518668125</v>
       </c>
       <c r="N6" t="n">
-        <v>4.470113737432057</v>
+        <v>4.383001931491272</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001889258083220671</v>
+        <v>0.001864795433950721</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001414324362306124</v>
+        <v>0.001386265774497913</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005284411842400103</v>
+        <v>0.0005315585590484993</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003981654181818305</v>
+        <v>0.0003945316973418944</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003463836569443224</v>
+        <v>0.0003435868921093666</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005648665157313318</v>
+        <v>0.005575014096319824</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0026088450515985</v>
+        <v>0.002577200478225922</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001205671237636301</v>
+        <v>0.001211473367826345</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009467178998113538</v>
+        <v>0.0009675842702812734</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00104753210921321</v>
+        <v>0.001032142793842978</v>
       </c>
     </row>
     <row r="7">
@@ -988,46 +988,46 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2003712390960207</v>
+        <v>0.2030468160086783</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1569124951558778</v>
+        <v>0.1596994159452441</v>
       </c>
       <c r="M7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.27650586554834</v>
       </c>
       <c r="N7" t="n">
-        <v>4.318255038521045</v>
+        <v>4.381338268498013</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003127768027265962</v>
+        <v>0.003103819155328756</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001953541400375513</v>
+        <v>0.001972992554386203</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005403160763438628</v>
+        <v>0.0005401657796003979</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009071785419641194</v>
+        <v>0.0009136247877191884</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004779406359390678</v>
+        <v>0.0004800161103622279</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01054793571725046</v>
+        <v>0.0104334866747243</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004673013064484137</v>
+        <v>0.004700635849353097</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001236109320505722</v>
+        <v>0.001236153287031197</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001664307246790194</v>
+        <v>0.001712647225019129</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001824505121905522</v>
+        <v>0.001817542950218138</v>
       </c>
     </row>
     <row r="8">
@@ -1068,46 +1068,46 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1629277668784354</v>
+        <v>0.1640874531430341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.137846199669644</v>
+        <v>0.1429798880331228</v>
       </c>
       <c r="M8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.438538840521598</v>
       </c>
       <c r="N8" t="n">
-        <v>4.279463263901131</v>
+        <v>4.410426778198659</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005241077439936704</v>
+        <v>0.005245165867247816</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002888230384873782</v>
+        <v>0.002918142886038812</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009960892679388759</v>
+        <v>0.001000006771831926</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001439459664706566</v>
+        <v>0.001447439816701102</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006701075182005366</v>
+        <v>0.0006763389631962464</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02119827401795712</v>
+        <v>0.02113413948619935</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01021951149840009</v>
+        <v>0.01025597389849785</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002294106120128624</v>
+        <v>0.002303843660330272</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003049421518947879</v>
+        <v>0.003105436274123283</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001403697068475782</v>
+        <v>0.001406568440965932</v>
       </c>
     </row>
     <row r="9">
@@ -1148,46 +1148,46 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2032150904583823</v>
+        <v>0.2020811236552771</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1613209216308875</v>
+        <v>0.1613723476081795</v>
       </c>
       <c r="M9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.239065410023795</v>
       </c>
       <c r="N9" t="n">
-        <v>4.38222245034776</v>
+        <v>4.367167907558467</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004313818484958983</v>
+        <v>0.004290225140850388</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002675075234514366</v>
+        <v>0.002649517914119729</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0007452350710326367</v>
+        <v>0.0007461854387285922</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000916790541715143</v>
+        <v>0.0009143079996859878</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0008159028485621171</v>
+        <v>0.0008138129006080895</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01528393972286469</v>
+        <v>0.01515852170608924</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006982386637018805</v>
+        <v>0.006973758107217394</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001661262747605026</v>
+        <v>0.001663209696673919</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00170475898529977</v>
+        <v>0.001748669885040012</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001649948709899403</v>
+        <v>0.001631246643017977</v>
       </c>
     </row>
     <row r="10">
@@ -1228,46 +1228,46 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2213013737149055</v>
+        <v>0.2191421824694482</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1193238436411976</v>
+        <v>0.1210509771029948</v>
       </c>
       <c r="M10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.12702849534982</v>
       </c>
       <c r="N10" t="n">
-        <v>4.176426177308977</v>
+        <v>4.237975785698606</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004321932596445966</v>
+        <v>0.00431271687013695</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002991073173066446</v>
+        <v>0.002997027429017953</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005590977071229034</v>
+        <v>0.0005597509843635526</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001033045748170887</v>
+        <v>0.001036493947908923</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005889349285582884</v>
+        <v>0.0005894502339337932</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01705865207726934</v>
+        <v>0.01700922303862318</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009885753452498211</v>
+        <v>0.009802820767895366</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001277067859669106</v>
+        <v>0.001281941200999306</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001898612872808055</v>
+        <v>0.001957330673147972</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001312472915018241</v>
+        <v>0.001308603085578598</v>
       </c>
     </row>
     <row r="11">
@@ -1308,46 +1308,46 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1824976994977321</v>
+        <v>0.1802913684560599</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3452986603517598</v>
+        <v>0.3465459166179319</v>
       </c>
       <c r="M11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.084108994242105</v>
       </c>
       <c r="N11" t="n">
-        <v>4.233252437525886</v>
+        <v>4.260313558854912</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002695819950591645</v>
+        <v>0.002733257216197332</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001724940052933724</v>
+        <v>0.001722193761365708</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001312637796841608</v>
+        <v>0.001315645779813892</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001874909692207699</v>
+        <v>0.001873257341608662</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001676548395499404</v>
+        <v>0.001671445189131837</v>
       </c>
       <c r="T11" t="n">
-        <v>0.008347934656468582</v>
+        <v>0.008519173098021407</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003442654374804505</v>
+        <v>0.003526720528374913</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002980443426954012</v>
+        <v>0.00300725694874557</v>
       </c>
       <c r="W11" t="n">
-        <v>0.003892770425993455</v>
+        <v>0.004227677013594756</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003643110374826549</v>
+        <v>0.003670979004647733</v>
       </c>
     </row>
     <row r="12">
@@ -1388,46 +1388,46 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1044963800343232</v>
+        <v>0.1045004028531513</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1275424662715627</v>
+        <v>0.1275452235151289</v>
       </c>
       <c r="M12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.089982626528647</v>
       </c>
       <c r="N12" t="n">
-        <v>4.061380054403066</v>
+        <v>4.108463327318218</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0009159074799388304</v>
+        <v>0.0009158516158195828</v>
       </c>
       <c r="P12" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0004820843341973374</v>
+        <v>0.0004820762617375363</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001174786939876925</v>
+        <v>0.001174786354567341</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004659018383056988</v>
+        <v>0.0004659019677374974</v>
       </c>
       <c r="T12" t="n">
-        <v>0.004000367069009281</v>
+        <v>0.004000147410888139</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02943848057414693</v>
+        <v>0.02943851980707652</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001111937687147566</v>
+        <v>0.001111923222144807</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03594037149499589</v>
+        <v>0.03594085991515948</v>
       </c>
       <c r="X12" t="n">
-        <v>0.002317218777374455</v>
+        <v>0.00231723272746222</v>
       </c>
     </row>
     <row r="13">
@@ -1468,46 +1468,46 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1317909138787342</v>
+        <v>0.1443570250143755</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2008708599122619</v>
+        <v>0.2187095491604443</v>
       </c>
       <c r="M13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.284315393262776</v>
       </c>
       <c r="N13" t="n">
-        <v>4.288834699930617</v>
+        <v>4.51567977581814</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002035632913171242</v>
+        <v>0.002105224092890962</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001467803482697654</v>
+        <v>0.001705262080890069</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0009022950225704934</v>
+        <v>0.0009283127061324889</v>
       </c>
       <c r="R13" t="n">
-        <v>0.008526752434270765</v>
+        <v>0.008650211624607083</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01465184370163046</v>
+        <v>0.01477562608661544</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01677870666896652</v>
+        <v>0.01681614225514103</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04358491745767994</v>
+        <v>0.0440895914784371</v>
       </c>
       <c r="V13" t="n">
-        <v>0.007247554864799007</v>
+        <v>0.007293313646723081</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02366645856284454</v>
+        <v>0.02387274856532783</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03953430976574845</v>
+        <v>0.03991274241042734</v>
       </c>
     </row>
     <row r="14">
@@ -1548,46 +1548,46 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1869492898432139</v>
+        <v>0.1882369422267624</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2743197642951365</v>
+        <v>0.276227815610285</v>
       </c>
       <c r="M14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.399378232032912</v>
       </c>
       <c r="N14" t="n">
-        <v>4.326634030391181</v>
+        <v>4.358713059953477</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01273754073208956</v>
+        <v>0.01272328519468487</v>
       </c>
       <c r="P14" t="n">
-        <v>0.003116661160176198</v>
+        <v>0.00317105273627055</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.007519622051376422</v>
+        <v>0.007528715583936452</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00694715051560166</v>
+        <v>0.00693444310215034</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01047395681203877</v>
+        <v>0.01055824826415903</v>
       </c>
       <c r="T14" t="n">
-        <v>0.03255484738591572</v>
+        <v>0.03211050747522869</v>
       </c>
       <c r="U14" t="n">
-        <v>0.000269012305192786</v>
+        <v>0.02191885708826445</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01481827867534919</v>
+        <v>0.01580386025966229</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01481733499839167</v>
+        <v>0.01453949753169552</v>
       </c>
       <c r="X14" t="n">
-        <v>0.030991649393644</v>
+        <v>0.02992868341229806</v>
       </c>
     </row>
     <row r="15">
@@ -1628,46 +1628,46 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1960420645582539</v>
+        <v>0.1874830231703039</v>
       </c>
       <c r="L15" t="n">
-        <v>0.279381087121396</v>
+        <v>0.2738406689335328</v>
       </c>
       <c r="M15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.085204214067701</v>
       </c>
       <c r="N15" t="n">
-        <v>4.326662476244422</v>
+        <v>4.242020397769503</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01259242399980739</v>
+        <v>0.01254241917934499</v>
       </c>
       <c r="P15" t="n">
-        <v>0.004959607549942636</v>
+        <v>0.004808876702551187</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.007641124420927807</v>
+        <v>0.007628422515599419</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005633914765786498</v>
+        <v>0.005527788073275897</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02521395221985542</v>
+        <v>0.02496862696886337</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03217399430349459</v>
+        <v>0.03198667718042063</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01499210614794427</v>
+        <v>0.01483979876365708</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0163566226379131</v>
+        <v>0.01635488726136984</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01187718662310406</v>
+        <v>0.01216612177749948</v>
       </c>
       <c r="X15" t="n">
-        <v>0.08835238774022416</v>
+        <v>0.08699806654188172</v>
       </c>
     </row>
     <row r="16">
@@ -1708,46 +1708,46 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5421174973423735</v>
+        <v>0.5161649251798621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5485102295930803</v>
+        <v>0.5289027221649324</v>
       </c>
       <c r="M16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.346437810309332</v>
       </c>
       <c r="N16" t="n">
-        <v>4.643241074490168</v>
+        <v>4.497654451769204</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02886203153188093</v>
+        <v>0.0281651377694198</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02044634333822731</v>
+        <v>0.01958518096781141</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02074035057850204</v>
+        <v>0.01984915215896495</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01327459689721378</v>
+        <v>0.01270990256982217</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01198014186595101</v>
+        <v>0.02222029913265714</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1863571767975405</v>
+        <v>0.08447027587891738</v>
       </c>
       <c r="U16" t="n">
-        <v>0.152869953486568</v>
+        <v>0.03338788909631528</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1454194107444872</v>
+        <v>0.05598673841203895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.08553360009668225</v>
+        <v>0.03195524007674559</v>
       </c>
       <c r="X16" t="n">
-        <v>2.286074118680861</v>
+        <v>18.89505989157118</v>
       </c>
     </row>
     <row r="17">
@@ -1788,46 +1788,46 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1754324955076012</v>
+        <v>0.1472285974082657</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2656662013964927</v>
+        <v>0.2360357464914354</v>
       </c>
       <c r="M17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.853984103588437</v>
       </c>
       <c r="N17" t="n">
-        <v>4.199328302826642</v>
+        <v>4.012166378646453</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01320438116933979</v>
+        <v>0.01304181252352631</v>
       </c>
       <c r="P17" t="n">
-        <v>0.002750801069478057</v>
+        <v>0.001315347535609482</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.006666346903864319</v>
+        <v>0.006565461335948802</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004592064581677076</v>
+        <v>0.003993807750292989</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0106935802375463</v>
+        <v>0.01044396415661191</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03244580643486972</v>
+        <v>0.03345641381409505</v>
       </c>
       <c r="U17" t="n">
-        <v>0.02285299616349317</v>
+        <v>0.04418673437050782</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01399994091914251</v>
+        <v>0.01429523897905623</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01149342771325293</v>
+        <v>0.02275818103347639</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0211548343745613</v>
+        <v>0.02236502629756599</v>
       </c>
     </row>
     <row r="18">
@@ -1868,46 +1868,46 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2393672981629223</v>
+        <v>0.2424607087442707</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2619967626825924</v>
+        <v>0.2651971061528096</v>
       </c>
       <c r="M18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.298420190621356</v>
       </c>
       <c r="N18" t="n">
-        <v>4.250715374390796</v>
+        <v>4.300116150274684</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01323169925071398</v>
+        <v>0.01326870139802743</v>
       </c>
       <c r="P18" t="n">
-        <v>0.006727476197229241</v>
+        <v>0.006809503203409333</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.006035452242969592</v>
+        <v>0.006045214067951051</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008406827621695458</v>
+        <v>0.008471813273374094</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008785265970355591</v>
+        <v>0.008835381506191332</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03322262828865942</v>
+        <v>0.03311493142453596</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01551800064002042</v>
+        <v>0.01546026927990645</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01271068539681428</v>
+        <v>0.01276674356694847</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01418394935344538</v>
+        <v>0.01479202865830817</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01548824021431785</v>
+        <v>0.01543526946701237</v>
       </c>
     </row>
     <row r="19">
@@ -1948,46 +1948,46 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1872651872905624</v>
+        <v>0.161033465819801</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2369565168857554</v>
+        <v>0.2233885571873788</v>
       </c>
       <c r="M19" t="n">
-        <v>4.597747250805167</v>
+        <v>3.990866149206148</v>
       </c>
       <c r="N19" t="n">
-        <v>4.654742948159486</v>
+        <v>4.377813604369669</v>
       </c>
       <c r="O19" t="n">
-        <v>0.005028598311069156</v>
+        <v>0.004944859657935866</v>
       </c>
       <c r="P19" t="n">
-        <v>0.01015851412942509</v>
+        <v>0.009647790526085663</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003395789422457008</v>
+        <v>0.003380252631110283</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001552526588885666</v>
+        <v>0.001508451365663482</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03201925623782433</v>
+        <v>0.03165977277557139</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01948566678466332</v>
+        <v>0.01933349438468121</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02445341275556395</v>
+        <v>0.02425993118002748</v>
       </c>
       <c r="V19" t="n">
-        <v>0.008999629501950173</v>
+        <v>0.008963682648373789</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006742923643828256</v>
+        <v>0.006852669240307164</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1601238362306998</v>
+        <v>0.159790445284404</v>
       </c>
     </row>
     <row r="20">
@@ -2028,46 +2028,46 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2655681489740055</v>
+        <v>0.2706740016525256</v>
       </c>
       <c r="L20" t="n">
-        <v>0.286746563530882</v>
+        <v>0.2927341412025184</v>
       </c>
       <c r="M20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.627752525577289</v>
       </c>
       <c r="N20" t="n">
-        <v>4.509483281727169</v>
+        <v>4.593214902107496</v>
       </c>
       <c r="O20" t="n">
-        <v>0.008339365019200929</v>
+        <v>0.008405074024867456</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0006291606115321974</v>
+        <v>0.0008181292013049757</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.004321680070792274</v>
+        <v>0.004350963669534897</v>
       </c>
       <c r="R20" t="n">
-        <v>0.00547998374946375</v>
+        <v>0.005514120826268748</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01479690492523568</v>
+        <v>0.01512166055457031</v>
       </c>
       <c r="T20" t="n">
-        <v>0.02161086706925803</v>
+        <v>0.02149601195623009</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01615307325416906</v>
+        <v>0.01607547089742069</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01009417208233144</v>
+        <v>0.01013008342966108</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01109133262096947</v>
+        <v>0.01141365875624619</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02899934012743344</v>
+        <v>0.02918885627428229</v>
       </c>
     </row>
     <row r="21">
@@ -2108,46 +2108,46 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1248690725745343</v>
+        <v>0.1202941340488625</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1390829116528026</v>
+        <v>0.1378533115986938</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.107682434211664</v>
       </c>
       <c r="N21" t="n">
-        <v>4.340480735682785</v>
+        <v>4.121165225382007</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01641214435089532</v>
+        <v>0.01552863482697239</v>
       </c>
       <c r="P21" t="n">
-        <v>0.05382319193973008</v>
+        <v>0.05125495867531689</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.004710534213953848</v>
+        <v>0.00495496347823411</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000000063e-05</v>
+        <v>1.000000000033484e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.000000000053727e-05</v>
+        <v>1.000000000931178e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05704569672981988</v>
+        <v>0.05404724424884073</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1674422907748445</v>
+        <v>0.159252307059572</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01351896569495002</v>
+        <v>0.01426035089263716</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01074239836055871</v>
+        <v>0.01114106901589464</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03636189043266625</v>
+        <v>0.03839815370889071</v>
       </c>
     </row>
     <row r="22">
@@ -2188,46 +2188,46 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2818072516144415</v>
+        <v>0.2818005832925195</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3252739446343098</v>
+        <v>0.3218063814813968</v>
       </c>
       <c r="M22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.137156494914622</v>
       </c>
       <c r="N22" t="n">
-        <v>4.39486516831361</v>
+        <v>4.309732006266833</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005827351896252475</v>
+        <v>0.005797547416033553</v>
       </c>
       <c r="P22" t="n">
-        <v>2.287419574685069e-05</v>
+        <v>1.00000000001984e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002665233057996927</v>
+        <v>0.002656208004106704</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003442149497698334</v>
+        <v>0.003429210519692688</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0126747645367958</v>
+        <v>0.01261914908567431</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01630349281011565</v>
+        <v>0.01601341512802824</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01901921188194897</v>
+        <v>0.01477007531210635</v>
       </c>
       <c r="V22" t="n">
-        <v>0.008670067925649994</v>
+        <v>0.00848921117124949</v>
       </c>
       <c r="W22" t="n">
-        <v>0.01016914079105187</v>
+        <v>0.009280671544128939</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02934660545175201</v>
+        <v>0.02761135262466899</v>
       </c>
     </row>
     <row r="23">
@@ -2268,46 +2268,46 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2103762298263011</v>
+        <v>0.208871687187535</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2749681303660277</v>
+        <v>0.2718044786969178</v>
       </c>
       <c r="M23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.863994820752609</v>
       </c>
       <c r="N23" t="n">
-        <v>4.198316898992754</v>
+        <v>4.10878782592642</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01078447777135767</v>
+        <v>0.01076874551793343</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004327474487364189</v>
+        <v>0.004270830336473298</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.003967677982716742</v>
+        <v>0.003955459835768994</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006246388358236002</v>
+        <v>0.006148793146596763</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02454156017317849</v>
+        <v>0.02437991319119103</v>
       </c>
       <c r="T23" t="n">
-        <v>0.02721776141716794</v>
+        <v>0.02713848602460157</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01969216792512986</v>
+        <v>0.01945583085355903</v>
       </c>
       <c r="V23" t="n">
-        <v>0.009719959237755814</v>
+        <v>0.009726277884612841</v>
       </c>
       <c r="W23" t="n">
-        <v>0.01602034837259134</v>
+        <v>0.01595988854778212</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07776311098842317</v>
+        <v>0.07673098070186342</v>
       </c>
     </row>
     <row r="24">
@@ -2348,46 +2348,46 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3675699485021797</v>
+        <v>0.3875416039382416</v>
       </c>
       <c r="L24" t="n">
-        <v>0.442821378039556</v>
+        <v>0.4585213846789534</v>
       </c>
       <c r="M24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.305819674281706</v>
       </c>
       <c r="N24" t="n">
-        <v>4.305748638173318</v>
+        <v>4.373982753815935</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01353389639905295</v>
+        <v>0.01335184653723498</v>
       </c>
       <c r="P24" t="n">
-        <v>0.009647120203042668</v>
+        <v>0.009495457683851587</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01323895176100257</v>
+        <v>0.01324016456593231</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01324212348481177</v>
+        <v>0.01331352524374036</v>
       </c>
       <c r="S24" t="n">
-        <v>0.358217434378986</v>
+        <v>1.000000002711727e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0.06646379268310354</v>
+        <v>0.04057200417275288</v>
       </c>
       <c r="U24" t="n">
-        <v>0.01997589477851445</v>
+        <v>0.0266029510037471</v>
       </c>
       <c r="V24" t="n">
-        <v>0.04125864049048487</v>
+        <v>0.03168082067550165</v>
       </c>
       <c r="W24" t="n">
-        <v>0.08010941136362196</v>
+        <v>0.02984261827472873</v>
       </c>
       <c r="X24" t="n">
-        <v>4614.445923029393</v>
+        <v>2.832379455353822</v>
       </c>
     </row>
     <row r="25">
@@ -2428,46 +2428,46 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2172140991091026</v>
+        <v>0.215848059616466</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2288449983322856</v>
+        <v>0.2284594467336942</v>
       </c>
       <c r="M25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.310157944037903</v>
       </c>
       <c r="N25" t="n">
-        <v>4.343883516427645</v>
+        <v>4.340621142564224</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002224733894522908</v>
+        <v>0.002231536890875667</v>
       </c>
       <c r="P25" t="n">
-        <v>1.000000000002801e-05</v>
+        <v>1.00000000000183e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.000543550064982269</v>
+        <v>0.0005427421474549116</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003329183849289244</v>
+        <v>0.0003337243919490771</v>
       </c>
       <c r="S25" t="n">
-        <v>9.952624625524875e-05</v>
+        <v>9.811530508613571e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.005392791782728346</v>
+        <v>0.005387245478812809</v>
       </c>
       <c r="U25" t="n">
-        <v>0.002853336407292126</v>
+        <v>0.002879068444643339</v>
       </c>
       <c r="V25" t="n">
-        <v>0.00154434385537854</v>
+        <v>0.001544802675924805</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001299293432618454</v>
+        <v>0.001344254172780884</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001332816705657222</v>
+        <v>0.001314073681162972</v>
       </c>
     </row>
     <row r="26">
@@ -2508,46 +2508,46 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3294247814180385</v>
+        <v>0.3197948172394026</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3152311360895437</v>
+        <v>0.3076761724502429</v>
       </c>
       <c r="M26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.224153844393832</v>
       </c>
       <c r="N26" t="n">
-        <v>4.389062043313722</v>
+        <v>4.299738132353408</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002878184586431424</v>
+        <v>0.002886451885566999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.00159196433162706</v>
+        <v>0.001543354958377238</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0006683935240617655</v>
+        <v>0.000660358953136808</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005745272852127742</v>
+        <v>0.0005625695089046828</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003304395969432639</v>
+        <v>0.0003215504714468515</v>
       </c>
       <c r="T26" t="n">
-        <v>0.005704056449412808</v>
+        <v>0.005709499860443091</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002425270720737341</v>
+        <v>0.002436937228166082</v>
       </c>
       <c r="V26" t="n">
-        <v>0.001726641877084286</v>
+        <v>0.00171961532673345</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001444177880058499</v>
+        <v>0.001513624191671615</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001287572091569202</v>
+        <v>0.001258532393978183</v>
       </c>
     </row>
     <row r="27">
@@ -2588,46 +2588,46 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2426473726089903</v>
+        <v>0.2439507965539418</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3074602625865642</v>
+        <v>0.3067422390276155</v>
       </c>
       <c r="M27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.149671453558346</v>
       </c>
       <c r="N27" t="n">
-        <v>4.155598304746717</v>
+        <v>4.151068964910465</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001457830202273945</v>
+        <v>0.001458714140586512</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005713633186129977</v>
+        <v>0.0005687835756680706</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001201570301404702</v>
+        <v>0.00119843705062235</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006443059553630736</v>
+        <v>0.0006419722126537749</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007206141473733462</v>
+        <v>0.0007223262149807405</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003396614213595701</v>
+        <v>0.003386164804875829</v>
       </c>
       <c r="U27" t="n">
-        <v>0.002344743242044198</v>
+        <v>0.00242254127015918</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002465594667381731</v>
+        <v>0.002472152956502945</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001612717070994784</v>
+        <v>0.001712390984599777</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001822500119372669</v>
+        <v>0.001794196421560956</v>
       </c>
     </row>
     <row r="28">
@@ -2668,46 +2668,46 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4028027310904022</v>
+        <v>0.3989356014586465</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3961586001697605</v>
+        <v>0.4106034617169131</v>
       </c>
       <c r="M28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.114744299841788</v>
       </c>
       <c r="N28" t="n">
-        <v>4.168585682284601</v>
+        <v>4.29421293162847</v>
       </c>
       <c r="O28" t="n">
-        <v>0.002046703051580896</v>
+        <v>0.0020037747322748</v>
       </c>
       <c r="P28" t="n">
-        <v>1.000000000000029e-05</v>
+        <v>1.000000000000033e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001493971551886288</v>
+        <v>0.001514722681317508</v>
       </c>
       <c r="R28" t="n">
-        <v>0.004785169238679765</v>
+        <v>0.005014510551538672</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01042114228629274</v>
+        <v>0.01036748981554327</v>
       </c>
       <c r="T28" t="n">
-        <v>0.004705479568672258</v>
+        <v>0.004603876541967948</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01115990522819833</v>
+        <v>0.01091474989644152</v>
       </c>
       <c r="V28" t="n">
-        <v>0.00325794082181607</v>
+        <v>0.00331408430370514</v>
       </c>
       <c r="W28" t="n">
-        <v>0.008734372874197632</v>
+        <v>0.009606173114659567</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02408461915530766</v>
+        <v>0.02351990982884054</v>
       </c>
     </row>
     <row r="29">
@@ -2748,46 +2748,46 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.512131704883432</v>
+        <v>0.5337507387871602</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3338854386569521</v>
+        <v>0.3455125462067315</v>
       </c>
       <c r="M29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.255427909449321</v>
       </c>
       <c r="N29" t="n">
-        <v>4.104282766141094</v>
+        <v>4.202276187780864</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004746714994801691</v>
+        <v>0.004750996569864848</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0182658057159367</v>
+        <v>0.01809454868918335</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.358790110329943e-05</v>
+        <v>0.0001807004228334998</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01588781043658673</v>
+        <v>0.01725164143317796</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009402973664420096</v>
+        <v>0.009480158620399576</v>
       </c>
       <c r="T29" t="n">
-        <v>0.009279152869440567</v>
+        <v>0.009135815873177288</v>
       </c>
       <c r="U29" t="n">
-        <v>0.06643753593536167</v>
+        <v>0.06252823516812714</v>
       </c>
       <c r="V29" t="n">
-        <v>0.002958887059674785</v>
+        <v>0.002987836248732887</v>
       </c>
       <c r="W29" t="n">
-        <v>0.02816274996616822</v>
+        <v>0.03301411606916037</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01666201922242477</v>
+        <v>0.01607130683896535</v>
       </c>
     </row>
     <row r="30">
@@ -2828,46 +2828,46 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4712108421979429</v>
+        <v>0.4912707336485012</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3828505200562759</v>
+        <v>0.4029182866425092</v>
       </c>
       <c r="M30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.515175522261403</v>
       </c>
       <c r="N30" t="n">
-        <v>4.107453753871422</v>
+        <v>4.313113498799031</v>
       </c>
       <c r="O30" t="n">
-        <v>0.00247271511803504</v>
+        <v>0.002505461740369046</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004669477946989609</v>
+        <v>0.005081990042261474</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0001553668418524192</v>
+        <v>0.000233203877926856</v>
       </c>
       <c r="R30" t="n">
-        <v>0.008727227563238982</v>
+        <v>0.009303857418504993</v>
       </c>
       <c r="S30" t="n">
-        <v>0.003890412876557163</v>
+        <v>0.004159474905871037</v>
       </c>
       <c r="T30" t="n">
-        <v>0.004767102022297919</v>
+        <v>0.004859962819699638</v>
       </c>
       <c r="U30" t="n">
-        <v>0.00401125648024239</v>
+        <v>0.009416457870441094</v>
       </c>
       <c r="V30" t="n">
-        <v>0.002905360025233848</v>
+        <v>0.003027736050667094</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01790229924469313</v>
+        <v>0.01538458243787846</v>
       </c>
       <c r="X30" t="n">
-        <v>0.005480361990924006</v>
+        <v>0.00566548586324424</v>
       </c>
     </row>
     <row r="31">
@@ -2908,46 +2908,46 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5036033975236921</v>
+        <v>0.4902078464552742</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4306085667695821</v>
+        <v>0.4307282667397589</v>
       </c>
       <c r="M31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.249538389327932</v>
       </c>
       <c r="N31" t="n">
-        <v>4.404431640777941</v>
+        <v>4.410351733710971</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002752105272760849</v>
+        <v>0.002730239733842983</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007331721926542179</v>
+        <v>0.007275503169651897</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0002775299860761727</v>
+        <v>0.0002667186749248477</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001798155856247989</v>
+        <v>0.001785835699265363</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0005837936050434623</v>
+        <v>0.00056394847497899</v>
       </c>
       <c r="T31" t="n">
-        <v>0.005027208092591074</v>
+        <v>0.004947534112347361</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01712550721705237</v>
+        <v>0.01692632058017633</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00254776276289189</v>
+        <v>0.00255117353923214</v>
       </c>
       <c r="W31" t="n">
-        <v>0.002840409966176999</v>
+        <v>0.003007772002258971</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002901901285554329</v>
+        <v>0.002801064412960188</v>
       </c>
     </row>
     <row r="32">
@@ -2988,46 +2988,46 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4586807473470598</v>
+        <v>0.5003204670714311</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3970435335101308</v>
+        <v>0.4277098015031122</v>
       </c>
       <c r="M32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.53028971271256</v>
       </c>
       <c r="N32" t="n">
-        <v>4.108208706196117</v>
+        <v>4.426130147752106</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008162267597497274</v>
+        <v>0.0008350083291765586</v>
       </c>
       <c r="P32" t="n">
-        <v>0.004980580138573445</v>
+        <v>0.005247746006639017</v>
       </c>
       <c r="Q32" t="n">
-        <v>1e-05</v>
+        <v>1.000000000000001e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004160374796625478</v>
+        <v>0.004418886554165519</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001309498348235365</v>
+        <v>0.001401838780852578</v>
       </c>
       <c r="T32" t="n">
-        <v>0.002802466342181446</v>
+        <v>0.00281365799203623</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01097215926106403</v>
+        <v>0.0113549929956145</v>
       </c>
       <c r="V32" t="n">
-        <v>0.002604218384186343</v>
+        <v>0.002600330117320171</v>
       </c>
       <c r="W32" t="n">
-        <v>0.007461868497858889</v>
+        <v>0.008108609775447266</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003603910971280884</v>
+        <v>0.003592609364448746</v>
       </c>
     </row>
     <row r="33">
@@ -3066,46 +3066,46 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2751054178962024</v>
+        <v>0.2851358817564152</v>
       </c>
       <c r="L33" t="n">
-        <v>0.304276628707371</v>
+        <v>0.318932250993743</v>
       </c>
       <c r="M33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.308512879316226</v>
       </c>
       <c r="N33" t="n">
-        <v>4.14580494093494</v>
+        <v>4.270877230228868</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006344100700986528</v>
+        <v>0.006255038232011506</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003832565088781347</v>
+        <v>0.004238498551876357</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003853317115930239</v>
+        <v>0.003966480546542436</v>
       </c>
       <c r="R33" t="n">
-        <v>0.007175092595513321</v>
+        <v>0.007572420642581414</v>
       </c>
       <c r="S33" t="n">
-        <v>0.004029274241962195</v>
+        <v>0.004151247082158103</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01625763807564425</v>
+        <v>0.01577010449583528</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02398795891729371</v>
+        <v>0.02412089826765769</v>
       </c>
       <c r="V33" t="n">
-        <v>0.008446272424582601</v>
+        <v>0.008798785252329851</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01282903336003163</v>
+        <v>0.01425303978700799</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007692459005278663</v>
+        <v>0.007886086965499323</v>
       </c>
     </row>
     <row r="34">
@@ -3146,46 +3146,46 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5165578838213738</v>
+        <v>0.5350531219152354</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4271302677901361</v>
+        <v>0.4497671777617613</v>
       </c>
       <c r="M34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.263995602912937</v>
       </c>
       <c r="N34" t="n">
-        <v>4.12171014191164</v>
+        <v>4.286052599309091</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005371648193829558</v>
+        <v>0.005327415999576042</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01399468239549424</v>
+        <v>0.01468639974602328</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.002692426888953022</v>
+        <v>0.00299204878747737</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01407975244804937</v>
+        <v>0.01477537078025103</v>
       </c>
       <c r="S34" t="n">
-        <v>0.007884168675975878</v>
+        <v>0.008485399023264808</v>
       </c>
       <c r="T34" t="n">
-        <v>0.008189461916496475</v>
+        <v>0.008064321238122247</v>
       </c>
       <c r="U34" t="n">
-        <v>0.05205895337648211</v>
+        <v>0.0557478055123624</v>
       </c>
       <c r="V34" t="n">
-        <v>0.005330002302714341</v>
+        <v>0.005681397228123481</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01719152436336144</v>
+        <v>0.01887525403640121</v>
       </c>
       <c r="X34" t="n">
-        <v>0.00712270322322664</v>
+        <v>0.007357860210382738</v>
       </c>
     </row>
     <row r="35">
@@ -3226,46 +3226,46 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3001566209783726</v>
+        <v>0.3019486698931895</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2386046329709729</v>
+        <v>0.2474304893651948</v>
       </c>
       <c r="M35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.049554670774522</v>
       </c>
       <c r="N35" t="n">
-        <v>4.028364179114558</v>
+        <v>4.156376315010339</v>
       </c>
       <c r="O35" t="n">
-        <v>0.002535360628805409</v>
+        <v>0.002523944227794765</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0719175884115781</v>
+        <v>0.06033587516207787</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0005977303064690831</v>
+        <v>0.000604247511046614</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004620426465677395</v>
+        <v>0.004779294493895975</v>
       </c>
       <c r="S35" t="n">
-        <v>0.000935651560586928</v>
+        <v>0.0009526229454978009</v>
       </c>
       <c r="T35" t="n">
-        <v>0.006918675980607555</v>
+        <v>0.01061879416498299</v>
       </c>
       <c r="U35" t="n">
-        <v>5.69525062283049</v>
+        <v>21.31882728780888</v>
       </c>
       <c r="V35" t="n">
-        <v>0.002143266710383263</v>
+        <v>0.002246607056725409</v>
       </c>
       <c r="W35" t="n">
-        <v>0.006339000125688511</v>
+        <v>0.01873085958607459</v>
       </c>
       <c r="X35" t="n">
-        <v>0.002554260610836954</v>
+        <v>0.002611759162348447</v>
       </c>
     </row>
     <row r="36">
@@ -3306,46 +3306,46 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4200622561347667</v>
+        <v>0.4306133506575378</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3842233609471395</v>
+        <v>0.3952362728840799</v>
       </c>
       <c r="M36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.307865273041947</v>
       </c>
       <c r="N36" t="n">
-        <v>4.208404567285298</v>
+        <v>4.321572623486516</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001333614522460875</v>
+        <v>0.001343523339487707</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002678251338008301</v>
+        <v>0.002753977254333692</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.000413266067278517</v>
+        <v>0.0004271144016157931</v>
       </c>
       <c r="R36" t="n">
-        <v>0.001873680330738568</v>
+        <v>0.00193282878989933</v>
       </c>
       <c r="S36" t="n">
-        <v>0.00127385458188844</v>
+        <v>0.001308574399388756</v>
       </c>
       <c r="T36" t="n">
-        <v>0.003556242156826433</v>
+        <v>0.003546840140929287</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006101630553988934</v>
+        <v>0.006142816038114112</v>
       </c>
       <c r="V36" t="n">
-        <v>0.002552784854269766</v>
+        <v>0.002583706314445259</v>
       </c>
       <c r="W36" t="n">
-        <v>0.00342371857628093</v>
+        <v>0.003628160873148946</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004575424679348516</v>
+        <v>0.004515743683529813</v>
       </c>
     </row>
     <row r="37">
@@ -3386,46 +3386,46 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1057540787127461</v>
+        <v>0.1032759135620988</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1082742646329419</v>
+        <v>0.105288088556548</v>
       </c>
       <c r="M37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.230764125716685</v>
       </c>
       <c r="N37" t="n">
-        <v>4.363107439453987</v>
+        <v>4.263240945631649</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007640484752974908</v>
+        <v>0.007667241941911612</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003418168024041415</v>
+        <v>0.003373473473283984</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.00113296453581415</v>
+        <v>0.001128822814805678</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0008513383794226677</v>
+        <v>0.0008424215255491023</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002290974793066988</v>
+        <v>0.002261621751080345</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02813471437153012</v>
+        <v>0.02824965751043103</v>
       </c>
       <c r="U37" t="n">
-        <v>0.009443155983499422</v>
+        <v>0.009400509936786258</v>
       </c>
       <c r="V37" t="n">
-        <v>0.003049368790298186</v>
+        <v>0.003042171779284847</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002528860061383794</v>
+        <v>0.002556232092759398</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005800457770313364</v>
+        <v>0.005709979705498007</v>
       </c>
     </row>
     <row r="38">
@@ -3466,46 +3466,46 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1483762115382365</v>
+        <v>0.1416438943560188</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1143904954562443</v>
+        <v>0.1093720223530449</v>
       </c>
       <c r="M38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.113546643685265</v>
       </c>
       <c r="N38" t="n">
-        <v>4.354453170822766</v>
+        <v>4.195688196265935</v>
       </c>
       <c r="O38" t="n">
-        <v>0.009343978604362979</v>
+        <v>0.009403217904520443</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002610231126538195</v>
+        <v>0.002589265482107528</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0006799883616167743</v>
+        <v>0.0006754920509172869</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0004808628254200616</v>
+        <v>0.0004656697738782062</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0004502748278017758</v>
+        <v>0.0003975030949684453</v>
       </c>
       <c r="T38" t="n">
-        <v>0.03117770219124168</v>
+        <v>0.0314208676008576</v>
       </c>
       <c r="U38" t="n">
-        <v>0.009151096554616933</v>
+        <v>0.009153900516608731</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002441298422847776</v>
+        <v>0.002435890371761852</v>
       </c>
       <c r="W38" t="n">
-        <v>0.002101780045653066</v>
+        <v>0.002125676676037555</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003200076127722264</v>
+        <v>0.003144106513486889</v>
       </c>
     </row>
     <row r="39">
@@ -3546,46 +3546,46 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1491847814540822</v>
+        <v>0.1514776863482813</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1314842053722177</v>
+        <v>0.1340398372572274</v>
       </c>
       <c r="M39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.258531293425802</v>
       </c>
       <c r="N39" t="n">
-        <v>4.189057783751848</v>
+        <v>4.266069201335666</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006482179711522262</v>
+        <v>0.006493221980259241</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002005621131915364</v>
+        <v>0.002046783212853728</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001057067149692427</v>
+        <v>0.001058373386804991</v>
       </c>
       <c r="R39" t="n">
-        <v>0.00231422911827573</v>
+        <v>0.002328310731240582</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001416746411028733</v>
+        <v>0.001423219936509659</v>
       </c>
       <c r="T39" t="n">
-        <v>0.01691605922992969</v>
+        <v>0.01689977535532027</v>
       </c>
       <c r="U39" t="n">
-        <v>0.009747851000706289</v>
+        <v>0.009748034530251472</v>
       </c>
       <c r="V39" t="n">
-        <v>0.002826566106864436</v>
+        <v>0.002831396688727956</v>
       </c>
       <c r="W39" t="n">
-        <v>0.003955346121353308</v>
+        <v>0.004037135450186052</v>
       </c>
       <c r="X39" t="n">
-        <v>0.003037090258338885</v>
+        <v>0.00302366556319029</v>
       </c>
     </row>
     <row r="40">
@@ -3626,46 +3626,46 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2450518885796166</v>
+        <v>0.2425659656922763</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4084427736099533</v>
+        <v>0.3996850531509176</v>
       </c>
       <c r="M40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.328296976830683</v>
       </c>
       <c r="N40" t="n">
-        <v>4.622222173551737</v>
+        <v>4.517619555015153</v>
       </c>
       <c r="O40" t="n">
-        <v>0.004173634811092499</v>
+        <v>0.00414377425017839</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002738497739059688</v>
+        <v>0.002646521723473389</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002503057831416969</v>
+        <v>0.002487207458091428</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002486886543068141</v>
+        <v>0.002452740023335495</v>
       </c>
       <c r="S40" t="n">
-        <v>0.05549088062129245</v>
+        <v>0.05427708640162198</v>
       </c>
       <c r="T40" t="n">
-        <v>0.008198659383323727</v>
+        <v>0.008114137801291416</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004452094025965542</v>
+        <v>0.004242165868538716</v>
       </c>
       <c r="V40" t="n">
-        <v>0.004890702979248473</v>
+        <v>0.004820983694162223</v>
       </c>
       <c r="W40" t="n">
-        <v>0.003604343686259607</v>
+        <v>0.003731053961252173</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2663734264847015</v>
+        <v>0.2583072179159262</v>
       </c>
     </row>
     <row r="41">
@@ -3706,46 +3706,46 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2672649319402196</v>
+        <v>0.2579668642380593</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2888340642701547</v>
+        <v>0.2828059115722345</v>
       </c>
       <c r="M41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.436658074738552</v>
       </c>
       <c r="N41" t="n">
-        <v>4.613105637494948</v>
+        <v>4.507114181196516</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001943288197102935</v>
+        <v>0.001926746162240694</v>
       </c>
       <c r="P41" t="n">
-        <v>0.003188312729626718</v>
+        <v>0.003097239927249255</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.000991081161385173</v>
+        <v>0.00099409428109113</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009738612473913832</v>
+        <v>0.0009567194267890806</v>
       </c>
       <c r="S41" t="n">
-        <v>0.003973097041301277</v>
+        <v>0.003921445231172699</v>
       </c>
       <c r="T41" t="n">
-        <v>0.004839300878081535</v>
+        <v>0.00478096832495594</v>
       </c>
       <c r="U41" t="n">
-        <v>0.005311231181973131</v>
+        <v>0.005278801004565194</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002241931876447594</v>
+        <v>0.002241589299968832</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002100797335360674</v>
+        <v>0.002146722492848939</v>
       </c>
       <c r="X41" t="n">
-        <v>0.007030688893087824</v>
+        <v>0.006902764030262055</v>
       </c>
     </row>
     <row r="42">
@@ -3786,46 +3786,46 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3163391884519726</v>
+        <v>0.317014523922711</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4073753104701423</v>
+        <v>0.3994590236895776</v>
       </c>
       <c r="M42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.517744602412055</v>
       </c>
       <c r="N42" t="n">
-        <v>4.593229920588862</v>
+        <v>4.483268743019152</v>
       </c>
       <c r="O42" t="n">
-        <v>0.005372188840992549</v>
+        <v>0.0052624267295362</v>
       </c>
       <c r="P42" t="n">
-        <v>0.004020120363709684</v>
+        <v>0.003751601650900459</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.004277642560590354</v>
+        <v>0.00422826523180969</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003050259609795899</v>
+        <v>0.003011014245468022</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0228292454936393</v>
+        <v>0.003492938453932675</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01392993527729039</v>
+        <v>0.0236488520407821</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0101164311338947</v>
+        <v>0.01567208263111223</v>
       </c>
       <c r="V42" t="n">
-        <v>0.01153988741318526</v>
+        <v>0.01232767719795073</v>
       </c>
       <c r="W42" t="n">
-        <v>0.006215496943070814</v>
+        <v>0.01288233031174165</v>
       </c>
       <c r="X42" t="n">
-        <v>5.529871894660746</v>
+        <v>3.865794396841796</v>
       </c>
     </row>
     <row r="43">
@@ -3866,46 +3866,46 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1604370972748382</v>
+        <v>0.1593858374334936</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2987200218761396</v>
+        <v>0.2958523719248615</v>
       </c>
       <c r="M43" t="n">
-        <v>4.103051778684014</v>
+        <v>3.921309732134107</v>
       </c>
       <c r="N43" t="n">
-        <v>4.275978902575533</v>
+        <v>4.233285879022268</v>
       </c>
       <c r="O43" t="n">
-        <v>0.03487959503122448</v>
+        <v>0.03496846901355562</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0138394746752003</v>
+        <v>0.01374484320356314</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.01524263351597576</v>
+        <v>0.0151856681346546</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0171620745509416</v>
+        <v>0.01698041540588782</v>
       </c>
       <c r="S43" t="n">
-        <v>0.05778882962317037</v>
+        <v>0.05767487231117728</v>
       </c>
       <c r="T43" t="n">
-        <v>0.09375667043045369</v>
+        <v>0.09380389881237274</v>
       </c>
       <c r="U43" t="n">
-        <v>0.021958061297082</v>
+        <v>0.02207080206657796</v>
       </c>
       <c r="V43" t="n">
-        <v>0.02993540140733379</v>
+        <v>0.02980073558654967</v>
       </c>
       <c r="W43" t="n">
-        <v>0.03789821834523062</v>
+        <v>0.03866146084124845</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1575253055576477</v>
+        <v>0.1572835530679738</v>
       </c>
     </row>
     <row r="44">
@@ -3946,46 +3946,46 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1778728783246155</v>
+        <v>0.1743546614482898</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3794939323828581</v>
+        <v>0.3610732774323228</v>
       </c>
       <c r="M44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.252007996567885</v>
       </c>
       <c r="N44" t="n">
-        <v>4.593247325858668</v>
+        <v>4.379586724816082</v>
       </c>
       <c r="O44" t="n">
-        <v>0.05846783010020204</v>
+        <v>0.05943180072319394</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02311492830091423</v>
+        <v>0.02258796355990136</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02198754334425015</v>
+        <v>0.02157829855557556</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01213743167205847</v>
+        <v>0.01165903541634562</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02338994656184534</v>
+        <v>0.02252466555922277</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1699189784466703</v>
+        <v>0.1751135108474007</v>
       </c>
       <c r="U44" t="n">
-        <v>0.04190353661078716</v>
+        <v>0.04189371151768493</v>
       </c>
       <c r="V44" t="n">
-        <v>0.05018439496563137</v>
+        <v>0.04916033192741588</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02371853443227965</v>
+        <v>0.02319956777261208</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04917515322695554</v>
+        <v>0.04696270116222825</v>
       </c>
     </row>
     <row r="45">
@@ -4026,46 +4026,46 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.399617491041528</v>
+        <v>0.3961005288343256</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2462967391959038</v>
+        <v>0.2479943294578413</v>
       </c>
       <c r="M45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.214350986480778</v>
       </c>
       <c r="N45" t="n">
-        <v>4.265819315629261</v>
+        <v>4.321283307910669</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1297926601708286</v>
+        <v>0.1307536841507036</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1317089525015838</v>
+        <v>0.1320966209382474</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.05099348232869915</v>
+        <v>0.05081882791349295</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09224052821307979</v>
+        <v>0.09173536452010415</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1077534075404519</v>
+        <v>0.1078988148880706</v>
       </c>
       <c r="T45" t="n">
-        <v>0.6299825418375563</v>
+        <v>0.6328950612962737</v>
       </c>
       <c r="U45" t="n">
-        <v>0.4290940398368555</v>
+        <v>0.4249006086480794</v>
       </c>
       <c r="V45" t="n">
-        <v>0.1504124830159988</v>
+        <v>0.151324651590732</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2359641164312501</v>
+        <v>0.2474850442376834</v>
       </c>
       <c r="X45" t="n">
-        <v>0.3902934712518307</v>
+        <v>0.3929057540413145</v>
       </c>
     </row>
     <row r="46">
@@ -4106,46 +4106,46 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4729359869420497</v>
+        <v>0.4197523519087317</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3610061853247347</v>
+        <v>0.3537994247664817</v>
       </c>
       <c r="M46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.774562388265622</v>
       </c>
       <c r="N46" t="n">
-        <v>4.4985356306696</v>
+        <v>4.475097579018535</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06969731571682189</v>
+        <v>0.06990515626302188</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04604323163671036</v>
+        <v>0.0447362377903212</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02564329266509691</v>
+        <v>0.02429470085322225</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03885541277465008</v>
+        <v>0.0363765242040655</v>
       </c>
       <c r="S46" t="n">
-        <v>0.177482010203954</v>
+        <v>0.1859470277317496</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1864652326621196</v>
+        <v>0.1891339483173926</v>
       </c>
       <c r="U46" t="n">
-        <v>0.09280673725791327</v>
+        <v>0.08991401939022291</v>
       </c>
       <c r="V46" t="n">
-        <v>0.0487387228363372</v>
+        <v>0.0464486439283922</v>
       </c>
       <c r="W46" t="n">
-        <v>0.05550712568268736</v>
+        <v>0.05656817999001105</v>
       </c>
       <c r="X46" t="n">
-        <v>1.730048315772004</v>
+        <v>2.115862403045977</v>
       </c>
     </row>
     <row r="47">
@@ -4186,46 +4186,46 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.251984504906933</v>
+        <v>0.2493695583752376</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3439983669287057</v>
+        <v>0.3343697951216354</v>
       </c>
       <c r="M47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.220558446554917</v>
       </c>
       <c r="N47" t="n">
-        <v>4.414463722143681</v>
+        <v>4.341455675135808</v>
       </c>
       <c r="O47" t="n">
-        <v>0.04701575692524116</v>
+        <v>0.04722494907936614</v>
       </c>
       <c r="P47" t="n">
-        <v>0.02102559070355592</v>
+        <v>0.02084494714261795</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.01802001458160042</v>
+        <v>0.0177498432008436</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01594605437272408</v>
+        <v>0.01565835932171035</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02356389476903414</v>
+        <v>0.02308905151123523</v>
       </c>
       <c r="T47" t="n">
-        <v>0.1171752595214532</v>
+        <v>0.1186555869560494</v>
       </c>
       <c r="U47" t="n">
-        <v>0.03897267960787861</v>
+        <v>0.03866223272704897</v>
       </c>
       <c r="V47" t="n">
-        <v>0.04023023771766213</v>
+        <v>0.03963500892286444</v>
       </c>
       <c r="W47" t="n">
-        <v>0.02822344413171739</v>
+        <v>0.02865151977507392</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04477521127716996</v>
+        <v>0.04388326360448622</v>
       </c>
     </row>
     <row r="48">
@@ -4266,46 +4266,46 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1259930651411941</v>
+        <v>0.109062118721277</v>
       </c>
       <c r="L48" t="n">
-        <v>0.485299667266846</v>
+        <v>0.4844389589843668</v>
       </c>
       <c r="M48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.575232101365941</v>
       </c>
       <c r="N48" t="n">
-        <v>4.397004267636007</v>
+        <v>4.355927683725671</v>
       </c>
       <c r="O48" t="n">
-        <v>0.03849209602726868</v>
+        <v>0.03702363992438523</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05801367686716061</v>
+        <v>0.05708986194302317</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.06179347096437893</v>
+        <v>0.06292346146347325</v>
       </c>
       <c r="R48" t="n">
-        <v>0.04819295857020065</v>
+        <v>0.0488321549946007</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2591775641376277</v>
+        <v>0.2381958633347792</v>
       </c>
       <c r="T48" t="n">
-        <v>0.1061013368598037</v>
+        <v>0.09799957050706212</v>
       </c>
       <c r="U48" t="n">
-        <v>0.126796352163413</v>
+        <v>0.12193229432994</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1331784673732208</v>
+        <v>0.1366994689081784</v>
       </c>
       <c r="W48" t="n">
-        <v>0.07567945656572742</v>
+        <v>0.08238586919110011</v>
       </c>
       <c r="X48" t="n">
-        <v>6.048991441267286</v>
+        <v>4.820433676246771</v>
       </c>
     </row>
     <row r="49">
@@ -4346,46 +4346,46 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3561331923175847</v>
+        <v>0.3590159275296238</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4683694590085564</v>
+        <v>0.4634981432331424</v>
       </c>
       <c r="M49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.039760162263589</v>
       </c>
       <c r="N49" t="n">
-        <v>4.422947014558481</v>
+        <v>4.38977869431469</v>
       </c>
       <c r="O49" t="n">
-        <v>0.02051392770980912</v>
+        <v>0.02022015296150826</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01244037538902378</v>
+        <v>0.0123503391792448</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01909904444503831</v>
+        <v>0.01866388306532232</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01819813592465933</v>
+        <v>0.01797189746831082</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09145951210694191</v>
+        <v>0.09076720941899231</v>
       </c>
       <c r="T49" t="n">
-        <v>0.0408895107158156</v>
+        <v>0.03989579727055428</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01709935201296975</v>
+        <v>0.01623377780370026</v>
       </c>
       <c r="V49" t="n">
-        <v>0.04165229337931408</v>
+        <v>0.0408414218222997</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02591296835674918</v>
+        <v>0.02775559265081241</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3106003945251282</v>
+        <v>0.3089221897184552</v>
       </c>
     </row>
     <row r="50">
@@ -4426,46 +4426,46 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5222632463286973</v>
+        <v>0.509975097271933</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5590661062166338</v>
+        <v>0.5510567329931866</v>
       </c>
       <c r="M50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.291212719785222</v>
       </c>
       <c r="N50" t="n">
-        <v>4.625685376448823</v>
+        <v>4.504047402474733</v>
       </c>
       <c r="O50" t="n">
-        <v>0.06494571133610226</v>
+        <v>0.06811326347880989</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06571963174937313</v>
+        <v>0.06354042613351439</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06409656341644362</v>
+        <v>0.06035715160801244</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03533953384795739</v>
+        <v>0.0330140599867615</v>
       </c>
       <c r="S50" t="n">
-        <v>0.03404231595603391</v>
+        <v>0.005333021605786354</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1682993297123482</v>
+        <v>0.22100307175416</v>
       </c>
       <c r="U50" t="n">
-        <v>0.1148140728981687</v>
+        <v>0.2020218657455441</v>
       </c>
       <c r="V50" t="n">
-        <v>0.1267122440542407</v>
+        <v>0.1298128226676996</v>
       </c>
       <c r="W50" t="n">
-        <v>0.05065324229619264</v>
+        <v>0.05767550358487186</v>
       </c>
       <c r="X50" t="n">
-        <v>0.2066094856930322</v>
+        <v>9.876632758716937</v>
       </c>
     </row>
     <row r="51">
@@ -4506,46 +4506,46 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5242408860059533</v>
+        <v>0.4767246818589526</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5520937947918677</v>
+        <v>0.5522639707573709</v>
       </c>
       <c r="M51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.852084868275818</v>
       </c>
       <c r="N51" t="n">
-        <v>4.428116143506686</v>
+        <v>4.429624212899792</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05632063883410715</v>
+        <v>0.05491846238935823</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0431757046714913</v>
+        <v>0.04117347659418068</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1315559015857763</v>
+        <v>0.1264695062825598</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06556497068539888</v>
+        <v>0.06297349632791406</v>
       </c>
       <c r="S51" t="n">
-        <v>0.193357820161781</v>
+        <v>0.2140358340015852</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1401854277155617</v>
+        <v>0.1333764015336087</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08891516932067864</v>
+        <v>0.08217932098259809</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2445162967567384</v>
+        <v>0.2325102286839425</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1103875131792209</v>
+        <v>0.1170833451957221</v>
       </c>
       <c r="X51" t="n">
-        <v>1.768375748591209</v>
+        <v>2.349713694515988</v>
       </c>
     </row>
     <row r="52">
@@ -4586,46 +4586,46 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1593376026831239</v>
+        <v>0.157761930875372</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2352890051057638</v>
+        <v>0.2333175373332652</v>
       </c>
       <c r="M52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.292754697312241</v>
       </c>
       <c r="N52" t="n">
-        <v>4.404173449091401</v>
+        <v>4.284848173608673</v>
       </c>
       <c r="O52" t="n">
-        <v>0.02224892950906648</v>
+        <v>0.02168766463117145</v>
       </c>
       <c r="P52" t="n">
-        <v>0.009667064998431653</v>
+        <v>0.009439895818457951</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.00799525825404733</v>
+        <v>0.008160915449791941</v>
       </c>
       <c r="R52" t="n">
-        <v>0.004685336761364851</v>
+        <v>0.004617006876690318</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01402713073531775</v>
+        <v>0.01393490247454197</v>
       </c>
       <c r="T52" t="n">
-        <v>0.05538758969379882</v>
+        <v>0.0540949132481233</v>
       </c>
       <c r="U52" t="n">
-        <v>0.02243014661965691</v>
+        <v>0.02182633007498416</v>
       </c>
       <c r="V52" t="n">
-        <v>0.01553015668237876</v>
+        <v>0.01592965560247066</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01200401515622942</v>
+        <v>0.01230258960988904</v>
       </c>
       <c r="X52" t="n">
-        <v>0.03986259633704829</v>
+        <v>0.03957910897396508</v>
       </c>
     </row>
     <row r="53">
@@ -4666,46 +4666,46 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.331297244801841</v>
+        <v>0.3306984100273074</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2179880940937189</v>
+        <v>0.2217652418478735</v>
       </c>
       <c r="M53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.388506524434447</v>
       </c>
       <c r="N53" t="n">
-        <v>4.340960299874791</v>
+        <v>4.433878034578161</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0374464131885511</v>
+        <v>0.03773171920031353</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02195848157331865</v>
+        <v>0.02216863315702666</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.009361339853536625</v>
+        <v>0.009369705110336168</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02178044983801221</v>
+        <v>0.02188702540227282</v>
       </c>
       <c r="S53" t="n">
-        <v>0.06742052162729134</v>
+        <v>0.06792457934647343</v>
       </c>
       <c r="T53" t="n">
-        <v>0.07834383830826983</v>
+        <v>0.07936928765021489</v>
       </c>
       <c r="U53" t="n">
-        <v>0.03725657159172706</v>
+        <v>0.03713849859144589</v>
       </c>
       <c r="V53" t="n">
-        <v>0.01629632537399234</v>
+        <v>0.01637342217525893</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03580575689760367</v>
+        <v>0.03699585122714485</v>
       </c>
       <c r="X53" t="n">
-        <v>0.08243456975037336</v>
+        <v>0.08374183778681031</v>
       </c>
     </row>
     <row r="54">
@@ -4746,46 +4746,46 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1883802962457301</v>
+        <v>0.1828418750194339</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4443800114724896</v>
+        <v>0.4229697815204041</v>
       </c>
       <c r="M54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.170489229158358</v>
       </c>
       <c r="N54" t="n">
-        <v>4.4838623906633</v>
+        <v>4.302732049517491</v>
       </c>
       <c r="O54" t="n">
-        <v>0.03397306153979253</v>
+        <v>0.03358846723253005</v>
       </c>
       <c r="P54" t="n">
-        <v>0.01015872580417466</v>
+        <v>0.009638921623333227</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02236488028076683</v>
+        <v>0.02189058373597026</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009962992889557095</v>
+        <v>0.009430019134853678</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02419622586250354</v>
+        <v>0.02324799663501636</v>
       </c>
       <c r="T54" t="n">
-        <v>0.08616690626955989</v>
+        <v>0.08552121911377887</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01803890256890172</v>
+        <v>0.017348400633967</v>
       </c>
       <c r="V54" t="n">
-        <v>0.05150432480899669</v>
+        <v>0.05045713042730044</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01834526882265374</v>
+        <v>0.01845493174218227</v>
       </c>
       <c r="X54" t="n">
-        <v>0.04526148187115488</v>
+        <v>0.04322265176301757</v>
       </c>
     </row>
     <row r="55">
@@ -4826,46 +4826,46 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1380087468264854</v>
+        <v>0.1383001117129509</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4718616957757393</v>
+        <v>0.4716690640923025</v>
       </c>
       <c r="M55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.460797912271313</v>
       </c>
       <c r="N55" t="n">
-        <v>4.385965365084856</v>
+        <v>4.389482784479831</v>
       </c>
       <c r="O55" t="n">
-        <v>0.02110691454628917</v>
+        <v>0.0205724019394174</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01094506378449695</v>
+        <v>0.01095636546003868</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.03306269089659647</v>
+        <v>0.03320931655410412</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01496729834540956</v>
+        <v>0.01511075803479242</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0158218047785395</v>
+        <v>0.01581976770629591</v>
       </c>
       <c r="T55" t="n">
-        <v>0.04715942808956435</v>
+        <v>0.04489493529264424</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01667433005874695</v>
+        <v>0.0166997677668316</v>
       </c>
       <c r="V55" t="n">
-        <v>0.07649124476720059</v>
+        <v>0.07671637573783197</v>
       </c>
       <c r="W55" t="n">
-        <v>0.01822833841839966</v>
+        <v>0.02000742623868202</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02415719907824873</v>
+        <v>0.02408317706382548</v>
       </c>
     </row>
     <row r="56">
@@ -4906,46 +4906,46 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2182594007781727</v>
+        <v>0.2039298221414741</v>
       </c>
       <c r="L56" t="n">
-        <v>0.335772249405254</v>
+        <v>0.3225291753110692</v>
       </c>
       <c r="M56" t="n">
-        <v>4.242619804626787</v>
+        <v>3.981252851815453</v>
       </c>
       <c r="N56" t="n">
-        <v>4.373072936465222</v>
+        <v>4.30712946662735</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02586185705806934</v>
+        <v>0.02623284382628321</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01246669166256177</v>
+        <v>0.01234599096944209</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01411160180948241</v>
+        <v>0.01361231652188452</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01325857278878855</v>
+        <v>0.01291216428751192</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04223121451259179</v>
+        <v>0.04266136529566093</v>
       </c>
       <c r="T56" t="n">
-        <v>0.0622446110108773</v>
+        <v>0.06351380760775961</v>
       </c>
       <c r="U56" t="n">
-        <v>0.02361311243020377</v>
+        <v>0.02360128902844759</v>
       </c>
       <c r="V56" t="n">
-        <v>0.03094693713938051</v>
+        <v>0.02963555531010365</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02293114079228329</v>
+        <v>0.02318867627299311</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1062114068490472</v>
+        <v>0.107608343986451</v>
       </c>
     </row>
     <row r="57">
@@ -4986,46 +4986,46 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3849234920957109</v>
+        <v>0.3806411666965068</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4517484216263014</v>
+        <v>0.447059970211117</v>
       </c>
       <c r="M57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.256768970266466</v>
       </c>
       <c r="N57" t="n">
-        <v>4.401479501613105</v>
+        <v>4.367587060948538</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02688725527344568</v>
+        <v>0.02703240398254442</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01032608689513506</v>
+        <v>0.01018010379005899</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01561030960306645</v>
+        <v>0.01544971659160706</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01369212451488133</v>
+        <v>0.01359616928404648</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02102182202739515</v>
+        <v>0.02077661567532103</v>
       </c>
       <c r="T57" t="n">
-        <v>0.05668893633053084</v>
+        <v>0.05679796409358333</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01741243173506563</v>
+        <v>0.01694821873466503</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03233303755647623</v>
+        <v>0.03208324969321535</v>
       </c>
       <c r="W57" t="n">
-        <v>0.0188002631123453</v>
+        <v>0.0200225501218064</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03322877556870644</v>
+        <v>0.03237617380169238</v>
       </c>
     </row>
     <row r="58">
@@ -5066,46 +5066,46 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1253615278418694</v>
+        <v>0.1189716300414537</v>
       </c>
       <c r="L58" t="n">
-        <v>0.511488805746165</v>
+        <v>0.4915421821440906</v>
       </c>
       <c r="M58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.137219511845506</v>
       </c>
       <c r="N58" t="n">
-        <v>4.754692767525441</v>
+        <v>4.400276476589231</v>
       </c>
       <c r="O58" t="n">
-        <v>0.05774104410455218</v>
+        <v>0.05722467700841838</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01159131571226783</v>
+        <v>0.01079322825767584</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.04432589518790003</v>
+        <v>0.0437047189441041</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008798069425087434</v>
+        <v>0.008149810648187716</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0446046992844243</v>
+        <v>0.04296410878307049</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1594243830452662</v>
+        <v>0.1604036129243858</v>
       </c>
       <c r="U58" t="n">
-        <v>0.02271625938779629</v>
+        <v>0.02096398775065494</v>
       </c>
       <c r="V58" t="n">
-        <v>0.1190059934827339</v>
+        <v>0.1170791467931494</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01907756427705438</v>
+        <v>0.01856088510491745</v>
       </c>
       <c r="X58" t="n">
-        <v>0.09751105742308666</v>
+        <v>0.09423267571717542</v>
       </c>
     </row>
     <row r="59">
@@ -5146,46 +5146,46 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4698313368793378</v>
+        <v>0.4654669130886756</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5162817403547273</v>
+        <v>0.5137334953270173</v>
       </c>
       <c r="M59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.192052202289072</v>
       </c>
       <c r="N59" t="n">
-        <v>4.39957804001801</v>
+        <v>4.384757005062604</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01118696558201471</v>
+        <v>0.01158213208727017</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004581230194354647</v>
+        <v>0.004501156376277752</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.008079896453050701</v>
+        <v>0.007971296892426216</v>
       </c>
       <c r="R59" t="n">
-        <v>0.006009917882977104</v>
+        <v>0.005960208500311382</v>
       </c>
       <c r="S59" t="n">
-        <v>0.006956029151752857</v>
+        <v>0.006862390422074775</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01915524544533431</v>
+        <v>0.0200455496222555</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005891030265633271</v>
+        <v>0.005691467311731722</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01219603723797654</v>
+        <v>0.01207448781874912</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005343879753612162</v>
+        <v>0.005801047073611358</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006781306315951782</v>
+        <v>0.006502913782881363</v>
       </c>
     </row>
     <row r="60">
@@ -5226,46 +5226,46 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3312705578089989</v>
+        <v>0.3195516907355711</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2455762625893165</v>
+        <v>0.2335821217569123</v>
       </c>
       <c r="M60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.041987989944264</v>
       </c>
       <c r="N60" t="n">
-        <v>4.306351167905562</v>
+        <v>4.211515428719657</v>
       </c>
       <c r="O60" t="n">
-        <v>0.00492553596872854</v>
+        <v>0.005119763135164285</v>
       </c>
       <c r="P60" t="n">
-        <v>0.003689268625005232</v>
+        <v>0.003631889696482466</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0009629682350097316</v>
+        <v>0.0009316206345992318</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001761045575533179</v>
+        <v>0.001681791884465103</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004827514084758701</v>
+        <v>0.004747628436562954</v>
       </c>
       <c r="T60" t="n">
-        <v>0.008421109668185336</v>
+        <v>0.008819318087748711</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005566192801693178</v>
+        <v>0.005534195711211343</v>
       </c>
       <c r="V60" t="n">
-        <v>0.001972125725562643</v>
+        <v>0.00194546240985284</v>
       </c>
       <c r="W60" t="n">
-        <v>0.002290107320457687</v>
+        <v>0.002317269556391085</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005541876933846708</v>
+        <v>0.005434801888720871</v>
       </c>
     </row>
     <row r="61">
@@ -5306,46 +5306,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2919016638915633</v>
+        <v>0.2918937862084307</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2569314482666408</v>
+        <v>0.2598346955432927</v>
       </c>
       <c r="M61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.826202503798687</v>
       </c>
       <c r="N61" t="n">
-        <v>4.187227762110225</v>
+        <v>4.253951092716853</v>
       </c>
       <c r="O61" t="n">
-        <v>0.008734953988697527</v>
+        <v>0.008825463309659293</v>
       </c>
       <c r="P61" t="n">
-        <v>0.007196609493708757</v>
+        <v>0.007261296395201843</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.002199347279108958</v>
+        <v>0.002201324515139227</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0102766535176533</v>
+        <v>0.01028467626798965</v>
       </c>
       <c r="S61" t="n">
-        <v>0.04404532999832503</v>
+        <v>0.04376229981575793</v>
       </c>
       <c r="T61" t="n">
-        <v>0.01530243872410191</v>
+        <v>0.01547200449610845</v>
       </c>
       <c r="U61" t="n">
-        <v>0.009476116942733639</v>
+        <v>0.009442641561690116</v>
       </c>
       <c r="V61" t="n">
-        <v>0.003544830946180966</v>
+        <v>0.003573337299191144</v>
       </c>
       <c r="W61" t="n">
-        <v>0.0095050551310578</v>
+        <v>0.010025634095602</v>
       </c>
       <c r="X61" t="n">
-        <v>0.3235235415550104</v>
+        <v>0.3199145130268217</v>
       </c>
     </row>
     <row r="62">
@@ -5386,46 +5386,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1508447051269653</v>
+        <v>0.1532581908813461</v>
       </c>
       <c r="L62" t="n">
-        <v>0.203299262562559</v>
+        <v>0.2066590868543457</v>
       </c>
       <c r="M62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.148400063035928</v>
       </c>
       <c r="N62" t="n">
-        <v>4.118872738556036</v>
+        <v>4.187562429165657</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01047892935603037</v>
+        <v>0.01050328050872985</v>
       </c>
       <c r="P62" t="n">
-        <v>0.005062161906466559</v>
+        <v>0.005163760427144291</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.002410213410068313</v>
+        <v>0.002415315030795406</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0135712281525675</v>
+        <v>0.01367947175723625</v>
       </c>
       <c r="S62" t="n">
-        <v>0.009650626272606461</v>
+        <v>0.009725001310454302</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02178031601625947</v>
+        <v>0.02175630933606802</v>
       </c>
       <c r="U62" t="n">
-        <v>0.01022624705763519</v>
+        <v>0.01013436189743866</v>
       </c>
       <c r="V62" t="n">
-        <v>0.003937805191127263</v>
+        <v>0.003957717964676706</v>
       </c>
       <c r="W62" t="n">
-        <v>0.0219884578124682</v>
+        <v>0.02210316017126304</v>
       </c>
       <c r="X62" t="n">
-        <v>0.02024768999752945</v>
+        <v>0.02036538870565461</v>
       </c>
     </row>
     <row r="63">
@@ -5466,46 +5466,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.269759348861875</v>
+        <v>0.2693602879820832</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2766104142455272</v>
+        <v>0.2801106513094213</v>
       </c>
       <c r="M63" t="n">
-        <v>4.076109010387499</v>
+        <v>3.977065693514069</v>
       </c>
       <c r="N63" t="n">
-        <v>4.19468330758944</v>
+        <v>4.246272872864611</v>
       </c>
       <c r="O63" t="n">
-        <v>0.007499763913287207</v>
+        <v>0.007524742774784452</v>
       </c>
       <c r="P63" t="n">
-        <v>0.006224351018692191</v>
+        <v>0.00623310251064766</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.002062524994854691</v>
+        <v>0.002065892440008845</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007997649377393352</v>
+        <v>0.007996123534263346</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01734770468844371</v>
+        <v>0.01738561124787679</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01319788142145704</v>
+        <v>0.01312228694373818</v>
       </c>
       <c r="U63" t="n">
-        <v>0.00872340980473668</v>
+        <v>0.008243090017401679</v>
       </c>
       <c r="V63" t="n">
-        <v>0.003348001469427609</v>
+        <v>0.003354211858710682</v>
       </c>
       <c r="W63" t="n">
-        <v>0.01110235242024961</v>
+        <v>0.01026329451454335</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03441272875200599</v>
+        <v>0.03580042266501465</v>
       </c>
     </row>
     <row r="64">
@@ -5546,46 +5546,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1942409677162144</v>
+        <v>0.2066785242826841</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2597197420140236</v>
+        <v>0.2655672477878417</v>
       </c>
       <c r="M64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.70690274747437</v>
       </c>
       <c r="N64" t="n">
-        <v>4.151838810960196</v>
+        <v>4.236555191142369</v>
       </c>
       <c r="O64" t="n">
-        <v>0.009664785202513447</v>
+        <v>0.009760760903214465</v>
       </c>
       <c r="P64" t="n">
-        <v>0.006283146394786142</v>
+        <v>0.00643235252875748</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.003192621976767015</v>
+        <v>0.003222573081497184</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0168402227707129</v>
+        <v>0.01713548534950339</v>
       </c>
       <c r="S64" t="n">
-        <v>0.07492735584014489</v>
+        <v>0.05811891173340788</v>
       </c>
       <c r="T64" t="n">
-        <v>0.01913538688166936</v>
+        <v>0.01915344547984018</v>
       </c>
       <c r="U64" t="n">
-        <v>0.009172854624481461</v>
+        <v>0.009283543946023829</v>
       </c>
       <c r="V64" t="n">
-        <v>0.005057789647864758</v>
+        <v>0.005105963832783464</v>
       </c>
       <c r="W64" t="n">
-        <v>0.02383806096283198</v>
+        <v>0.02472468306879162</v>
       </c>
       <c r="X64" t="n">
-        <v>2.204900547087687</v>
+        <v>1.151000526307225</v>
       </c>
     </row>
     <row r="65">
@@ -5626,46 +5626,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2848721463559863</v>
+        <v>0.2856673816535896</v>
       </c>
       <c r="L65" t="n">
-        <v>0.336035758270328</v>
+        <v>0.3407398181334132</v>
       </c>
       <c r="M65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.911375026612862</v>
       </c>
       <c r="N65" t="n">
-        <v>4.213454858177437</v>
+        <v>4.268358977938123</v>
       </c>
       <c r="O65" t="n">
-        <v>0.008229088470310529</v>
+        <v>0.008282046321541905</v>
       </c>
       <c r="P65" t="n">
-        <v>0.007639919591292572</v>
+        <v>0.007711272640738872</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.003858850413283327</v>
+        <v>0.003871316101479553</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01018710613815288</v>
+        <v>0.0102545450169213</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03222623138296898</v>
+        <v>0.03226326562997626</v>
       </c>
       <c r="T65" t="n">
-        <v>0.01386067686689359</v>
+        <v>0.01390244162706635</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01008850790798658</v>
+        <v>0.01023459178253347</v>
       </c>
       <c r="V65" t="n">
-        <v>0.006097821109955399</v>
+        <v>0.006170399118336068</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01173830501182497</v>
+        <v>0.01254462835527181</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1325845659537502</v>
+        <v>0.1324165213036682</v>
       </c>
     </row>
     <row r="66">
@@ -5706,46 +5706,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2502564140929328</v>
+        <v>0.252410987791241</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2709820904190222</v>
+        <v>0.2768480174094493</v>
       </c>
       <c r="M66" t="n">
-        <v>4.099154174190237</v>
+        <v>3.951261926227352</v>
       </c>
       <c r="N66" t="n">
-        <v>4.153421109969911</v>
+        <v>4.239687518074408</v>
       </c>
       <c r="O66" t="n">
-        <v>0.009235331052253052</v>
+        <v>0.009307159429461826</v>
       </c>
       <c r="P66" t="n">
-        <v>0.006872091418572358</v>
+        <v>0.007026690262257136</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.003277502766215464</v>
+        <v>0.003300995512780985</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0153170058785795</v>
+        <v>0.01553748687722207</v>
       </c>
       <c r="S66" t="n">
-        <v>0.02993068978996192</v>
+        <v>0.03002311711928095</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01772471444644889</v>
+        <v>0.01773217631235429</v>
       </c>
       <c r="U66" t="n">
-        <v>0.009569713172765682</v>
+        <v>0.009608652580356303</v>
       </c>
       <c r="V66" t="n">
-        <v>0.005161778926643436</v>
+        <v>0.005223290950400216</v>
       </c>
       <c r="W66" t="n">
-        <v>0.01950267460624764</v>
+        <v>0.02034173901394747</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1605091500818053</v>
+        <v>0.1607002691872437</v>
       </c>
     </row>
     <row r="67">
@@ -5786,46 +5786,46 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4199481606275527</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3864876609417378</v>
+        <v>0.3946079364087451</v>
       </c>
       <c r="M67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.396330197414215</v>
       </c>
       <c r="N67" t="n">
-        <v>4.256193383531747</v>
+        <v>4.346590404488876</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005578412771237122</v>
+        <v>0.005686700075282018</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01401339088566428</v>
+        <v>0.01442873312203694</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.004068425124450636</v>
+        <v>0.004110210004764778</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009205170347857656</v>
+        <v>0.009170193196447662</v>
       </c>
       <c r="S67" t="n">
-        <v>0.04923400404541596</v>
+        <v>0.05182828079878329</v>
       </c>
       <c r="T67" t="n">
-        <v>0.007866572970956484</v>
+        <v>0.008212848023578015</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01305969224908627</v>
+        <v>0.01324118018161912</v>
       </c>
       <c r="V67" t="n">
-        <v>0.009168018791690191</v>
+        <v>0.009267349298949569</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01253829129624317</v>
+        <v>0.01302232762513014</v>
       </c>
       <c r="X67" t="n">
-        <v>0.07467932060475028</v>
+        <v>0.07949518583970677</v>
       </c>
     </row>
     <row r="68">
@@ -5866,46 +5866,46 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4285023488478826</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3723368859856501</v>
+        <v>0.388790083391</v>
       </c>
       <c r="M68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.480408325582514</v>
       </c>
       <c r="N68" t="n">
-        <v>4.186476675654941</v>
+        <v>4.345648594021345</v>
       </c>
       <c r="O68" t="n">
-        <v>0.00606018367327063</v>
+        <v>0.006211707985160668</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01621645700001562</v>
+        <v>0.01721004510934526</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.004462630051927047</v>
+        <v>0.004624498510364156</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01378151042978103</v>
+        <v>0.01376600744844261</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01383079897871538</v>
+        <v>0.01573548912561343</v>
       </c>
       <c r="T68" t="n">
-        <v>0.01086886976351628</v>
+        <v>0.01127896137210743</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01555668049300938</v>
+        <v>0.01600387510660763</v>
       </c>
       <c r="V68" t="n">
-        <v>0.007956343296437362</v>
+        <v>0.008227188002768738</v>
       </c>
       <c r="W68" t="n">
-        <v>0.01946146101517696</v>
+        <v>0.01952518742244272</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02308446218695407</v>
+        <v>0.02549845019953893</v>
       </c>
     </row>
     <row r="69">
@@ -5946,46 +5946,46 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1547738540766385</v>
+        <v>0.1574541057329026</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2025567887315575</v>
+        <v>0.2052525266463846</v>
       </c>
       <c r="M69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.332138796392004</v>
       </c>
       <c r="N69" t="n">
-        <v>4.256896200133737</v>
+        <v>4.301259047737942</v>
       </c>
       <c r="O69" t="n">
-        <v>0.008704420674643526</v>
+        <v>0.008697335882864268</v>
       </c>
       <c r="P69" t="n">
-        <v>0.00533774353401272</v>
+        <v>0.005397398916447352</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.003671604256486734</v>
+        <v>0.003684531310681907</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004238267649207492</v>
+        <v>0.004267353123611629</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004145433685938331</v>
+        <v>0.004153910651498359</v>
       </c>
       <c r="T69" t="n">
-        <v>0.01855741757909253</v>
+        <v>0.01844820755406056</v>
       </c>
       <c r="U69" t="n">
-        <v>0.009661215313763015</v>
+        <v>0.009630476247740338</v>
       </c>
       <c r="V69" t="n">
-        <v>0.00578508568741367</v>
+        <v>0.005812052722773665</v>
       </c>
       <c r="W69" t="n">
-        <v>0.005813650849479726</v>
+        <v>0.005999333156887494</v>
       </c>
       <c r="X69" t="n">
-        <v>0.006136465536548035</v>
+        <v>0.006095744047079951</v>
       </c>
     </row>
     <row r="70">
@@ -6026,46 +6026,46 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.153202753067615</v>
+        <v>0.1548184556465437</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2831686061594044</v>
+        <v>0.2821165444330669</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.393884558299479</v>
       </c>
       <c r="N70" t="n">
-        <v>4.368615252654925</v>
+        <v>4.356902676963256</v>
       </c>
       <c r="O70" t="n">
-        <v>0.007056060091638477</v>
+        <v>0.007041754705486096</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009931718247072259</v>
+        <v>0.009916987065314005</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.005605805205319904</v>
+        <v>0.005609818782489916</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004617287574017523</v>
+        <v>0.004620176931972432</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006479123150455466</v>
+        <v>0.006475976953657859</v>
       </c>
       <c r="T70" t="n">
-        <v>0.01349036203956334</v>
+        <v>0.01338069637391916</v>
       </c>
       <c r="U70" t="n">
-        <v>0.0139132387395667</v>
+        <v>0.01381308858031555</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009062928444698887</v>
+        <v>0.009080225123130677</v>
       </c>
       <c r="W70" t="n">
-        <v>0.006516396687317963</v>
+        <v>0.006717288047944464</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009838510190614026</v>
+        <v>0.009743408757198643</v>
       </c>
     </row>
     <row r="71">
@@ -6106,46 +6106,46 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3261006684563419</v>
+        <v>0.3259372932035616</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3501773912679607</v>
+        <v>0.3495122827845789</v>
       </c>
       <c r="M71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.435983776929537</v>
       </c>
       <c r="N71" t="n">
-        <v>4.457096554123856</v>
+        <v>4.438765799706143</v>
       </c>
       <c r="O71" t="n">
-        <v>0.008578652237724801</v>
+        <v>0.008538237815690698</v>
       </c>
       <c r="P71" t="n">
-        <v>0.009273427160697255</v>
+        <v>0.009237006911603483</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.004649105559270682</v>
+        <v>0.004661901364167855</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005162364825481265</v>
+        <v>0.005153535629014602</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005569732492794713</v>
+        <v>0.005562343198507328</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01405266995023319</v>
+        <v>0.01387597490106091</v>
       </c>
       <c r="U71" t="n">
-        <v>0.009990127057438172</v>
+        <v>0.009902587743156315</v>
       </c>
       <c r="V71" t="n">
-        <v>0.007418842385959243</v>
+        <v>0.007437539250542451</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006481379110390297</v>
+        <v>0.006776745720272799</v>
       </c>
       <c r="X71" t="n">
-        <v>0.007061751729021942</v>
+        <v>0.006932320374759091</v>
       </c>
     </row>
     <row r="72">
@@ -6186,46 +6186,46 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3263018165925168</v>
+        <v>0.3247916833722452</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4179990537206515</v>
+        <v>0.4127186230893385</v>
       </c>
       <c r="M72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.528094939538367</v>
       </c>
       <c r="N72" t="n">
-        <v>4.560550370595196</v>
+        <v>4.500728602013576</v>
       </c>
       <c r="O72" t="n">
-        <v>0.006211939227981747</v>
+        <v>0.006160620005598041</v>
       </c>
       <c r="P72" t="n">
-        <v>0.007158758713644402</v>
+        <v>0.007061793149966656</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.005623343401014035</v>
+        <v>0.005623081508063347</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004440614455302098</v>
+        <v>0.004398654641003785</v>
       </c>
       <c r="S72" t="n">
-        <v>0.00610379650971178</v>
+        <v>0.006047072051250384</v>
       </c>
       <c r="T72" t="n">
-        <v>0.009157679324637588</v>
+        <v>0.008992879365170294</v>
       </c>
       <c r="U72" t="n">
-        <v>0.008113608087834122</v>
+        <v>0.008021590002114092</v>
       </c>
       <c r="V72" t="n">
-        <v>0.009048725960474853</v>
+        <v>0.009016568120366681</v>
       </c>
       <c r="W72" t="n">
-        <v>0.00591606209113582</v>
+        <v>0.006169601223022439</v>
       </c>
       <c r="X72" t="n">
-        <v>0.007960345442374712</v>
+        <v>0.007714964968362422</v>
       </c>
     </row>
     <row r="73">
@@ -6266,46 +6266,46 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.07823057899988078</v>
+        <v>0.08004889403840529</v>
       </c>
       <c r="L73" t="n">
-        <v>0.0789735688145573</v>
+        <v>0.08113991389542105</v>
       </c>
       <c r="M73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.341167164957967</v>
       </c>
       <c r="N73" t="n">
-        <v>4.219498679683764</v>
+        <v>4.328594414246572</v>
       </c>
       <c r="O73" t="n">
-        <v>0.01321303913880696</v>
+        <v>0.01323244292225256</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01242899536321497</v>
+        <v>0.01256801918834716</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.001840800754663579</v>
+        <v>0.001841608910406477</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002532754873270239</v>
+        <v>0.002548885856111626</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003700460753241341</v>
+        <v>0.0003786034117191857</v>
       </c>
       <c r="T73" t="n">
-        <v>0.03778822380197871</v>
+        <v>0.03777100137267746</v>
       </c>
       <c r="U73" t="n">
-        <v>0.02528122966327237</v>
+        <v>0.0252108259623172</v>
       </c>
       <c r="V73" t="n">
-        <v>0.003449967252861038</v>
+        <v>0.003453255620810314</v>
       </c>
       <c r="W73" t="n">
-        <v>0.00410424297434909</v>
+        <v>0.004161393983429871</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003232276301438997</v>
+        <v>0.003226953352581988</v>
       </c>
     </row>
     <row r="74">
@@ -6346,46 +6346,46 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08513405677699858</v>
+        <v>0.08447253359755409</v>
       </c>
       <c r="L74" t="n">
-        <v>0.165585505902094</v>
+        <v>0.1625880726057796</v>
       </c>
       <c r="M74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.398896242437559</v>
       </c>
       <c r="N74" t="n">
-        <v>4.456859542157701</v>
+        <v>4.385985339944041</v>
       </c>
       <c r="O74" t="n">
-        <v>0.006320476783071688</v>
+        <v>0.006292812977601652</v>
       </c>
       <c r="P74" t="n">
-        <v>0.008705941455379262</v>
+        <v>0.008619410209494893</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003382137731122961</v>
+        <v>0.003381667276977047</v>
       </c>
       <c r="R74" t="n">
-        <v>0.00212229168522629</v>
+        <v>0.002113418783171738</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003738285578494648</v>
+        <v>0.003726249521864578</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01635404000125613</v>
+        <v>0.01629589020276353</v>
       </c>
       <c r="U74" t="n">
-        <v>0.01452324549968646</v>
+        <v>0.0145034888740591</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005353095585928044</v>
+        <v>0.005347454516546753</v>
       </c>
       <c r="W74" t="n">
-        <v>0.00362935504874988</v>
+        <v>0.003684016781749129</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005672621254416173</v>
+        <v>0.005623921283970385</v>
       </c>
     </row>
     <row r="75">
@@ -6426,46 +6426,46 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.210319821056764</v>
+        <v>0.2074205046880389</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2634862878119731</v>
+        <v>0.2623727640782005</v>
       </c>
       <c r="M75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.197065933067138</v>
       </c>
       <c r="N75" t="n">
-        <v>4.299117739584633</v>
+        <v>4.282963131348233</v>
       </c>
       <c r="O75" t="n">
-        <v>0.006253905287160431</v>
+        <v>0.006245120541096643</v>
       </c>
       <c r="P75" t="n">
-        <v>0.009700745758114896</v>
+        <v>0.009670164516327455</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.00402745098591299</v>
+        <v>0.004021698121183217</v>
       </c>
       <c r="R75" t="n">
-        <v>0.004775442572911684</v>
+        <v>0.004762930561152022</v>
       </c>
       <c r="S75" t="n">
-        <v>0.007172460417886275</v>
+        <v>0.00717411220561622</v>
       </c>
       <c r="T75" t="n">
-        <v>0.01217889780474768</v>
+        <v>0.01211322190424821</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01273464283818685</v>
+        <v>0.01264484894402839</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006366625708202526</v>
+        <v>0.006370435967034196</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006305046973249727</v>
+        <v>0.006517516058862821</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01094823229768064</v>
+        <v>0.01087003527579221</v>
       </c>
     </row>
     <row r="76">
@@ -6506,46 +6506,46 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.01998426772365844</v>
+        <v>0.02053193225236777</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02451680666624679</v>
+        <v>0.02514679805700491</v>
       </c>
       <c r="M76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.359073588567345</v>
       </c>
       <c r="N76" t="n">
-        <v>4.216644300630954</v>
+        <v>4.318116560981346</v>
       </c>
       <c r="O76" t="n">
-        <v>0.04208906870220217</v>
+        <v>0.04210715459668449</v>
       </c>
       <c r="P76" t="n">
-        <v>0.02718102980456403</v>
+        <v>0.02727963062340896</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002066804073982537</v>
+        <v>0.002067085639341657</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002212799401919402</v>
+        <v>0.002217603147539648</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007928470445238277</v>
+        <v>0.0007945353140518981</v>
       </c>
       <c r="T76" t="n">
-        <v>0.1416469603756101</v>
+        <v>0.1416058625041486</v>
       </c>
       <c r="U76" t="n">
-        <v>0.08370138789630331</v>
+        <v>0.08361900735273005</v>
       </c>
       <c r="V76" t="n">
-        <v>0.003583075240640479</v>
+        <v>0.003583708688033575</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003723097047321722</v>
+        <v>0.003737440631798268</v>
       </c>
       <c r="X76" t="n">
-        <v>0.002701079920039876</v>
+        <v>0.00269881302661401</v>
       </c>
     </row>
     <row r="77">
@@ -6586,46 +6586,46 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03972700182767472</v>
+        <v>0.03782537579660925</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08797326851037784</v>
+        <v>0.08097815804016646</v>
       </c>
       <c r="M77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.268656568147811</v>
       </c>
       <c r="N77" t="n">
-        <v>4.552868385926671</v>
+        <v>4.245138155328809</v>
       </c>
       <c r="O77" t="n">
-        <v>0.0138621777604546</v>
+        <v>0.01381894615408611</v>
       </c>
       <c r="P77" t="n">
-        <v>0.004012595281075292</v>
+        <v>0.003757490358159672</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002039453805508909</v>
+        <v>0.002032619045363282</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003878735945343272</v>
+        <v>0.0003791909046618231</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001784044609380518</v>
+        <v>0.001767978679563574</v>
       </c>
       <c r="T77" t="n">
-        <v>0.03394750559876858</v>
+        <v>0.03403154285305804</v>
       </c>
       <c r="U77" t="n">
-        <v>0.01324537945428596</v>
+        <v>0.01318563316280446</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003065145542866914</v>
+        <v>0.003054291550795958</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002006951597692298</v>
+        <v>0.002024625475944558</v>
       </c>
       <c r="X77" t="n">
-        <v>0.002789968636216411</v>
+        <v>0.00276789467274687</v>
       </c>
     </row>
     <row r="78">
@@ -6666,46 +6666,46 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02841134719532212</v>
+        <v>0.02723295651487582</v>
       </c>
       <c r="L78" t="n">
-        <v>0.08105945091459836</v>
+        <v>0.0766008676009966</v>
       </c>
       <c r="M78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.413573948301897</v>
       </c>
       <c r="N78" t="n">
-        <v>4.641243546122713</v>
+        <v>4.37829161508492</v>
       </c>
       <c r="O78" t="n">
-        <v>0.00640835829183604</v>
+        <v>0.006302566309750019</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000008612e-05</v>
+        <v>1.000000000071305e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.001787363808416304</v>
+        <v>0.001805496917605349</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001560689229830855</v>
+        <v>0.0001674553222235624</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000000021e-05</v>
+        <v>1.000000000000033e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.02172631650019382</v>
+        <v>0.0215391969134919</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01933912530041995</v>
+        <v>0.0189688646835046</v>
       </c>
       <c r="V78" t="n">
-        <v>0.002872591262784501</v>
+        <v>0.002891265875586965</v>
       </c>
       <c r="W78" t="n">
-        <v>0.001683814286156597</v>
+        <v>0.00170555842652797</v>
       </c>
       <c r="X78" t="n">
-        <v>0.002940483283978969</v>
+        <v>0.002934388439255799</v>
       </c>
     </row>
     <row r="79">
@@ -6746,46 +6746,46 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2899193890845111</v>
+        <v>0.2905655997701949</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3127484679037562</v>
+        <v>0.3193251383257389</v>
       </c>
       <c r="M79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.384688376048642</v>
       </c>
       <c r="N79" t="n">
-        <v>4.432630849743337</v>
+        <v>4.414745075458724</v>
       </c>
       <c r="O79" t="n">
-        <v>0.003200336108288485</v>
+        <v>0.003147207099280328</v>
       </c>
       <c r="P79" t="n">
-        <v>0.001838170651927963</v>
+        <v>0.00181777187931982</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001423361437551938</v>
+        <v>0.001444320371422225</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001611478530215939</v>
+        <v>0.001630442173610273</v>
       </c>
       <c r="S79" t="n">
-        <v>0.3641148005769934</v>
+        <v>0.0005977485697859727</v>
       </c>
       <c r="T79" t="n">
-        <v>0.006229841297077021</v>
+        <v>0.00607770090173849</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002213647934412034</v>
+        <v>0.002150034004461958</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002485983116867376</v>
+        <v>0.002565919663114426</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002236609687663651</v>
+        <v>0.002597945957028094</v>
       </c>
       <c r="X79" t="n">
-        <v>320.5612682602643</v>
+        <v>0.154595460590586</v>
       </c>
     </row>
     <row r="80">
@@ -6826,46 +6826,46 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1594873656769697</v>
+        <v>0.1624757209231998</v>
       </c>
       <c r="L80" t="n">
-        <v>0.238115959928494</v>
+        <v>0.2462244769929051</v>
       </c>
       <c r="M80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.522041228329741</v>
       </c>
       <c r="N80" t="n">
-        <v>4.462496180152695</v>
+        <v>4.466768919963216</v>
       </c>
       <c r="O80" t="n">
-        <v>0.004417341773305467</v>
+        <v>0.004352998420737021</v>
       </c>
       <c r="P80" t="n">
-        <v>0.002666602695677826</v>
+        <v>0.002638442960042925</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.001786592018186298</v>
+        <v>0.001807076613868658</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001702696429736139</v>
+        <v>0.001726803461836381</v>
       </c>
       <c r="S80" t="n">
-        <v>0.2046203827375931</v>
+        <v>1.000000001324653e-05</v>
       </c>
       <c r="T80" t="n">
-        <v>0.01076198011061572</v>
+        <v>0.01046157986673176</v>
       </c>
       <c r="U80" t="n">
-        <v>0.003450335661040702</v>
+        <v>0.003125894024472116</v>
       </c>
       <c r="V80" t="n">
-        <v>0.003102177274131927</v>
+        <v>0.003152564688256193</v>
       </c>
       <c r="W80" t="n">
-        <v>0.002576426971020751</v>
+        <v>0.002868581738658547</v>
       </c>
       <c r="X80" t="n">
-        <v>268.4056137047056</v>
+        <v>0.1347039345787046</v>
       </c>
     </row>
     <row r="81">
@@ -6906,46 +6906,46 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2784130221473441</v>
+        <v>0.2764885304045394</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2484194163746214</v>
+        <v>0.2567972681835818</v>
       </c>
       <c r="M81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.543506980364979</v>
       </c>
       <c r="N81" t="n">
-        <v>4.556786804190114</v>
+        <v>4.588717551710889</v>
       </c>
       <c r="O81" t="n">
-        <v>0.00389208121980406</v>
+        <v>0.003861634035074769</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002266540339343636</v>
+        <v>0.002251801281670118</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001114863698995041</v>
+        <v>0.001123941612958597</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001606250068673371</v>
+        <v>0.001628878612580421</v>
       </c>
       <c r="S81" t="n">
-        <v>0.327459844528324</v>
+        <v>1.00000000000048e-05</v>
       </c>
       <c r="T81" t="n">
-        <v>0.008008728666669726</v>
+        <v>0.007830854480611368</v>
       </c>
       <c r="U81" t="n">
-        <v>0.002744251161800315</v>
+        <v>0.003271441487494405</v>
       </c>
       <c r="V81" t="n">
-        <v>0.001951184566076477</v>
+        <v>0.001996657285093528</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002178541180036263</v>
+        <v>0.002502731092812272</v>
       </c>
       <c r="X81" t="n">
-        <v>526.1880807456354</v>
+        <v>0.1141189430623603</v>
       </c>
     </row>
     <row r="82">
@@ -6986,46 +6986,46 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1863539639022372</v>
+        <v>0.1873857992577476</v>
       </c>
       <c r="L82" t="n">
-        <v>0.144646556527771</v>
+        <v>0.1461279938730407</v>
       </c>
       <c r="M82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.465612453484066</v>
       </c>
       <c r="N82" t="n">
-        <v>4.541621095556766</v>
+        <v>4.5948294093929</v>
       </c>
       <c r="O82" t="n">
-        <v>0.006844169069359357</v>
+        <v>0.006871720059069834</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003108256889944278</v>
+        <v>0.003131021004272071</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.0009610547818086904</v>
+        <v>0.0009602008629425483</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001788093158871219</v>
+        <v>0.001784373168837745</v>
       </c>
       <c r="S82" t="n">
-        <v>0.1251245440906446</v>
+        <v>0.2287772810153216</v>
       </c>
       <c r="T82" t="n">
-        <v>0.01765815681808544</v>
+        <v>0.02780797484512675</v>
       </c>
       <c r="U82" t="n">
-        <v>0.006147764116374175</v>
+        <v>0.006942045095459899</v>
       </c>
       <c r="V82" t="n">
-        <v>0.001687043686579425</v>
+        <v>0.001769355116460212</v>
       </c>
       <c r="W82" t="n">
-        <v>0.002578373270279191</v>
+        <v>0.003043758480154077</v>
       </c>
       <c r="X82" t="n">
-        <v>415.2366768333397</v>
+        <v>5438.420271339656</v>
       </c>
     </row>
     <row r="83">
@@ -7064,46 +7064,46 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1872142165502269</v>
+        <v>0.1900383461359677</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1772295411748909</v>
+        <v>0.1855790480569224</v>
       </c>
       <c r="M83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.580927191812872</v>
       </c>
       <c r="N83" t="n">
-        <v>4.49712219963092</v>
+        <v>4.571329756778653</v>
       </c>
       <c r="O83" t="n">
-        <v>0.004161280328394758</v>
+        <v>0.004106819793420861</v>
       </c>
       <c r="P83" t="n">
-        <v>0.001693854309011158</v>
+        <v>0.001704682090402879</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.0009902417253326648</v>
+        <v>0.000998696866006887</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001398776318746772</v>
+        <v>0.00142244321359066</v>
       </c>
       <c r="S83" t="n">
-        <v>0.1989212093388746</v>
+        <v>1.000000000025039e-05</v>
       </c>
       <c r="T83" t="n">
-        <v>0.009847517655859908</v>
+        <v>0.009656310806411373</v>
       </c>
       <c r="U83" t="n">
-        <v>0.004990136929241952</v>
+        <v>0.004878179448193665</v>
       </c>
       <c r="V83" t="n">
-        <v>0.001757984628883797</v>
+        <v>0.001816976652035546</v>
       </c>
       <c r="W83" t="n">
-        <v>0.002070719389004721</v>
+        <v>0.002365581625461602</v>
       </c>
       <c r="X83" t="n">
-        <v>597.0724173175942</v>
+        <v>0.130510815641632</v>
       </c>
     </row>
     <row r="84">
@@ -7142,46 +7142,46 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1659043674747134</v>
+        <v>0.1700871734410854</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2245775996157477</v>
+        <v>0.2305510722140747</v>
       </c>
       <c r="M84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.554043371413063</v>
       </c>
       <c r="N84" t="n">
-        <v>4.427880906394733</v>
+        <v>4.502375865319721</v>
       </c>
       <c r="O84" t="n">
-        <v>0.004589627173142038</v>
+        <v>0.004580612431084036</v>
       </c>
       <c r="P84" t="n">
-        <v>1.00000000000321e-05</v>
+        <v>1.000000000001186e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001698338787854876</v>
+        <v>0.001674498145792546</v>
       </c>
       <c r="R84" t="n">
-        <v>0.001950933873072528</v>
+        <v>0.002005585337766274</v>
       </c>
       <c r="S84" t="n">
-        <v>0.4999999999997146</v>
+        <v>1.000000000000519e-05</v>
       </c>
       <c r="T84" t="n">
-        <v>0.01178387948397145</v>
+        <v>0.0116420548043375</v>
       </c>
       <c r="U84" t="n">
-        <v>0.006297361822815689</v>
+        <v>0.006982834285418339</v>
       </c>
       <c r="V84" t="n">
-        <v>0.002977964451484856</v>
+        <v>0.002968594967667026</v>
       </c>
       <c r="W84" t="n">
-        <v>0.002913602219748724</v>
+        <v>0.003366699868374119</v>
       </c>
       <c r="X84" t="n">
-        <v>469.3872816125058</v>
+        <v>0.1163796120549553</v>
       </c>
     </row>
     <row r="85">
@@ -7220,46 +7220,46 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2307899480131057</v>
+        <v>0.234087371719241</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2711454355219414</v>
+        <v>0.280140121329051</v>
       </c>
       <c r="M85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.488615918273156</v>
       </c>
       <c r="N85" t="n">
-        <v>4.439962810172488</v>
+        <v>4.486629258925698</v>
       </c>
       <c r="O85" t="n">
-        <v>0.003398813600267468</v>
+        <v>0.003296136043681622</v>
       </c>
       <c r="P85" t="n">
-        <v>1e-05</v>
+        <v>1.000000000000389e-05</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001468855054690203</v>
+        <v>0.001469872716214687</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001663671441295562</v>
+        <v>0.001743971564358019</v>
       </c>
       <c r="S85" t="n">
-        <v>0.02843903804865015</v>
+        <v>1.000000000000016e-05</v>
       </c>
       <c r="T85" t="n">
-        <v>0.008004299260479519</v>
+        <v>0.007173279975091383</v>
       </c>
       <c r="U85" t="n">
-        <v>0.008420221070907985</v>
+        <v>0.008869431645645152</v>
       </c>
       <c r="V85" t="n">
-        <v>0.00277654925995669</v>
+        <v>0.002771769748580426</v>
       </c>
       <c r="W85" t="n">
-        <v>0.0024980893071266</v>
+        <v>0.00281278493756876</v>
       </c>
       <c r="X85" t="n">
-        <v>47.76940191999788</v>
+        <v>0.1248270624367359</v>
       </c>
     </row>
     <row r="86">
@@ -7298,46 +7298,46 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1218510305567165</v>
+        <v>0.1246919775437176</v>
       </c>
       <c r="L86" t="n">
-        <v>0.150920255932235</v>
+        <v>0.1550425121143549</v>
       </c>
       <c r="M86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.567691173450373</v>
       </c>
       <c r="N86" t="n">
-        <v>4.397027100878813</v>
+        <v>4.512548632694066</v>
       </c>
       <c r="O86" t="n">
-        <v>0.005856470229560452</v>
+        <v>0.005849095074375368</v>
       </c>
       <c r="P86" t="n">
-        <v>1e-05</v>
+        <v>1.000000000000081e-05</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.00143257894703717</v>
+        <v>0.001430381346093342</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001760414585017851</v>
+        <v>0.001787067398720183</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000348625754188e-05</v>
+        <v>1.000000000000013e-05</v>
       </c>
       <c r="T86" t="n">
-        <v>0.01773048097352194</v>
+        <v>0.01733173470967076</v>
       </c>
       <c r="U86" t="n">
-        <v>0.009823434232775157</v>
+        <v>0.01091931350920984</v>
       </c>
       <c r="V86" t="n">
-        <v>0.002390246238344402</v>
+        <v>0.002402706329626853</v>
       </c>
       <c r="W86" t="n">
-        <v>0.002719605722315283</v>
+        <v>0.002984945666529529</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1769343338870807</v>
+        <v>0.1683221126162023</v>
       </c>
     </row>
     <row r="87">
@@ -7376,46 +7376,46 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1823831187847791</v>
+        <v>0.183694725148222</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2641693060315123</v>
+        <v>0.2687456357101996</v>
       </c>
       <c r="M87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.672692369942369</v>
       </c>
       <c r="N87" t="n">
-        <v>4.553830090712459</v>
+        <v>4.616044464788106</v>
       </c>
       <c r="O87" t="n">
-        <v>0.004980633119109176</v>
+        <v>0.004964727179279235</v>
       </c>
       <c r="P87" t="n">
-        <v>1.000000000070573e-05</v>
+        <v>1.000000000000001e-05</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.002062261297962087</v>
+        <v>0.002033794528026338</v>
       </c>
       <c r="R87" t="n">
-        <v>0.00212325050228108</v>
+        <v>0.002179270426489814</v>
       </c>
       <c r="S87" t="n">
-        <v>0.007282707616781694</v>
+        <v>1e-05</v>
       </c>
       <c r="T87" t="n">
-        <v>0.01407802161630126</v>
+        <v>0.01278550199599605</v>
       </c>
       <c r="U87" t="n">
-        <v>0.01014363916015775</v>
+        <v>0.01022621818961415</v>
       </c>
       <c r="V87" t="n">
-        <v>0.003890187839336987</v>
+        <v>0.003740057321166303</v>
       </c>
       <c r="W87" t="n">
-        <v>0.003408748037372227</v>
+        <v>0.003549715269311207</v>
       </c>
       <c r="X87" t="n">
-        <v>3.198489394796905</v>
+        <v>0.1202410704999621</v>
       </c>
     </row>
     <row r="88">
@@ -7454,46 +7454,46 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2319557577696864</v>
+        <v>0.2274032847723464</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1671546780541192</v>
+        <v>0.1673328583440921</v>
       </c>
       <c r="M88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.517087837474207</v>
       </c>
       <c r="N88" t="n">
-        <v>4.562998910270895</v>
+        <v>4.647285499139455</v>
       </c>
       <c r="O88" t="n">
-        <v>0.005120347597205814</v>
+        <v>0.005266147828622851</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0005605653615454847</v>
+        <v>0.0005465931621263184</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0008527314629994465</v>
+        <v>0.0008493419608545413</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001426069481131531</v>
+        <v>0.001407573790231963</v>
       </c>
       <c r="S88" t="n">
-        <v>1.000000040629886e-05</v>
+        <v>1.00000000000075e-05</v>
       </c>
       <c r="T88" t="n">
-        <v>0.01207422810232853</v>
+        <v>0.01243257252173008</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01043046732070606</v>
+        <v>0.01083660223235061</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001552070467311101</v>
+        <v>0.001553682158523592</v>
       </c>
       <c r="W88" t="n">
-        <v>0.002100137902891962</v>
+        <v>0.002124945130946269</v>
       </c>
       <c r="X88" t="n">
-        <v>0.1820735318449627</v>
+        <v>0.1818832472986572</v>
       </c>
     </row>
     <row r="89">
@@ -7532,46 +7532,46 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3258478558501788</v>
+        <v>0.3272038829542777</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3107837414290504</v>
+        <v>0.321952740767023</v>
       </c>
       <c r="M89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.487315914632268</v>
       </c>
       <c r="N89" t="n">
-        <v>4.618521904924356</v>
+        <v>4.608693782980143</v>
       </c>
       <c r="O89" t="n">
-        <v>0.00442444307581052</v>
+        <v>0.004305939976017327</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001471881158040339</v>
+        <v>0.001456081439865403</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001381549427026332</v>
+        <v>0.001404315030037233</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001854816277450143</v>
+        <v>0.001916351078513785</v>
       </c>
       <c r="S89" t="n">
-        <v>0.05805564735399318</v>
+        <v>1.000000000000149e-05</v>
       </c>
       <c r="T89" t="n">
-        <v>0.009370829777707519</v>
+        <v>0.008668944829848734</v>
       </c>
       <c r="U89" t="n">
-        <v>0.004493940831301072</v>
+        <v>0.004370310872916383</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002378641491881329</v>
+        <v>0.002421010923300436</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002465537211000412</v>
+        <v>0.002843692963168578</v>
       </c>
       <c r="X89" t="n">
-        <v>120.2336647825411</v>
+        <v>0.07664868788764578</v>
       </c>
     </row>
     <row r="90">
@@ -7610,46 +7610,46 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1998835850923684</v>
+        <v>0.2282474838080587</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3874672239799537</v>
+        <v>0.4832343948314514</v>
       </c>
       <c r="M90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.491846084938333</v>
       </c>
       <c r="N90" t="n">
-        <v>3.538022648052697</v>
+        <v>4.280875882070323</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003704659594391141</v>
+        <v>0.003757399696253097</v>
       </c>
       <c r="P90" t="n">
-        <v>0.002849472316108913</v>
+        <v>0.003634252918635858</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.005342055151261642</v>
+        <v>0.006439946019001296</v>
       </c>
       <c r="R90" t="n">
-        <v>0.008123417943435091</v>
+        <v>0.009893870077762896</v>
       </c>
       <c r="S90" t="n">
-        <v>1.000000000065243e-05</v>
+        <v>0.002401356286536427</v>
       </c>
       <c r="T90" t="n">
-        <v>0.005629010447954375</v>
+        <v>0.00697155200881593</v>
       </c>
       <c r="U90" t="n">
-        <v>0.007869739791176635</v>
+        <v>0.005981129556628113</v>
       </c>
       <c r="V90" t="n">
-        <v>0.0128293440073442</v>
+        <v>0.01242154336331217</v>
       </c>
       <c r="W90" t="n">
-        <v>0.02171970270917327</v>
+        <v>0.02564634798467763</v>
       </c>
       <c r="X90" t="n">
-        <v>0.01752724607770281</v>
+        <v>0.08972936629531826</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Flexible CUE/Local_estpar_protection_True_vo_False_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_estpar_protection_True_vo_False_CUE_True.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.230173922345163</v>
+        <v>0.1675307491422628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2038584361609218</v>
+        <v>0.2048300406722742</v>
       </c>
       <c r="M2" t="n">
-        <v>4.404174468294835</v>
+        <v>4.389847264452648</v>
       </c>
       <c r="N2" t="n">
-        <v>4.431700328899079</v>
+        <v>4.431576054995937</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002691167565226858</v>
+        <v>0.003853953478220601</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002705328869841683</v>
+        <v>0.002513778863497358</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007388555130337309</v>
+        <v>0.0007259599729831546</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009972553073629008</v>
+        <v>0.0009436085537551152</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006271730006101701</v>
+        <v>0.0005963129724235647</v>
       </c>
       <c r="T2" t="n">
-        <v>0.008429000661916652</v>
+        <v>0.01448133346667146</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006114632638712192</v>
+        <v>0.007018565941274484</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001650796340018038</v>
+        <v>0.001587892912391682</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001951147053555535</v>
+        <v>0.001933332546647551</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001511764627242887</v>
+        <v>0.00146920357232798</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1194156710580432</v>
+        <v>0.06728994388303008</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1413287515195503</v>
+        <v>0.1147533473965417</v>
       </c>
       <c r="M3" t="n">
-        <v>4.321674553984673</v>
+        <v>4.320004150219157</v>
       </c>
       <c r="N3" t="n">
-        <v>4.331611202164182</v>
+        <v>4.325751599928199</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00297629722833991</v>
+        <v>0.00485205513413454</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001658051600468724</v>
+        <v>0.001506651412331335</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006110701801911452</v>
+        <v>0.0006050271674086546</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005416627933942327</v>
+        <v>0.0004945637880854745</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003075901248437788</v>
+        <v>0.0002775217814487309</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01069902560507406</v>
+        <v>0.02103436418520736</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003595712092669254</v>
+        <v>0.004487076223386675</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001344252488470284</v>
+        <v>0.001301463270110606</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001154851164725616</v>
+        <v>0.001106177292728386</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001101890743741658</v>
+        <v>0.001060440430609973</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4194869788621236</v>
+        <v>0.3790979175914366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2269943105173577</v>
+        <v>0.3184655559598977</v>
       </c>
       <c r="M4" t="n">
-        <v>4.305760853918062</v>
+        <v>4.287350971919315</v>
       </c>
       <c r="N4" t="n">
-        <v>4.566683054074947</v>
+        <v>4.557790015552257</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002736524493574656</v>
+        <v>0.003374865004098183</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002303342962690763</v>
+        <v>0.002207599506483555</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003126631300834826</v>
+        <v>0.000322732870561805</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001177590037346351</v>
+        <v>0.001189601919583946</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002881513962370256</v>
+        <v>0.0003756720376218764</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008055813858564654</v>
+        <v>0.01142924617285042</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006067675723701741</v>
+        <v>0.006350583394504265</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001290341320083157</v>
+        <v>0.001302150441683301</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002155228545424732</v>
+        <v>0.002266294007937966</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001631635945398531</v>
+        <v>0.001834266108019734</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1836362466865699</v>
+        <v>0.1248471298400898</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2222504432753144</v>
+        <v>0.2038781249000921</v>
       </c>
       <c r="M5" t="n">
-        <v>4.304261087108948</v>
+        <v>4.305018687016936</v>
       </c>
       <c r="N5" t="n">
-        <v>4.346505225166321</v>
+        <v>4.340541272329272</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002405050948081549</v>
+        <v>0.003463628797660147</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002171415004770004</v>
+        <v>0.002035862702427586</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008481916127724251</v>
+        <v>0.0008345851684829496</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000831983808958567</v>
+        <v>0.000785116565266984</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001154948362134588</v>
+        <v>0.001090965269440374</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007421336883031586</v>
+        <v>0.01293630062902802</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004364053333945715</v>
+        <v>0.004969911039530487</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001913631676307882</v>
+        <v>0.001836553786907319</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001657997414157822</v>
+        <v>0.001620513015563399</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002462008849885081</v>
+        <v>0.002339785824961803</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1696931496494424</v>
+        <v>0.107225671629976</v>
       </c>
       <c r="L6" t="n">
-        <v>0.202075292835271</v>
+        <v>0.1680837610175768</v>
       </c>
       <c r="M6" t="n">
-        <v>4.366354518668125</v>
+        <v>4.368954957723821</v>
       </c>
       <c r="N6" t="n">
-        <v>4.383001931491272</v>
+        <v>4.375818493033783</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001864795433950721</v>
+        <v>0.002634925784352573</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001386265774497913</v>
+        <v>0.001199688980577356</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005315585590484993</v>
+        <v>0.0005223052362560459</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003945316973418944</v>
+        <v>0.0003565045102219321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003435868921093666</v>
+        <v>0.0002984251147419407</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005575014096319824</v>
+        <v>0.009314299154794162</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002577200478225922</v>
+        <v>0.002678780104464536</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001211473367826345</v>
+        <v>0.001170401773550842</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009675842702812734</v>
+        <v>0.0009324557397638258</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001032142793842978</v>
+        <v>0.000969514941902956</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2030468160086783</v>
+        <v>0.1333701387526627</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1596994159452441</v>
+        <v>0.1625235119008206</v>
       </c>
       <c r="M7" t="n">
-        <v>4.27650586554834</v>
+        <v>4.248251975604964</v>
       </c>
       <c r="N7" t="n">
-        <v>4.381338268498013</v>
+        <v>4.382559995682484</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003103819155328756</v>
+        <v>0.004711414226248903</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001972992554386203</v>
+        <v>0.001844412951006271</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005401657796003979</v>
+        <v>0.0005322613546376014</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009136247877191884</v>
+        <v>0.0008581942783232899</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004800161103622279</v>
+        <v>0.0004591556798768062</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0104334866747243</v>
+        <v>0.01907880234870372</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004700635849353097</v>
+        <v>0.005592854959018339</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001236153287031197</v>
+        <v>0.001206711739554871</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001712647225019129</v>
+        <v>0.001688397069030864</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001817542950218138</v>
+        <v>0.001840137105696079</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1640874531430341</v>
+        <v>0.1151420749833156</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1429798880331228</v>
+        <v>0.1534975316168945</v>
       </c>
       <c r="M8" t="n">
-        <v>4.438538840521598</v>
+        <v>4.414720542971803</v>
       </c>
       <c r="N8" t="n">
-        <v>4.410426778198659</v>
+        <v>4.415178420793291</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005245165867247816</v>
+        <v>0.008739183111701895</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002918142886038812</v>
+        <v>0.003286089759654253</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001000006771831926</v>
+        <v>0.000989457185409487</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001447439816701102</v>
+        <v>0.001395893080353674</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006763389631962464</v>
+        <v>0.0006528538755013741</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02113413948619935</v>
+        <v>0.04463828781542144</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01025597389849785</v>
+        <v>0.01610157218877823</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002303843660330272</v>
+        <v>0.002239167921278919</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003105436274123283</v>
+        <v>0.003103384277823828</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001406568440965932</v>
+        <v>0.001374179442450977</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2020811236552771</v>
+        <v>0.1394388633541007</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1613723476081795</v>
+        <v>0.1651878946910895</v>
       </c>
       <c r="M9" t="n">
-        <v>4.239065410023795</v>
+        <v>4.219037933743781</v>
       </c>
       <c r="N9" t="n">
-        <v>4.367167907558467</v>
+        <v>4.366094553886756</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004290225140850388</v>
+        <v>0.006644817911578864</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002649517914119729</v>
+        <v>0.002653413394878246</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0007461854387285922</v>
+        <v>0.0007375089167094092</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009143079996859878</v>
+        <v>0.0008754842255644615</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0008138129006080895</v>
+        <v>0.0007884022964809121</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01515852170608924</v>
+        <v>0.02887633128993129</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006973758107217394</v>
+        <v>0.009541871206054502</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001663209696673919</v>
+        <v>0.001614294759595759</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001748669885040012</v>
+        <v>0.001761642571119023</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001631246643017977</v>
+        <v>0.001605702377407433</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2191421824694482</v>
+        <v>0.1601968509094092</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1210509771029948</v>
+        <v>0.130920201519755</v>
       </c>
       <c r="M10" t="n">
-        <v>4.12702849534982</v>
+        <v>4.10267319021357</v>
       </c>
       <c r="N10" t="n">
-        <v>4.237975785698606</v>
+        <v>4.239142325210715</v>
       </c>
       <c r="O10" t="n">
-        <v>0.00431271687013695</v>
+        <v>0.007304645677345035</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002997027429017953</v>
+        <v>0.003699421877335026</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005597509843635526</v>
+        <v>0.0005537148155987974</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001036493947908923</v>
+        <v>0.0009741802659076991</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005894502339337932</v>
+        <v>0.0005762582108201532</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01700922303862318</v>
+        <v>0.03714941934485087</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009802820767895366</v>
+        <v>0.01777649237644448</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001281941200999306</v>
+        <v>0.0012598723698478</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001957330673147972</v>
+        <v>0.001936759185674851</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001308603085578598</v>
+        <v>0.001320214901310492</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1802913684560599</v>
+        <v>0.1526494909041163</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3465459166179319</v>
+        <v>0.3617543883286449</v>
       </c>
       <c r="M11" t="n">
-        <v>4.084108994242105</v>
+        <v>4.071785132257231</v>
       </c>
       <c r="N11" t="n">
-        <v>4.260313558854912</v>
+        <v>4.259343320790163</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002733257216197332</v>
+        <v>0.003380069405007881</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001722193761365708</v>
+        <v>0.001726414282796366</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001315645779813892</v>
+        <v>0.001167382545501663</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001873257341608662</v>
+        <v>0.001824041866324323</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001671445189131837</v>
+        <v>0.001635389523585516</v>
       </c>
       <c r="T11" t="n">
-        <v>0.008519173098021407</v>
+        <v>0.01329369107103272</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003526720528374913</v>
+        <v>0.00330016638752387</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00300725694874557</v>
+        <v>0.002783038135309828</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004227677013594756</v>
+        <v>0.004480391447575571</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003670979004647733</v>
+        <v>0.003683163643177728</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1045004028531513</v>
+        <v>0.08829076404957915</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1275452235151289</v>
+        <v>0.1564306765210551</v>
       </c>
       <c r="M12" t="n">
-        <v>4.089982626528647</v>
+        <v>4.076006435080762</v>
       </c>
       <c r="N12" t="n">
-        <v>4.108463327318218</v>
+        <v>4.119084544729942</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0009158516158195828</v>
+        <v>0.002029943159896892</v>
       </c>
       <c r="P12" t="n">
-        <v>1e-05</v>
+        <v>0.0007508268616601299</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0004820762617375363</v>
+        <v>0.000518983548751209</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001174786354567341</v>
+        <v>0.001746797905673515</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004659019677374974</v>
+        <v>0.0005154623926404089</v>
       </c>
       <c r="T12" t="n">
-        <v>0.004000147410888139</v>
+        <v>0.0102431723704459</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02943851980707652</v>
+        <v>0.005678411356210642</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001111923222144807</v>
+        <v>0.001179260997514533</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03594085991515948</v>
+        <v>0.01152685779567679</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00231723272746222</v>
+        <v>0.001233756474361169</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1443570250143755</v>
+        <v>0.1269149850337687</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2187095491604443</v>
+        <v>0.1956628171470529</v>
       </c>
       <c r="M13" t="n">
-        <v>4.284315393262776</v>
+        <v>4.279020890353953</v>
       </c>
       <c r="N13" t="n">
-        <v>4.51567977581814</v>
+        <v>4.518930854765108</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002105224092890962</v>
+        <v>0.002592748027993644</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001705262080890069</v>
+        <v>0.001691600073228232</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0009283127061324889</v>
+        <v>0.0008940940929066572</v>
       </c>
       <c r="R13" t="n">
-        <v>0.008650211624607083</v>
+        <v>0.008498174816453791</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01477562608661544</v>
+        <v>0.01462609888250145</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01681614225514103</v>
+        <v>0.01999697253493458</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0440895914784371</v>
+        <v>0.04264701158801772</v>
       </c>
       <c r="V13" t="n">
-        <v>0.007293313646723081</v>
+        <v>0.00686496569608934</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02387274856532783</v>
+        <v>0.02136914023335823</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03991274241042734</v>
+        <v>0.03815968010805875</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1882369422267624</v>
+        <v>0.1438330238577966</v>
       </c>
       <c r="L14" t="n">
-        <v>0.276227815610285</v>
+        <v>0.2260562535148885</v>
       </c>
       <c r="M14" t="n">
-        <v>4.399378232032912</v>
+        <v>4.392368297887129</v>
       </c>
       <c r="N14" t="n">
-        <v>4.358713059953477</v>
+        <v>4.350003611700329</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01272328519468487</v>
+        <v>0.01731843332614435</v>
       </c>
       <c r="P14" t="n">
-        <v>0.00317105273627055</v>
+        <v>0.001606890339938171</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.007528715583936452</v>
+        <v>0.007119977468138647</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00693444310215034</v>
+        <v>0.00608832496987312</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01055824826415903</v>
+        <v>0.00878674120230399</v>
       </c>
       <c r="T14" t="n">
-        <v>0.03211050747522869</v>
+        <v>0.05166185875555837</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02191885708826445</v>
+        <v>0.02217203453552895</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01580386025966229</v>
+        <v>0.01500815610162146</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01453949753169552</v>
+        <v>0.01378659802322258</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02992868341229806</v>
+        <v>0.02729739364817373</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1874830231703039</v>
+        <v>0.1307591005177591</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2738406689335328</v>
+        <v>0.2273896064186872</v>
       </c>
       <c r="M15" t="n">
-        <v>4.085204214067701</v>
+        <v>4.079261036110907</v>
       </c>
       <c r="N15" t="n">
-        <v>4.242020397769503</v>
+        <v>4.223894393655108</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01254241917934499</v>
+        <v>0.01631021968681497</v>
       </c>
       <c r="P15" t="n">
-        <v>0.004808876702551187</v>
+        <v>0.004127096205365092</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.007628422515599419</v>
+        <v>0.007373053898522652</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005527788073275897</v>
+        <v>0.00472099740469856</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02496862696886337</v>
+        <v>0.02287937334887536</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03198667718042063</v>
+        <v>0.04872768288020187</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01483979876365708</v>
+        <v>0.01637470834662126</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01635488726136984</v>
+        <v>0.01579128497194075</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01216612177749948</v>
+        <v>0.01142315549228086</v>
       </c>
       <c r="X15" t="n">
-        <v>0.08699806654188172</v>
+        <v>0.07802305702130345</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5161649251798621</v>
+        <v>0.5129655543643412</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5289027221649324</v>
+        <v>0.557259640164412</v>
       </c>
       <c r="M16" t="n">
-        <v>4.346437810309332</v>
+        <v>4.407580888704488</v>
       </c>
       <c r="N16" t="n">
-        <v>4.497654451769204</v>
+        <v>4.533891488100918</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0281651377694198</v>
+        <v>0.0281033980222152</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01958518096781141</v>
+        <v>0.01962191051292817</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01984915215896495</v>
+        <v>0.02089202593957276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01270990256982217</v>
+        <v>0.01324684577104615</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02222029913265714</v>
+        <v>0.006392029570576234</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08447027587891738</v>
+        <v>0.4081434550788374</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03338788909631528</v>
+        <v>0.3437940804518302</v>
       </c>
       <c r="V16" t="n">
-        <v>0.05598673841203895</v>
+        <v>0.3070877940680208</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03195524007674559</v>
+        <v>0.1782552037006788</v>
       </c>
       <c r="X16" t="n">
-        <v>18.89505989157118</v>
+        <v>40.00688704927386</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1472285974082657</v>
+        <v>0.1557936046085961</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2360357464914354</v>
+        <v>0.2186598458224473</v>
       </c>
       <c r="M17" t="n">
-        <v>3.853984103588437</v>
+        <v>3.843478583732289</v>
       </c>
       <c r="N17" t="n">
-        <v>4.012166378646453</v>
+        <v>4.003957091057472</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01304181252352631</v>
+        <v>0.01648834078966527</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001315347535609482</v>
+        <v>0.002203229778118012</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.006565461335948802</v>
+        <v>0.006498393042520786</v>
       </c>
       <c r="R17" t="n">
-        <v>0.003993807750292989</v>
+        <v>0.003791007255171619</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01044396415661191</v>
+        <v>0.01035876462970347</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03345641381409505</v>
+        <v>0.04703005936744935</v>
       </c>
       <c r="U17" t="n">
-        <v>0.04418673437050782</v>
+        <v>0.01607643618150006</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01429523897905623</v>
+        <v>0.01364663172357149</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02275818103347639</v>
+        <v>0.009870199832760407</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02236502629756599</v>
+        <v>0.02040256571215567</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2424607087442707</v>
+        <v>0.1816593812827441</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2651971061528096</v>
+        <v>0.2297599240156478</v>
       </c>
       <c r="M18" t="n">
-        <v>4.298420190621356</v>
+        <v>4.289171463703494</v>
       </c>
       <c r="N18" t="n">
-        <v>4.300116150274684</v>
+        <v>4.29001168622623</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01326870139802743</v>
+        <v>0.01739261734314398</v>
       </c>
       <c r="P18" t="n">
-        <v>0.006809503203409333</v>
+        <v>0.006830928706074936</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.006045214067951051</v>
+        <v>0.005864640039434408</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008471813273374094</v>
+        <v>0.007731479483988783</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008835381506191332</v>
+        <v>0.008269234149345694</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03311493142453596</v>
+        <v>0.05021187966092077</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01546026927990645</v>
+        <v>0.01787639024362694</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01276674356694847</v>
+        <v>0.01241972120058862</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01479202865830817</v>
+        <v>0.01426045826164472</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01543526946701237</v>
+        <v>0.01483387158463595</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.161033465819801</v>
+        <v>0.107691775349662</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2233885571873788</v>
+        <v>0.1758416743262448</v>
       </c>
       <c r="M19" t="n">
-        <v>3.990866149206148</v>
+        <v>3.99750997059567</v>
       </c>
       <c r="N19" t="n">
-        <v>4.377813604369669</v>
+        <v>4.368548141329543</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004944859657935866</v>
+        <v>0.006398901137877754</v>
       </c>
       <c r="P19" t="n">
-        <v>0.009647790526085663</v>
+        <v>0.009313786462988539</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003380252631110283</v>
+        <v>0.003312838791621745</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001508451365663482</v>
+        <v>0.001365805554459212</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03165977277557139</v>
+        <v>0.02905336378899924</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01933349438468121</v>
+        <v>0.02716891950590889</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02425993118002748</v>
+        <v>0.02601667078406661</v>
       </c>
       <c r="V19" t="n">
-        <v>0.008963682648373789</v>
+        <v>0.008823830071816474</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006852669240307164</v>
+        <v>0.006621070205702204</v>
       </c>
       <c r="X19" t="n">
-        <v>0.159790445284404</v>
+        <v>0.1377689274951135</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2706740016525256</v>
+        <v>0.2057022057339838</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2927341412025184</v>
+        <v>0.2460353464898241</v>
       </c>
       <c r="M20" t="n">
-        <v>4.627752525577289</v>
+        <v>4.630732926731516</v>
       </c>
       <c r="N20" t="n">
-        <v>4.593214902107496</v>
+        <v>4.596083151047137</v>
       </c>
       <c r="O20" t="n">
-        <v>0.008405074024867456</v>
+        <v>0.0103417849159518</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0008181292013049757</v>
+        <v>1.000000000000963e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.004350963669534897</v>
+        <v>0.004347903284454896</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005514120826268748</v>
+        <v>0.005119101740639123</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01512166055457031</v>
+        <v>0.01285926643958463</v>
       </c>
       <c r="T20" t="n">
-        <v>0.02149601195623009</v>
+        <v>0.02918269803251593</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01607547089742069</v>
+        <v>0.01705318662732906</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01013008342966108</v>
+        <v>0.0100686371778519</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01141365875624619</v>
+        <v>0.01102993125728473</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02918885627428229</v>
+        <v>0.02694208264364232</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1202941340488625</v>
+        <v>0.07261609984294198</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1378533115986938</v>
+        <v>0.1314178125355716</v>
       </c>
       <c r="M21" t="n">
-        <v>4.107682434211664</v>
+        <v>4.163497628306884</v>
       </c>
       <c r="N21" t="n">
-        <v>4.121165225382007</v>
+        <v>4.130754803237112</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01552863482697239</v>
+        <v>0.0189004924063926</v>
       </c>
       <c r="P21" t="n">
-        <v>0.05125495867531689</v>
+        <v>0.06249404395426711</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.00495496347823411</v>
+        <v>0.006481828016717642</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000033484e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.000000000931178e-05</v>
+        <v>1.000000000001769e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05404724424884073</v>
+        <v>0.08128145033746066</v>
       </c>
       <c r="U21" t="n">
-        <v>0.159252307059572</v>
+        <v>0.2450136175425877</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01426035089263716</v>
+        <v>0.01982066511612264</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01114106901589464</v>
+        <v>0.01276218550501924</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03839815370889071</v>
+        <v>0.05859776011175964</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2818005832925195</v>
+        <v>0.2535748896970106</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3218063814813968</v>
+        <v>0.2788887968123748</v>
       </c>
       <c r="M22" t="n">
-        <v>4.137156494914622</v>
+        <v>4.130086663000352</v>
       </c>
       <c r="N22" t="n">
-        <v>4.309732006266833</v>
+        <v>4.298500606978414</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005797547416033553</v>
+        <v>0.006872253663045675</v>
       </c>
       <c r="P22" t="n">
-        <v>1.00000000001984e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002656208004106704</v>
+        <v>0.002633998113527869</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003429210519692688</v>
+        <v>0.003212239643198801</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01261914908567431</v>
+        <v>0.01205624202677407</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01601341512802824</v>
+        <v>0.02008115770515083</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01477007531210635</v>
+        <v>0.01278400450270836</v>
       </c>
       <c r="V22" t="n">
-        <v>0.00848921117124949</v>
+        <v>0.008374303456408348</v>
       </c>
       <c r="W22" t="n">
-        <v>0.009280671544128939</v>
+        <v>0.008780055244100096</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02761135262466899</v>
+        <v>0.02617285586858337</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.208871687187535</v>
+        <v>0.164483483710421</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2718044786969178</v>
+        <v>0.2359576027923808</v>
       </c>
       <c r="M23" t="n">
-        <v>3.863994820752609</v>
+        <v>3.861994256796289</v>
       </c>
       <c r="N23" t="n">
-        <v>4.10878782592642</v>
+        <v>4.088450438325594</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01076874551793343</v>
+        <v>0.01364396008633799</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004270830336473298</v>
+        <v>0.003812892867812038</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.003955459835768994</v>
+        <v>0.003798503165484583</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006148793146596763</v>
+        <v>0.005039233828749968</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02437991319119103</v>
+        <v>0.02282347393154775</v>
       </c>
       <c r="T23" t="n">
-        <v>0.02713848602460157</v>
+        <v>0.03907336887971351</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01945583085355903</v>
+        <v>0.01973122813687771</v>
       </c>
       <c r="V23" t="n">
-        <v>0.009726277884612841</v>
+        <v>0.009524583584433959</v>
       </c>
       <c r="W23" t="n">
-        <v>0.01595988854778212</v>
+        <v>0.01535919420764513</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07673098070186342</v>
+        <v>0.07039096781526448</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3875416039382416</v>
+        <v>0.3446324318476313</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4585213846789534</v>
+        <v>0.452020538268895</v>
       </c>
       <c r="M24" t="n">
-        <v>4.305819674281706</v>
+        <v>4.315611646840071</v>
       </c>
       <c r="N24" t="n">
-        <v>4.373982753815935</v>
+        <v>4.364672008334238</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01335184653723498</v>
+        <v>0.01418672412253162</v>
       </c>
       <c r="P24" t="n">
-        <v>0.009495457683851587</v>
+        <v>0.009568504000572138</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01324016456593231</v>
+        <v>0.0131546271725437</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01331352524374036</v>
+        <v>0.01303765519961699</v>
       </c>
       <c r="S24" t="n">
-        <v>1.000000002711727e-05</v>
+        <v>1.000000000000016e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0.04057200417275288</v>
+        <v>0.0671877340657514</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0266029510037471</v>
+        <v>0.0393448202960815</v>
       </c>
       <c r="V24" t="n">
-        <v>0.03168082067550165</v>
+        <v>0.03162314203714289</v>
       </c>
       <c r="W24" t="n">
-        <v>0.02984261827472873</v>
+        <v>0.02311918699882783</v>
       </c>
       <c r="X24" t="n">
-        <v>2.832379455353822</v>
+        <v>3.591836590380365</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.215848059616466</v>
+        <v>0.1556201893189063</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2284594467336942</v>
+        <v>0.1790189136154802</v>
       </c>
       <c r="M25" t="n">
-        <v>4.310157944037903</v>
+        <v>4.317303423812332</v>
       </c>
       <c r="N25" t="n">
-        <v>4.340621142564224</v>
+        <v>4.341380298872839</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002231536890875667</v>
+        <v>0.00300498158514161</v>
       </c>
       <c r="P25" t="n">
-        <v>1.00000000000183e-05</v>
+        <v>1.000000000000013e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0005427421474549116</v>
+        <v>0.0005914794219626882</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003337243919490771</v>
+        <v>0.0003192861493801596</v>
       </c>
       <c r="S25" t="n">
-        <v>9.811530508613571e-05</v>
+        <v>7.319086832606948e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.005387245478812809</v>
+        <v>0.007940678178872469</v>
       </c>
       <c r="U25" t="n">
-        <v>0.002879068444643339</v>
+        <v>0.003267684661634188</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001544802675924805</v>
+        <v>0.001600596823571486</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001344254172780884</v>
+        <v>0.00131732034540001</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001314073681162972</v>
+        <v>0.001298920647312621</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3197948172394026</v>
+        <v>0.2658710797035032</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3076761724502429</v>
+        <v>0.267236756879264</v>
       </c>
       <c r="M26" t="n">
-        <v>4.224153844393832</v>
+        <v>4.209752341131509</v>
       </c>
       <c r="N26" t="n">
-        <v>4.299738132353408</v>
+        <v>4.288592832345312</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002886451885566999</v>
+        <v>0.003501881328880443</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001543354958377238</v>
+        <v>0.001333305726534032</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.000660358953136808</v>
+        <v>0.0006280711980899499</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005625695089046828</v>
+        <v>0.0004991557484121078</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003215504714468515</v>
+        <v>0.0002789492508540321</v>
       </c>
       <c r="T26" t="n">
-        <v>0.005709499860443091</v>
+        <v>0.007543815995314331</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002436937228166082</v>
+        <v>0.002329226323486624</v>
       </c>
       <c r="V26" t="n">
-        <v>0.00171961532673345</v>
+        <v>0.001682785369071658</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001513624191671615</v>
+        <v>0.001465860506004005</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001258532393978183</v>
+        <v>0.001238211879703194</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2439507965539418</v>
+        <v>0.1853792209497878</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3067422390276155</v>
+        <v>0.2584091786475279</v>
       </c>
       <c r="M27" t="n">
-        <v>4.149671453558346</v>
+        <v>4.135160058706046</v>
       </c>
       <c r="N27" t="n">
-        <v>4.151068964910465</v>
+        <v>4.129305238841737</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001458714140586512</v>
+        <v>0.001731396150195134</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005687835756680706</v>
+        <v>0.0003003211034702188</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.00119843705062235</v>
+        <v>0.001184104518192363</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006419722126537749</v>
+        <v>0.000537613651776248</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007223262149807405</v>
+        <v>0.0006850676245755442</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003386164804875829</v>
+        <v>0.004392134417186663</v>
       </c>
       <c r="U27" t="n">
-        <v>0.00242254127015918</v>
+        <v>0.002434931435213605</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002472152956502945</v>
+        <v>0.002460741437311616</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001712390984599777</v>
+        <v>0.001625009656909543</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001794196421560956</v>
+        <v>0.001768732302565485</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3989356014586465</v>
+        <v>0.3642355136098986</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4106034617169131</v>
+        <v>0.4013541408333951</v>
       </c>
       <c r="M28" t="n">
-        <v>4.114744299841788</v>
+        <v>4.119195147734761</v>
       </c>
       <c r="N28" t="n">
-        <v>4.29421293162847</v>
+        <v>4.289586198139278</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0020037747322748</v>
+        <v>0.00221464884003137</v>
       </c>
       <c r="P28" t="n">
-        <v>1.000000000000033e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001514722681317508</v>
+        <v>0.001543134509394177</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005014510551538672</v>
+        <v>0.004995506758890183</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01036748981554327</v>
+        <v>0.01018175800852629</v>
       </c>
       <c r="T28" t="n">
-        <v>0.004603876541967948</v>
+        <v>0.005358061366185148</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01091474989644152</v>
+        <v>0.01045295458559381</v>
       </c>
       <c r="V28" t="n">
-        <v>0.00331408430370514</v>
+        <v>0.003416734306455159</v>
       </c>
       <c r="W28" t="n">
-        <v>0.009606173114659567</v>
+        <v>0.0104860953876412</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02351990982884054</v>
+        <v>0.02336936268326069</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5337507387871602</v>
+        <v>0.541363956397434</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3455125462067315</v>
+        <v>0.523576445841029</v>
       </c>
       <c r="M29" t="n">
-        <v>4.255427909449321</v>
+        <v>4.316787024057529</v>
       </c>
       <c r="N29" t="n">
-        <v>4.202276187780864</v>
+        <v>4.269220077614253</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004750996569864848</v>
+        <v>0.004070993851702244</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01809454868918335</v>
+        <v>0.01910672843730625</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0001807004228334998</v>
+        <v>0.0008484369058424253</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01725164143317796</v>
+        <v>0.02113150125770955</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009480158620399576</v>
+        <v>0.01040541863446287</v>
       </c>
       <c r="T29" t="n">
-        <v>0.009135815873177288</v>
+        <v>0.006805880669072288</v>
       </c>
       <c r="U29" t="n">
-        <v>0.06252823516812714</v>
+        <v>0.07573825798056674</v>
       </c>
       <c r="V29" t="n">
-        <v>0.002987836248732887</v>
+        <v>0.003525289405341013</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03301411606916037</v>
+        <v>0.04776847093810734</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01607130683896535</v>
+        <v>0.01792079846937225</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4912707336485012</v>
+        <v>0.4591268398364413</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4029182866425092</v>
+        <v>0.4569091943417217</v>
       </c>
       <c r="M30" t="n">
-        <v>4.515175522261403</v>
+        <v>4.522217691948997</v>
       </c>
       <c r="N30" t="n">
-        <v>4.313113498799031</v>
+        <v>4.322085829707604</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002505461740369046</v>
+        <v>0.002607532933212039</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005081990042261474</v>
+        <v>0.004974153736206312</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.000233203877926856</v>
+        <v>0.0003056591202693142</v>
       </c>
       <c r="R30" t="n">
-        <v>0.009303857418504993</v>
+        <v>0.00966894559042625</v>
       </c>
       <c r="S30" t="n">
-        <v>0.004159474905871037</v>
+        <v>0.004470108735842222</v>
       </c>
       <c r="T30" t="n">
-        <v>0.004859962819699638</v>
+        <v>0.00511594580291493</v>
       </c>
       <c r="U30" t="n">
-        <v>0.009416457870441094</v>
+        <v>0.009084047655176983</v>
       </c>
       <c r="V30" t="n">
-        <v>0.003027736050667094</v>
+        <v>0.003195357207277522</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01538458243787846</v>
+        <v>0.01646205528088828</v>
       </c>
       <c r="X30" t="n">
-        <v>0.00566548586324424</v>
+        <v>0.006248092915545901</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4902078464552742</v>
+        <v>0.4761534586665042</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4307282667397589</v>
+        <v>0.4435755784201663</v>
       </c>
       <c r="M31" t="n">
-        <v>4.249538389327932</v>
+        <v>4.256876131451557</v>
       </c>
       <c r="N31" t="n">
-        <v>4.410351733710971</v>
+        <v>4.406501501649976</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002730239733842983</v>
+        <v>0.002837765847474639</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007275503169651897</v>
+        <v>0.006895209102495803</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0002667186749248477</v>
+        <v>0.0002659987817971182</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001785835699265363</v>
+        <v>0.001796465695426211</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00056394847497899</v>
+        <v>0.0005773366436962788</v>
       </c>
       <c r="T31" t="n">
-        <v>0.004947534112347361</v>
+        <v>0.005244506604222339</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01692632058017633</v>
+        <v>0.01498676172744096</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00255117353923214</v>
+        <v>0.002600231076028347</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003007772002258971</v>
+        <v>0.003174667230699651</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002801064412960188</v>
+        <v>0.002898112892481788</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003204670714311</v>
+        <v>0.4784259818721357</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4277098015031122</v>
+        <v>0.4395375417643161</v>
       </c>
       <c r="M32" t="n">
-        <v>4.53028971271256</v>
+        <v>4.54395154441503</v>
       </c>
       <c r="N32" t="n">
-        <v>4.426130147752106</v>
+        <v>4.423048245990696</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008350083291765586</v>
+        <v>0.0009157733761689355</v>
       </c>
       <c r="P32" t="n">
-        <v>0.005247746006639017</v>
+        <v>0.00518126371884231</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004418886554165519</v>
+        <v>0.004562738219853206</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001401838780852578</v>
+        <v>0.001424639663582253</v>
       </c>
       <c r="T32" t="n">
-        <v>0.00281365799203623</v>
+        <v>0.0030684238680674</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0113549929956145</v>
+        <v>0.01087878385678573</v>
       </c>
       <c r="V32" t="n">
-        <v>0.002600330117320171</v>
+        <v>0.002618432918736213</v>
       </c>
       <c r="W32" t="n">
-        <v>0.008108609775447266</v>
+        <v>0.008778150161159445</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003592609364448746</v>
+        <v>0.003666927493215529</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2851358817564152</v>
+        <v>0.2262549868912993</v>
       </c>
       <c r="L33" t="n">
-        <v>0.318932250993743</v>
+        <v>0.2965494809834754</v>
       </c>
       <c r="M33" t="n">
-        <v>4.308512879316226</v>
+        <v>4.301098115789768</v>
       </c>
       <c r="N33" t="n">
-        <v>4.270877230228868</v>
+        <v>4.26286686107843</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006255038232011506</v>
+        <v>0.007706245063438562</v>
       </c>
       <c r="P33" t="n">
-        <v>0.004238498551876357</v>
+        <v>0.002426124663233034</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003966480546542436</v>
+        <v>0.003904030670491616</v>
       </c>
       <c r="R33" t="n">
-        <v>0.007572420642581414</v>
+        <v>0.007029752232605614</v>
       </c>
       <c r="S33" t="n">
-        <v>0.004151247082158103</v>
+        <v>0.003845834602410518</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01577010449583528</v>
+        <v>0.023314874408194</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02412089826765769</v>
+        <v>0.02052905189638906</v>
       </c>
       <c r="V33" t="n">
-        <v>0.008798785252329851</v>
+        <v>0.008692206022018971</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01425303978700799</v>
+        <v>0.01495124525637704</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007886086965499323</v>
+        <v>0.007837770432662943</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5350531219152354</v>
+        <v>0.5348911130605229</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4497671777617613</v>
+        <v>0.5384668528672936</v>
       </c>
       <c r="M34" t="n">
-        <v>4.263995602912937</v>
+        <v>4.266762406485488</v>
       </c>
       <c r="N34" t="n">
-        <v>4.286052599309091</v>
+        <v>4.312442066410434</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005327415999576042</v>
+        <v>0.00629562701552152</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01468639974602328</v>
+        <v>0.01685103135998725</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.00299204878747737</v>
+        <v>0.003609084823573983</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01477537078025103</v>
+        <v>0.0175965156972246</v>
       </c>
       <c r="S34" t="n">
-        <v>0.008485399023264808</v>
+        <v>0.01047946919245789</v>
       </c>
       <c r="T34" t="n">
-        <v>0.008064321238122247</v>
+        <v>0.009999946561555709</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0557478055123624</v>
+        <v>0.08038445959465043</v>
       </c>
       <c r="V34" t="n">
-        <v>0.005681397228123481</v>
+        <v>0.005150928961116965</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01887525403640121</v>
+        <v>0.02268251891265146</v>
       </c>
       <c r="X34" t="n">
-        <v>0.007357860210382738</v>
+        <v>0.008952354075695538</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3019486698931895</v>
+        <v>0.2505787503790524</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2474304893651948</v>
+        <v>0.2477167002302391</v>
       </c>
       <c r="M35" t="n">
-        <v>4.049554670774522</v>
+        <v>4.045568310128426</v>
       </c>
       <c r="N35" t="n">
-        <v>4.156376315010339</v>
+        <v>4.151139496855899</v>
       </c>
       <c r="O35" t="n">
-        <v>0.002523944227794765</v>
+        <v>0.003337606199172594</v>
       </c>
       <c r="P35" t="n">
-        <v>0.06033587516207787</v>
+        <v>0.07167335909014153</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.000604247511046614</v>
+        <v>0.0005711440859596975</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004779294493895975</v>
+        <v>0.004608579173720933</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0009526229454978009</v>
+        <v>0.0009309639731777782</v>
       </c>
       <c r="T35" t="n">
-        <v>0.01061879416498299</v>
+        <v>0.01476773726321702</v>
       </c>
       <c r="U35" t="n">
-        <v>21.31882728780888</v>
+        <v>31.47066514277005</v>
       </c>
       <c r="V35" t="n">
-        <v>0.002246607056725409</v>
+        <v>0.00216711561491804</v>
       </c>
       <c r="W35" t="n">
-        <v>0.01873085958607459</v>
+        <v>0.01544481478572656</v>
       </c>
       <c r="X35" t="n">
-        <v>0.002611759162348447</v>
+        <v>0.002520839165341034</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4306133506575378</v>
+        <v>0.3956792038623253</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3952362728840799</v>
+        <v>0.3771774987149752</v>
       </c>
       <c r="M36" t="n">
-        <v>4.307865273041947</v>
+        <v>4.298761590070961</v>
       </c>
       <c r="N36" t="n">
-        <v>4.321572623486516</v>
+        <v>4.314521842931012</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001343523339487707</v>
+        <v>0.001469854402202507</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002753977254333692</v>
+        <v>0.002620853217931327</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0004271144016157931</v>
+        <v>0.0003958491160124328</v>
       </c>
       <c r="R36" t="n">
-        <v>0.00193282878989933</v>
+        <v>0.001820364886196814</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001308574399388756</v>
+        <v>0.001239223763040016</v>
       </c>
       <c r="T36" t="n">
-        <v>0.003546840140929287</v>
+        <v>0.004030738006360441</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006142816038114112</v>
+        <v>0.00577013456384589</v>
       </c>
       <c r="V36" t="n">
-        <v>0.002583706314445259</v>
+        <v>0.002558983121866279</v>
       </c>
       <c r="W36" t="n">
-        <v>0.003628160873148946</v>
+        <v>0.003589935731194455</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004515743683529813</v>
+        <v>0.004475253503331811</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1032759135620988</v>
+        <v>0.05738019622196385</v>
       </c>
       <c r="L37" t="n">
-        <v>0.105288088556548</v>
+        <v>0.07190125053007634</v>
       </c>
       <c r="M37" t="n">
-        <v>4.230764125716685</v>
+        <v>4.219329310499894</v>
       </c>
       <c r="N37" t="n">
-        <v>4.263240945631649</v>
+        <v>4.254748164104436</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007667241941911612</v>
+        <v>0.01419430751719529</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003373473473283984</v>
+        <v>0.003970387760790649</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001128822814805678</v>
+        <v>0.00110150966213122</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0008424215255491023</v>
+        <v>0.0007391393914700466</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002261621751080345</v>
+        <v>0.001948695408616885</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02824965751043103</v>
+        <v>0.06175502143646608</v>
       </c>
       <c r="U37" t="n">
-        <v>0.009400509936786258</v>
+        <v>0.01516786162684424</v>
       </c>
       <c r="V37" t="n">
-        <v>0.003042171779284847</v>
+        <v>0.002950268865545247</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002556232092759398</v>
+        <v>0.002462149102474331</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005709979705498007</v>
+        <v>0.005000771704942957</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1416438943560188</v>
+        <v>0.08867237739422326</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1093720223530449</v>
+        <v>0.07320842366714349</v>
       </c>
       <c r="M38" t="n">
-        <v>4.113546643685265</v>
+        <v>4.086901387408154</v>
       </c>
       <c r="N38" t="n">
-        <v>4.195688196265935</v>
+        <v>4.186769011306909</v>
       </c>
       <c r="O38" t="n">
-        <v>0.009403217904520443</v>
+        <v>0.01808078005569926</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002589265482107528</v>
+        <v>0.004211454220738628</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0006754920509172869</v>
+        <v>0.0006318491899226312</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0004656697738782062</v>
+        <v>0.000364327607185966</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0003975030949684453</v>
+        <v>1.513315947776252e-05</v>
       </c>
       <c r="T38" t="n">
-        <v>0.0314208676008576</v>
+        <v>0.06931498535894959</v>
       </c>
       <c r="U38" t="n">
-        <v>0.009153900516608731</v>
+        <v>0.01784522996214306</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002435890371761852</v>
+        <v>0.002354218943057131</v>
       </c>
       <c r="W38" t="n">
-        <v>0.002125676676037555</v>
+        <v>0.002050240595088031</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003144106513486889</v>
+        <v>0.002561366906263916</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514776863482813</v>
+        <v>0.09605755582229301</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1340398372572274</v>
+        <v>0.09759740726244502</v>
       </c>
       <c r="M39" t="n">
-        <v>4.258531293425802</v>
+        <v>4.239319110069875</v>
       </c>
       <c r="N39" t="n">
-        <v>4.266069201335666</v>
+        <v>4.257443659965783</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006493221980259241</v>
+        <v>0.01072037594928983</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002046783212853728</v>
+        <v>0.00196295982645286</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001058373386804991</v>
+        <v>0.001027527987212673</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002328310731240582</v>
+        <v>0.002113319065201823</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001423219936509659</v>
+        <v>0.001326701221836573</v>
       </c>
       <c r="T39" t="n">
-        <v>0.01689977535532027</v>
+        <v>0.03135488703786923</v>
       </c>
       <c r="U39" t="n">
-        <v>0.009748034530251472</v>
+        <v>0.01333831421713467</v>
       </c>
       <c r="V39" t="n">
-        <v>0.002831396688727956</v>
+        <v>0.00278094164293222</v>
       </c>
       <c r="W39" t="n">
-        <v>0.004037135450186052</v>
+        <v>0.003892841141048429</v>
       </c>
       <c r="X39" t="n">
-        <v>0.00302366556319029</v>
+        <v>0.002971323793524849</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2425659656922763</v>
+        <v>0.2142256566055331</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3996850531509176</v>
+        <v>0.394661534830651</v>
       </c>
       <c r="M40" t="n">
-        <v>4.328296976830683</v>
+        <v>4.344681894901522</v>
       </c>
       <c r="N40" t="n">
-        <v>4.517619555015153</v>
+        <v>4.514170259022397</v>
       </c>
       <c r="O40" t="n">
-        <v>0.00414377425017839</v>
+        <v>0.004651307991861894</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002646521723473389</v>
+        <v>0.002322485574023203</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002487207458091428</v>
+        <v>0.002436350575892888</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002452740023335495</v>
+        <v>0.002407602950242811</v>
       </c>
       <c r="S40" t="n">
-        <v>0.05427708640162198</v>
+        <v>0.04976876260678639</v>
       </c>
       <c r="T40" t="n">
-        <v>0.008114137801291416</v>
+        <v>0.009831078775435457</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004242165868538716</v>
+        <v>0.003961829011912363</v>
       </c>
       <c r="V40" t="n">
-        <v>0.004820983694162223</v>
+        <v>0.004832110841256744</v>
       </c>
       <c r="W40" t="n">
-        <v>0.003731053961252173</v>
+        <v>0.003794380446145862</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2583072179159262</v>
+        <v>0.2370730511669516</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2579668642380593</v>
+        <v>0.1960309265200225</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2828059115722345</v>
+        <v>0.2440453252000151</v>
       </c>
       <c r="M41" t="n">
-        <v>4.436658074738552</v>
+        <v>4.444022518146278</v>
       </c>
       <c r="N41" t="n">
-        <v>4.507114181196516</v>
+        <v>4.504187498359534</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001926746162240694</v>
+        <v>0.002338319740587516</v>
       </c>
       <c r="P41" t="n">
-        <v>0.003097239927249255</v>
+        <v>0.002594306828901853</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.00099409428109113</v>
+        <v>0.0009655053583199624</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009567194267890806</v>
+        <v>0.0008835907059930344</v>
       </c>
       <c r="S41" t="n">
-        <v>0.003921445231172699</v>
+        <v>0.003625695167361862</v>
       </c>
       <c r="T41" t="n">
-        <v>0.00478096832495594</v>
+        <v>0.006351939856943257</v>
       </c>
       <c r="U41" t="n">
-        <v>0.005278801004565194</v>
+        <v>0.00471260350543347</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002241589299968832</v>
+        <v>0.002199047180917988</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002146722492848939</v>
+        <v>0.002080480487086319</v>
       </c>
       <c r="X41" t="n">
-        <v>0.006902764030262055</v>
+        <v>0.006525697841731908</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.317014523922711</v>
+        <v>0.2509391170687325</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3994590236895776</v>
+        <v>0.3542623710802913</v>
       </c>
       <c r="M42" t="n">
-        <v>4.517744602412055</v>
+        <v>4.41672374136586</v>
       </c>
       <c r="N42" t="n">
-        <v>4.483268743019152</v>
+        <v>4.454935633917987</v>
       </c>
       <c r="O42" t="n">
-        <v>0.0052624267295362</v>
+        <v>0.006230201891398958</v>
       </c>
       <c r="P42" t="n">
-        <v>0.003751601650900459</v>
+        <v>0.002626640639557112</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.00422826523180969</v>
+        <v>0.003897268389341374</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003011014245468022</v>
+        <v>0.002806490660117976</v>
       </c>
       <c r="S42" t="n">
-        <v>0.003492938453932675</v>
+        <v>0.0114140369663968</v>
       </c>
       <c r="T42" t="n">
-        <v>0.0236488520407821</v>
+        <v>0.03954123015637864</v>
       </c>
       <c r="U42" t="n">
-        <v>0.01567208263111223</v>
+        <v>0.01154140968778515</v>
       </c>
       <c r="V42" t="n">
-        <v>0.01232767719795073</v>
+        <v>0.01057745512854912</v>
       </c>
       <c r="W42" t="n">
-        <v>0.01288233031174165</v>
+        <v>0.006334336323043348</v>
       </c>
       <c r="X42" t="n">
-        <v>3.865794396841796</v>
+        <v>17.28081695375366</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1593858374334936</v>
+        <v>0.1205565534842748</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2958523719248615</v>
+        <v>0.2629900009239222</v>
       </c>
       <c r="M43" t="n">
-        <v>3.921309732134107</v>
+        <v>3.918089231682008</v>
       </c>
       <c r="N43" t="n">
-        <v>4.233285879022268</v>
+        <v>4.219831538059108</v>
       </c>
       <c r="O43" t="n">
-        <v>0.03496846901355562</v>
+        <v>0.05523202991634595</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01374484320356314</v>
+        <v>0.01475387000891239</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0151856681346546</v>
+        <v>0.01389446427198884</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01698041540588782</v>
+        <v>0.01408014656704563</v>
       </c>
       <c r="S43" t="n">
-        <v>0.05767487231117728</v>
+        <v>0.0551767230886849</v>
       </c>
       <c r="T43" t="n">
-        <v>0.09380389881237274</v>
+        <v>0.1788110585784342</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02207080206657796</v>
+        <v>0.02673997772584549</v>
       </c>
       <c r="V43" t="n">
-        <v>0.02980073558654967</v>
+        <v>0.02728178448711684</v>
       </c>
       <c r="W43" t="n">
-        <v>0.03866146084124845</v>
+        <v>0.03406812448394574</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1572835530679738</v>
+        <v>0.1501719446044795</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1743546614482898</v>
+        <v>0.1161247165757327</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3610732774323228</v>
+        <v>0.2746994828953634</v>
       </c>
       <c r="M44" t="n">
-        <v>4.252007996567885</v>
+        <v>4.226110669456893</v>
       </c>
       <c r="N44" t="n">
-        <v>4.379586724816082</v>
+        <v>4.359696884688503</v>
       </c>
       <c r="O44" t="n">
-        <v>0.05943180072319394</v>
+        <v>0.09695824472565918</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02258796355990136</v>
+        <v>0.02927531683909404</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02157829855557556</v>
+        <v>0.01724321576425785</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01165903541634562</v>
+        <v>0.009785859000917108</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02252466555922277</v>
+        <v>0.01783441789055376</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1751135108474007</v>
+        <v>0.3418325628441926</v>
       </c>
       <c r="U44" t="n">
-        <v>0.04189371151768493</v>
+        <v>0.07891293966683598</v>
       </c>
       <c r="V44" t="n">
-        <v>0.04916033192741588</v>
+        <v>0.03566762918147429</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02319956777261208</v>
+        <v>0.01979541483860568</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04696270116222825</v>
+        <v>0.03676803080609439</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3961005288343256</v>
+        <v>0.3561715337841546</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2479943294578413</v>
+        <v>0.4598071986904772</v>
       </c>
       <c r="M45" t="n">
-        <v>4.214350986480778</v>
+        <v>4.204683775347685</v>
       </c>
       <c r="N45" t="n">
-        <v>4.321283307910669</v>
+        <v>4.424013673050669</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1307536841507036</v>
+        <v>0.1557151657858743</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1320966209382474</v>
+        <v>0.1388645884401747</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.05081882791349295</v>
+        <v>0.05061058147934436</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09173536452010415</v>
+        <v>0.09297534242724799</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1078988148880706</v>
+        <v>0.1159768802417834</v>
       </c>
       <c r="T45" t="n">
-        <v>0.6328950612962737</v>
+        <v>0.9372508569352602</v>
       </c>
       <c r="U45" t="n">
-        <v>0.4249006086480794</v>
+        <v>0.5121542114541249</v>
       </c>
       <c r="V45" t="n">
-        <v>0.151324651590732</v>
+        <v>0.1497409404427728</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2474850442376834</v>
+        <v>0.2681851975479116</v>
       </c>
       <c r="X45" t="n">
-        <v>0.3929057540413145</v>
+        <v>0.4465962169503613</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4197523519087317</v>
+        <v>0.4073750266228692</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3537994247664817</v>
+        <v>0.4880065708911719</v>
       </c>
       <c r="M46" t="n">
-        <v>3.774562388265622</v>
+        <v>3.814004562068153</v>
       </c>
       <c r="N46" t="n">
-        <v>4.475097579018535</v>
+        <v>4.469350610938019</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06990515626302188</v>
+        <v>0.07682959994522309</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0447362377903212</v>
+        <v>0.04836617575629115</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02429470085322225</v>
+        <v>0.0248778324833259</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0363765242040655</v>
+        <v>0.03873490004149029</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1859470277317496</v>
+        <v>0.1786212383203389</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1891339483173926</v>
+        <v>0.2187012618047699</v>
       </c>
       <c r="U46" t="n">
-        <v>0.08991401939022291</v>
+        <v>0.1005000216569451</v>
       </c>
       <c r="V46" t="n">
-        <v>0.0464486439283922</v>
+        <v>0.04509803799823041</v>
       </c>
       <c r="W46" t="n">
-        <v>0.05656817999001105</v>
+        <v>0.0619766858571695</v>
       </c>
       <c r="X46" t="n">
-        <v>2.115862403045977</v>
+        <v>1.804040518948512</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2493695583752376</v>
+        <v>0.1887746212355711</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3343697951216354</v>
+        <v>0.2874290224747945</v>
       </c>
       <c r="M47" t="n">
-        <v>4.220558446554917</v>
+        <v>4.185310192182019</v>
       </c>
       <c r="N47" t="n">
-        <v>4.341455675135808</v>
+        <v>4.328583899228017</v>
       </c>
       <c r="O47" t="n">
-        <v>0.04722494907936614</v>
+        <v>0.07110940241914274</v>
       </c>
       <c r="P47" t="n">
-        <v>0.02084494714261795</v>
+        <v>0.02770484688983762</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0177498432008436</v>
+        <v>0.0150711770579044</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01565835932171035</v>
+        <v>0.0134730992980786</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02308905151123523</v>
+        <v>0.019428418788142</v>
       </c>
       <c r="T47" t="n">
-        <v>0.1186555869560494</v>
+        <v>0.2133976947131692</v>
       </c>
       <c r="U47" t="n">
-        <v>0.03866223272704897</v>
+        <v>0.06748491365311077</v>
       </c>
       <c r="V47" t="n">
-        <v>0.03963500892286444</v>
+        <v>0.03070221996367363</v>
       </c>
       <c r="W47" t="n">
-        <v>0.02865151977507392</v>
+        <v>0.02444713432633894</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04388326360448622</v>
+        <v>0.03594619863005422</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.109062118721277</v>
+        <v>0.06767257822732965</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4844389589843668</v>
+        <v>0.3444655170478663</v>
       </c>
       <c r="M48" t="n">
-        <v>3.575232101365941</v>
+        <v>3.655465587484483</v>
       </c>
       <c r="N48" t="n">
-        <v>4.355927683725671</v>
+        <v>4.377152554950563</v>
       </c>
       <c r="O48" t="n">
-        <v>0.03702363992438523</v>
+        <v>0.1270028619427106</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05708986194302317</v>
+        <v>0.09873750319455882</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.06292346146347325</v>
+        <v>0.03592619996030982</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0488321549946007</v>
+        <v>0.0223041059189317</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2381958633347792</v>
+        <v>0.135429311126786</v>
       </c>
       <c r="T48" t="n">
-        <v>0.09799957050706212</v>
+        <v>0.5735611188183101</v>
       </c>
       <c r="U48" t="n">
-        <v>0.12193229432994</v>
+        <v>0.36919788510868</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1366994689081784</v>
+        <v>0.08415747515012176</v>
       </c>
       <c r="W48" t="n">
-        <v>0.08238586919110011</v>
+        <v>0.07474960721771885</v>
       </c>
       <c r="X48" t="n">
-        <v>4.820433676246771</v>
+        <v>1.433990799904918</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3590159275296238</v>
+        <v>0.3236571036150679</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4634981432331424</v>
+        <v>0.4686144102921178</v>
       </c>
       <c r="M49" t="n">
-        <v>4.039760162263589</v>
+        <v>4.059016345835413</v>
       </c>
       <c r="N49" t="n">
-        <v>4.38977869431469</v>
+        <v>4.382834935369007</v>
       </c>
       <c r="O49" t="n">
-        <v>0.02022015296150826</v>
+        <v>0.02192113966028977</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0123503391792448</v>
+        <v>0.0122837639981582</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01866388306532232</v>
+        <v>0.01827357291708274</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01797189746831082</v>
+        <v>0.01803190180433827</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09076720941899231</v>
+        <v>0.08645827567644777</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03989579727055428</v>
+        <v>0.04646816075417215</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01623377780370026</v>
+        <v>0.01620464291260096</v>
       </c>
       <c r="V49" t="n">
-        <v>0.0408414218222997</v>
+        <v>0.04043125544948525</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02775559265081241</v>
+        <v>0.02941485181432486</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3089221897184552</v>
+        <v>0.2873370510662619</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.509975097271933</v>
+        <v>0.5001414823415646</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5510567329931866</v>
+        <v>0.5577757949470938</v>
       </c>
       <c r="M50" t="n">
-        <v>4.291212719785222</v>
+        <v>4.295513413439029</v>
       </c>
       <c r="N50" t="n">
-        <v>4.504047402474733</v>
+        <v>4.457044878795037</v>
       </c>
       <c r="O50" t="n">
-        <v>0.06811326347880989</v>
+        <v>0.06788926081304565</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06354042613351439</v>
+        <v>0.06368326268118228</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06035715160801244</v>
+        <v>0.06115764601149682</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0330140599867615</v>
+        <v>0.03428496332131594</v>
       </c>
       <c r="S50" t="n">
-        <v>0.005333021605786354</v>
+        <v>0.01154321531393496</v>
       </c>
       <c r="T50" t="n">
-        <v>0.22100307175416</v>
+        <v>0.2593573616478965</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2020218657455441</v>
+        <v>0.2522866336263648</v>
       </c>
       <c r="V50" t="n">
-        <v>0.1298128226676996</v>
+        <v>0.2198777376994573</v>
       </c>
       <c r="W50" t="n">
-        <v>0.05767550358487186</v>
+        <v>0.1318869145564563</v>
       </c>
       <c r="X50" t="n">
-        <v>9.876632758716937</v>
+        <v>16.03225845867846</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4767246818589526</v>
+        <v>0.4746629412539786</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5522639707573709</v>
+        <v>0.5586512994732975</v>
       </c>
       <c r="M51" t="n">
-        <v>3.852084868275818</v>
+        <v>3.848875145161648</v>
       </c>
       <c r="N51" t="n">
-        <v>4.429624212899792</v>
+        <v>4.430374646935658</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05491846238935823</v>
+        <v>0.05471086747587899</v>
       </c>
       <c r="P51" t="n">
-        <v>0.04117347659418068</v>
+        <v>0.04132291046026035</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1264695062825598</v>
+        <v>0.1282684037246763</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06297349632791406</v>
+        <v>0.06379599648539155</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2140358340015852</v>
+        <v>0.2176649002617974</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1333764015336087</v>
+        <v>0.1325736777540877</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08217932098259809</v>
+        <v>0.0824556483190052</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2325102286839425</v>
+        <v>0.2290102194938922</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1170833451957221</v>
+        <v>0.1194794949804297</v>
       </c>
       <c r="X51" t="n">
-        <v>2.349713694515988</v>
+        <v>2.407352494974069</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.157761930875372</v>
+        <v>0.101465410040746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2333175373332652</v>
+        <v>0.1832309999901167</v>
       </c>
       <c r="M52" t="n">
-        <v>4.292754697312241</v>
+        <v>4.284078512333842</v>
       </c>
       <c r="N52" t="n">
-        <v>4.284848173608673</v>
+        <v>4.269507928507823</v>
       </c>
       <c r="O52" t="n">
-        <v>0.02168766463117145</v>
+        <v>0.03164884833657914</v>
       </c>
       <c r="P52" t="n">
-        <v>0.009439895818457951</v>
+        <v>0.01072562051701149</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.008160915449791941</v>
+        <v>0.007621309862449675</v>
       </c>
       <c r="R52" t="n">
-        <v>0.004617006876690318</v>
+        <v>0.003781409868006571</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01393490247454197</v>
+        <v>0.01078147063485251</v>
       </c>
       <c r="T52" t="n">
-        <v>0.0540949132481233</v>
+        <v>0.09460701130040967</v>
       </c>
       <c r="U52" t="n">
-        <v>0.02182633007498416</v>
+        <v>0.03021695865445212</v>
       </c>
       <c r="V52" t="n">
-        <v>0.01592965560247066</v>
+        <v>0.01460165865356912</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01230258960988904</v>
+        <v>0.01128793644165299</v>
       </c>
       <c r="X52" t="n">
-        <v>0.03957910897396508</v>
+        <v>0.03366380531981379</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3306984100273074</v>
+        <v>0.2727378027638814</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2217652418478735</v>
+        <v>0.2724215023286474</v>
       </c>
       <c r="M53" t="n">
-        <v>4.388506524434447</v>
+        <v>4.35109846563273</v>
       </c>
       <c r="N53" t="n">
-        <v>4.433878034578161</v>
+        <v>4.43548326789218</v>
       </c>
       <c r="O53" t="n">
-        <v>0.03773171920031353</v>
+        <v>0.05422302654978829</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02216863315702666</v>
+        <v>0.02504921565826318</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.009369705110336168</v>
+        <v>0.009120558779230275</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02188702540227282</v>
+        <v>0.02152047579568387</v>
       </c>
       <c r="S53" t="n">
-        <v>0.06792457934647343</v>
+        <v>0.0627282334772222</v>
       </c>
       <c r="T53" t="n">
-        <v>0.07936928765021489</v>
+        <v>0.1381598229581298</v>
       </c>
       <c r="U53" t="n">
-        <v>0.03713849859144589</v>
+        <v>0.04899978974172908</v>
       </c>
       <c r="V53" t="n">
-        <v>0.01637342217525893</v>
+        <v>0.01597795871589956</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03699585122714485</v>
+        <v>0.03832787774158337</v>
       </c>
       <c r="X53" t="n">
-        <v>0.08374183778681031</v>
+        <v>0.08041437243331148</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1828418750194339</v>
+        <v>0.1507171304147059</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4229697815204041</v>
+        <v>0.3839328907551371</v>
       </c>
       <c r="M54" t="n">
-        <v>4.170489229158358</v>
+        <v>4.160594641493467</v>
       </c>
       <c r="N54" t="n">
-        <v>4.302732049517491</v>
+        <v>4.280994575350889</v>
       </c>
       <c r="O54" t="n">
-        <v>0.03358846723253005</v>
+        <v>0.0432457899983635</v>
       </c>
       <c r="P54" t="n">
-        <v>0.009638921623333227</v>
+        <v>0.009751030045334249</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02189058373597026</v>
+        <v>0.01940175804747217</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009430019134853678</v>
+        <v>0.008132258299902499</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02324799663501636</v>
+        <v>0.02094211482779389</v>
       </c>
       <c r="T54" t="n">
-        <v>0.08552121911377887</v>
+        <v>0.1286771504668285</v>
       </c>
       <c r="U54" t="n">
-        <v>0.017348400633967</v>
+        <v>0.01770162733294266</v>
       </c>
       <c r="V54" t="n">
-        <v>0.05045713042730044</v>
+        <v>0.04426542774684408</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01845493174218227</v>
+        <v>0.01877364297216614</v>
       </c>
       <c r="X54" t="n">
-        <v>0.04322265176301757</v>
+        <v>0.04079018636841365</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1383001117129509</v>
+        <v>0.09413185541746323</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4716690640923025</v>
+        <v>0.480744243713867</v>
       </c>
       <c r="M55" t="n">
-        <v>4.460797912271313</v>
+        <v>4.486646905356348</v>
       </c>
       <c r="N55" t="n">
-        <v>4.389482784479831</v>
+        <v>4.388791560515845</v>
       </c>
       <c r="O55" t="n">
-        <v>0.0205724019394174</v>
+        <v>0.02110525765947869</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01095636546003868</v>
+        <v>0.01110335657637757</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.03320931655410412</v>
+        <v>0.03851058706574381</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01511075803479242</v>
+        <v>0.01542693351464197</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01581976770629591</v>
+        <v>0.01642955388658309</v>
       </c>
       <c r="T55" t="n">
-        <v>0.04489493529264424</v>
+        <v>0.04829836606929928</v>
       </c>
       <c r="U55" t="n">
-        <v>0.0166997677668316</v>
+        <v>0.01705686322379564</v>
       </c>
       <c r="V55" t="n">
-        <v>0.07671637573783197</v>
+        <v>0.08948770498789549</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02000742623868202</v>
+        <v>0.02035885045898444</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02408317706382548</v>
+        <v>0.02362710550306913</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2039298221414741</v>
+        <v>0.1460704737966806</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3225291753110692</v>
+        <v>0.2351975054111471</v>
       </c>
       <c r="M56" t="n">
-        <v>3.981252851815453</v>
+        <v>3.92679468727763</v>
       </c>
       <c r="N56" t="n">
-        <v>4.30712946662735</v>
+        <v>4.297981081719553</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02623284382628321</v>
+        <v>0.04691155749775006</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01234599096944209</v>
+        <v>0.01754630138991416</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01361231652188452</v>
+        <v>0.01039009808029463</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01291216428751192</v>
+        <v>0.01089843856978162</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04266136529566093</v>
+        <v>0.04095224224370835</v>
       </c>
       <c r="T56" t="n">
-        <v>0.06351380760775961</v>
+        <v>0.141546383456622</v>
       </c>
       <c r="U56" t="n">
-        <v>0.02360128902844759</v>
+        <v>0.04586335934233195</v>
       </c>
       <c r="V56" t="n">
-        <v>0.02963555531010365</v>
+        <v>0.02056490507558185</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02318867627299311</v>
+        <v>0.0195862729450151</v>
       </c>
       <c r="X56" t="n">
-        <v>0.107608343986451</v>
+        <v>0.1054397614063806</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3806411666965068</v>
+        <v>0.3372330102865788</v>
       </c>
       <c r="L57" t="n">
-        <v>0.447059970211117</v>
+        <v>0.4424917996776094</v>
       </c>
       <c r="M57" t="n">
-        <v>4.256768970266466</v>
+        <v>4.259702116978529</v>
       </c>
       <c r="N57" t="n">
-        <v>4.367587060948538</v>
+        <v>4.360492222091802</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02703240398254442</v>
+        <v>0.03001506794234124</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01018010379005899</v>
+        <v>0.01075414859172882</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01544971659160706</v>
+        <v>0.01458239889799871</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01359616928404648</v>
+        <v>0.01327408214149144</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02077661567532103</v>
+        <v>0.01974595170503979</v>
       </c>
       <c r="T57" t="n">
-        <v>0.05679796409358333</v>
+        <v>0.06637711045979706</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01694821873466503</v>
+        <v>0.01897269308462377</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03208324969321535</v>
+        <v>0.03030687108507573</v>
       </c>
       <c r="W57" t="n">
-        <v>0.0200225501218064</v>
+        <v>0.02062594924265041</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03237617380169238</v>
+        <v>0.03155294837477465</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1189716300414537</v>
+        <v>0.09167383144256949</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4915421821440906</v>
+        <v>0.4883211526853771</v>
       </c>
       <c r="M58" t="n">
-        <v>4.137219511845506</v>
+        <v>4.152556949971706</v>
       </c>
       <c r="N58" t="n">
-        <v>4.400276476589231</v>
+        <v>4.396733730183681</v>
       </c>
       <c r="O58" t="n">
-        <v>0.05722467700841838</v>
+        <v>0.06505016116030883</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01079322825767584</v>
+        <v>0.01052648432824317</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.0437047189441041</v>
+        <v>0.04495793975838448</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008149810648187716</v>
+        <v>0.007816272671367256</v>
       </c>
       <c r="S58" t="n">
-        <v>0.04296410878307049</v>
+        <v>0.04139947179332527</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1604036129243858</v>
+        <v>0.2021990115927247</v>
       </c>
       <c r="U58" t="n">
-        <v>0.02096398775065494</v>
+        <v>0.02091645052198375</v>
       </c>
       <c r="V58" t="n">
-        <v>0.1170791467931494</v>
+        <v>0.1231167648359903</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01856088510491745</v>
+        <v>0.01892037623526714</v>
       </c>
       <c r="X58" t="n">
-        <v>0.09423267571717542</v>
+        <v>0.09194514602734521</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4654669130886756</v>
+        <v>0.4454560940571964</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5137334953270173</v>
+        <v>0.5303019881341847</v>
       </c>
       <c r="M59" t="n">
-        <v>4.192052202289072</v>
+        <v>4.193144733448825</v>
       </c>
       <c r="N59" t="n">
-        <v>4.384757005062604</v>
+        <v>4.384951131560275</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01158213208727017</v>
+        <v>0.01216147893062486</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004501156376277752</v>
+        <v>0.004654816807526239</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.007971296892426216</v>
+        <v>0.007358421428858283</v>
       </c>
       <c r="R59" t="n">
-        <v>0.005960208500311382</v>
+        <v>0.006060300676625849</v>
       </c>
       <c r="S59" t="n">
-        <v>0.006862390422074775</v>
+        <v>0.006904487335112672</v>
       </c>
       <c r="T59" t="n">
-        <v>0.0200455496222555</v>
+        <v>0.02150230324014513</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005691467311731722</v>
+        <v>0.005969074602656554</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01207448781874912</v>
+        <v>0.01080816827615231</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005801047073611358</v>
+        <v>0.006041543118390611</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006502913782881363</v>
+        <v>0.006590207800777785</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3195516907355711</v>
+        <v>0.2701213903358244</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2335821217569123</v>
+        <v>0.219369108257831</v>
       </c>
       <c r="M60" t="n">
-        <v>4.041987989944264</v>
+        <v>4.028615073796866</v>
       </c>
       <c r="N60" t="n">
-        <v>4.211515428719657</v>
+        <v>4.210327474966972</v>
       </c>
       <c r="O60" t="n">
-        <v>0.005119763135164285</v>
+        <v>0.008102504003424008</v>
       </c>
       <c r="P60" t="n">
-        <v>0.003631889696482466</v>
+        <v>0.003739665668404545</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0009316206345992318</v>
+        <v>0.000859763141062474</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001681791884465103</v>
+        <v>0.00150686814901146</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004747628436562954</v>
+        <v>0.004414145453054481</v>
       </c>
       <c r="T60" t="n">
-        <v>0.008819318087748711</v>
+        <v>0.01614756307976096</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005534195711211343</v>
+        <v>0.006333113862525901</v>
       </c>
       <c r="V60" t="n">
-        <v>0.00194546240985284</v>
+        <v>0.001853023033286949</v>
       </c>
       <c r="W60" t="n">
-        <v>0.002317269556391085</v>
+        <v>0.002245432903739793</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005434801888720871</v>
+        <v>0.005140082501156945</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2918937862084307</v>
+        <v>0.2352207679818122</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2598346955432927</v>
+        <v>0.3528943445894322</v>
       </c>
       <c r="M61" t="n">
-        <v>3.826202503798687</v>
+        <v>3.90269338648964</v>
       </c>
       <c r="N61" t="n">
-        <v>4.253951092716853</v>
+        <v>4.266087600095104</v>
       </c>
       <c r="O61" t="n">
-        <v>0.008825463309659293</v>
+        <v>0.01057442814825096</v>
       </c>
       <c r="P61" t="n">
-        <v>0.007261296395201843</v>
+        <v>0.006360704815677527</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.002201324515139227</v>
+        <v>0.002216171543185875</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01028467626798965</v>
+        <v>0.01006359817266253</v>
       </c>
       <c r="S61" t="n">
-        <v>0.04376229981575793</v>
+        <v>0.03315561382883824</v>
       </c>
       <c r="T61" t="n">
-        <v>0.01547200449610845</v>
+        <v>0.02230511744504156</v>
       </c>
       <c r="U61" t="n">
-        <v>0.009442641561690116</v>
+        <v>0.008519194200087036</v>
       </c>
       <c r="V61" t="n">
-        <v>0.003573337299191144</v>
+        <v>0.003727323601308651</v>
       </c>
       <c r="W61" t="n">
-        <v>0.010025634095602</v>
+        <v>0.01247624466751179</v>
       </c>
       <c r="X61" t="n">
-        <v>0.3199145130268217</v>
+        <v>0.1647982820632887</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1532581908813461</v>
+        <v>0.1179114706658067</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2066590868543457</v>
+        <v>0.2764509217429959</v>
       </c>
       <c r="M62" t="n">
-        <v>4.148400063035928</v>
+        <v>4.133780946112485</v>
       </c>
       <c r="N62" t="n">
-        <v>4.187562429165657</v>
+        <v>4.207516710079696</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01050328050872985</v>
+        <v>0.01214439895381005</v>
       </c>
       <c r="P62" t="n">
-        <v>0.005163760427144291</v>
+        <v>0.004432149895250751</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.002415315030795406</v>
+        <v>0.002408703114065269</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01367947175723625</v>
+        <v>0.01281672433884701</v>
       </c>
       <c r="S62" t="n">
-        <v>0.009725001310454302</v>
+        <v>0.009308894781909077</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02175630933606802</v>
+        <v>0.02862996218873461</v>
       </c>
       <c r="U62" t="n">
-        <v>0.01013436189743866</v>
+        <v>0.007885176875249405</v>
       </c>
       <c r="V62" t="n">
-        <v>0.003957717964676706</v>
+        <v>0.00405733925242044</v>
       </c>
       <c r="W62" t="n">
-        <v>0.02210316017126304</v>
+        <v>0.02160442353163397</v>
       </c>
       <c r="X62" t="n">
-        <v>0.02036538870565461</v>
+        <v>0.01962872650662955</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2693602879820832</v>
+        <v>0.2141960782563756</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2801106513094213</v>
+        <v>0.3487495177631457</v>
       </c>
       <c r="M63" t="n">
-        <v>3.977065693514069</v>
+        <v>3.988319022978723</v>
       </c>
       <c r="N63" t="n">
-        <v>4.246272872864611</v>
+        <v>4.245981291611202</v>
       </c>
       <c r="O63" t="n">
-        <v>0.007524742774784452</v>
+        <v>0.008652175849787567</v>
       </c>
       <c r="P63" t="n">
-        <v>0.00623310251064766</v>
+        <v>0.005472231088578525</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.002065892440008845</v>
+        <v>0.002047206612409724</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007996123534263346</v>
+        <v>0.007686824307216186</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01738561124787679</v>
+        <v>0.0156450617226742</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01312228694373818</v>
+        <v>0.01732723428801709</v>
       </c>
       <c r="U63" t="n">
-        <v>0.008243090017401679</v>
+        <v>0.007328419181324657</v>
       </c>
       <c r="V63" t="n">
-        <v>0.003354211858710682</v>
+        <v>0.003506180119350197</v>
       </c>
       <c r="W63" t="n">
-        <v>0.01026329451454335</v>
+        <v>0.0119639079762153</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03580042266501465</v>
+        <v>0.03174648636259891</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2066785242826841</v>
+        <v>0.1809408828464476</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2655672477878417</v>
+        <v>0.3528408208695349</v>
       </c>
       <c r="M64" t="n">
-        <v>3.70690274747437</v>
+        <v>3.842031705252123</v>
       </c>
       <c r="N64" t="n">
-        <v>4.236555191142369</v>
+        <v>4.258389080963941</v>
       </c>
       <c r="O64" t="n">
-        <v>0.009760760903214465</v>
+        <v>0.01116038163902643</v>
       </c>
       <c r="P64" t="n">
-        <v>0.00643235252875748</v>
+        <v>0.005665029557881388</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.003222573081497184</v>
+        <v>0.003256499466513213</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01713548534950339</v>
+        <v>0.0170471191446408</v>
       </c>
       <c r="S64" t="n">
-        <v>0.05811891173340788</v>
+        <v>0.04383841392034955</v>
       </c>
       <c r="T64" t="n">
-        <v>0.01915344547984018</v>
+        <v>0.02491063003326341</v>
       </c>
       <c r="U64" t="n">
-        <v>0.009283543946023829</v>
+        <v>0.00781128702695008</v>
       </c>
       <c r="V64" t="n">
-        <v>0.005105963832783464</v>
+        <v>0.005310490088359769</v>
       </c>
       <c r="W64" t="n">
-        <v>0.02472468306879162</v>
+        <v>0.02677812262794139</v>
       </c>
       <c r="X64" t="n">
-        <v>1.151000526307225</v>
+        <v>0.5128246592809944</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2856673816535896</v>
+        <v>0.2343549687378016</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3407398181334132</v>
+        <v>0.4011844941158877</v>
       </c>
       <c r="M65" t="n">
-        <v>3.911375026612862</v>
+        <v>3.934277280939161</v>
       </c>
       <c r="N65" t="n">
-        <v>4.268358977938123</v>
+        <v>4.274548057304283</v>
       </c>
       <c r="O65" t="n">
-        <v>0.008282046321541905</v>
+        <v>0.009694695277283503</v>
       </c>
       <c r="P65" t="n">
-        <v>0.007711272640738872</v>
+        <v>0.007023237589017922</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.003871316101479553</v>
+        <v>0.003732467523735393</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0102545450169213</v>
+        <v>0.01004995159946265</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03226326562997626</v>
+        <v>0.02912865009510926</v>
       </c>
       <c r="T65" t="n">
-        <v>0.01390244162706635</v>
+        <v>0.01948105360046402</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01023459178253347</v>
+        <v>0.009730584980185615</v>
       </c>
       <c r="V65" t="n">
-        <v>0.006170399118336068</v>
+        <v>0.0063529154241192</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01254462835527181</v>
+        <v>0.01569636290595381</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1324165213036682</v>
+        <v>0.1093438685540792</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.252410987791241</v>
+        <v>0.2127213958762116</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2768480174094493</v>
+        <v>0.3646663745897433</v>
       </c>
       <c r="M66" t="n">
-        <v>3.951261926227352</v>
+        <v>3.974061279508674</v>
       </c>
       <c r="N66" t="n">
-        <v>4.239687518074408</v>
+        <v>4.260966974231366</v>
       </c>
       <c r="O66" t="n">
-        <v>0.009307159429461826</v>
+        <v>0.01054476078678367</v>
       </c>
       <c r="P66" t="n">
-        <v>0.007026690262257136</v>
+        <v>0.006196771010511841</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.003300995512780985</v>
+        <v>0.003324369131817166</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01553748687722207</v>
+        <v>0.0154605572723855</v>
       </c>
       <c r="S66" t="n">
-        <v>0.03002311711928095</v>
+        <v>0.02793740645459074</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01773217631235429</v>
+        <v>0.02278976562550286</v>
       </c>
       <c r="U66" t="n">
-        <v>0.009608652580356303</v>
+        <v>0.008196497493146569</v>
       </c>
       <c r="V66" t="n">
-        <v>0.005223290950400216</v>
+        <v>0.005436855408716415</v>
       </c>
       <c r="W66" t="n">
-        <v>0.02034173901394747</v>
+        <v>0.02222747100514111</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1607002691872437</v>
+        <v>0.1361302664234136</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4199481606275527</v>
+        <v>0.3806197152985693</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3946079364087451</v>
+        <v>0.4180326217377048</v>
       </c>
       <c r="M67" t="n">
-        <v>4.396330197414215</v>
+        <v>4.399192715745248</v>
       </c>
       <c r="N67" t="n">
-        <v>4.346590404488876</v>
+        <v>4.340914391682475</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005686700075282018</v>
+        <v>0.007193966750402698</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01442873312203694</v>
+        <v>0.01425465359679961</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.004110210004764778</v>
+        <v>0.004528732420121326</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009170193196447662</v>
+        <v>0.01016404133349689</v>
       </c>
       <c r="S67" t="n">
-        <v>0.05182828079878329</v>
+        <v>0.05807498360695549</v>
       </c>
       <c r="T67" t="n">
-        <v>0.008212848023578015</v>
+        <v>0.01079420917877434</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01324118018161912</v>
+        <v>0.0131673881058785</v>
       </c>
       <c r="V67" t="n">
-        <v>0.009267349298949569</v>
+        <v>0.01020209149938274</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01302232762513014</v>
+        <v>0.01535941888135656</v>
       </c>
       <c r="X67" t="n">
-        <v>0.07949518583970677</v>
+        <v>0.08973177086584896</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4285023488478826</v>
+        <v>0.3886321562971758</v>
       </c>
       <c r="L68" t="n">
-        <v>0.388790083391</v>
+        <v>0.4210307798996787</v>
       </c>
       <c r="M68" t="n">
-        <v>4.480408325582514</v>
+        <v>4.486141889112794</v>
       </c>
       <c r="N68" t="n">
-        <v>4.345648594021345</v>
+        <v>4.343721631660722</v>
       </c>
       <c r="O68" t="n">
-        <v>0.006211707985160668</v>
+        <v>0.007471699487229868</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01721004510934526</v>
+        <v>0.01646491273462727</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.004624498510364156</v>
+        <v>0.004768738195580125</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01376600744844261</v>
+        <v>0.01462602566640978</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01573548912561343</v>
+        <v>0.01676048354192652</v>
       </c>
       <c r="T68" t="n">
-        <v>0.01127896137210743</v>
+        <v>0.0144578451765362</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01600387510660763</v>
+        <v>0.01494406867446437</v>
       </c>
       <c r="V68" t="n">
-        <v>0.008227188002768738</v>
+        <v>0.008441007304457316</v>
       </c>
       <c r="W68" t="n">
-        <v>0.01952518742244272</v>
+        <v>0.02218429764408432</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02549845019953893</v>
+        <v>0.02709640484260496</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1574541057329026</v>
+        <v>0.1010562527983535</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2052525266463846</v>
+        <v>0.1728154412239898</v>
       </c>
       <c r="M69" t="n">
-        <v>4.332138796392004</v>
+        <v>4.331832199947486</v>
       </c>
       <c r="N69" t="n">
-        <v>4.301259047737942</v>
+        <v>4.292494753096341</v>
       </c>
       <c r="O69" t="n">
-        <v>0.008697335882864268</v>
+        <v>0.01227836227065161</v>
       </c>
       <c r="P69" t="n">
-        <v>0.005397398916447352</v>
+        <v>0.005171910872736205</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.003684531310681907</v>
+        <v>0.003621849674885609</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004267353123611629</v>
+        <v>0.00393319929732327</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004153910651498359</v>
+        <v>0.003959550028344942</v>
       </c>
       <c r="T69" t="n">
-        <v>0.01844820755406056</v>
+        <v>0.03119960710472874</v>
       </c>
       <c r="U69" t="n">
-        <v>0.009630476247740338</v>
+        <v>0.01126999654084391</v>
       </c>
       <c r="V69" t="n">
-        <v>0.005812052722773665</v>
+        <v>0.005660831473145589</v>
       </c>
       <c r="W69" t="n">
-        <v>0.005999333156887494</v>
+        <v>0.005770215295190083</v>
       </c>
       <c r="X69" t="n">
-        <v>0.006095744047079951</v>
+        <v>0.005911360709834601</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548184556465437</v>
+        <v>0.09856641470047335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2821165444330669</v>
+        <v>0.2505198071039456</v>
       </c>
       <c r="M70" t="n">
-        <v>4.393884558299479</v>
+        <v>4.407350183726711</v>
       </c>
       <c r="N70" t="n">
-        <v>4.356902676963256</v>
+        <v>4.347484747920573</v>
       </c>
       <c r="O70" t="n">
-        <v>0.007041754705486096</v>
+        <v>0.008900343123081009</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009916987065314005</v>
+        <v>0.01082228342232973</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.005609818782489916</v>
+        <v>0.005510675920288217</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004620176931972432</v>
+        <v>0.004298058762111358</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006475976953657859</v>
+        <v>0.006106313610785698</v>
       </c>
       <c r="T70" t="n">
-        <v>0.01338069637391916</v>
+        <v>0.02032112834075771</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01381308858031555</v>
+        <v>0.01783416247620849</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009080225123130677</v>
+        <v>0.008790946560765173</v>
       </c>
       <c r="W70" t="n">
-        <v>0.006717288047944464</v>
+        <v>0.006477371296333982</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009743408757198643</v>
+        <v>0.009295405813250108</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259372932035616</v>
+        <v>0.2690457232237147</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3495122827845789</v>
+        <v>0.3369175539482026</v>
       </c>
       <c r="M71" t="n">
-        <v>4.435983776929537</v>
+        <v>4.440211154547947</v>
       </c>
       <c r="N71" t="n">
-        <v>4.438765799706143</v>
+        <v>4.434015584745439</v>
       </c>
       <c r="O71" t="n">
-        <v>0.008538237815690698</v>
+        <v>0.00991629372546874</v>
       </c>
       <c r="P71" t="n">
-        <v>0.009237006911603483</v>
+        <v>0.00848197248577397</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.004661901364167855</v>
+        <v>0.004549219987528587</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005153535629014602</v>
+        <v>0.004876232308383993</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005562343198507328</v>
+        <v>0.005271864127605714</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01387597490106091</v>
+        <v>0.01811938122738775</v>
       </c>
       <c r="U71" t="n">
-        <v>0.009902587743156315</v>
+        <v>0.009448037052860179</v>
       </c>
       <c r="V71" t="n">
-        <v>0.007437539250542451</v>
+        <v>0.007274447047360384</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006776745720272799</v>
+        <v>0.006731810439762302</v>
       </c>
       <c r="X71" t="n">
-        <v>0.006932320374759091</v>
+        <v>0.006781796234543846</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3247916833722452</v>
+        <v>0.2663662166319356</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4127186230893385</v>
+        <v>0.391675815211094</v>
       </c>
       <c r="M72" t="n">
-        <v>4.528094939538367</v>
+        <v>4.543373877819946</v>
       </c>
       <c r="N72" t="n">
-        <v>4.500728602013576</v>
+        <v>4.497098791971776</v>
       </c>
       <c r="O72" t="n">
-        <v>0.006160620005598041</v>
+        <v>0.006617664925347296</v>
       </c>
       <c r="P72" t="n">
-        <v>0.007061793149966656</v>
+        <v>0.006726549259816711</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.005623081508063347</v>
+        <v>0.005441161779033739</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004398654641003785</v>
+        <v>0.004159600483390923</v>
       </c>
       <c r="S72" t="n">
-        <v>0.006047072051250384</v>
+        <v>0.005724517079152029</v>
       </c>
       <c r="T72" t="n">
-        <v>0.008992879365170294</v>
+        <v>0.01033473285357992</v>
       </c>
       <c r="U72" t="n">
-        <v>0.008021590002114092</v>
+        <v>0.007885581611308916</v>
       </c>
       <c r="V72" t="n">
-        <v>0.009016568120366681</v>
+        <v>0.008797125155105638</v>
       </c>
       <c r="W72" t="n">
-        <v>0.006169601223022439</v>
+        <v>0.00603326875278102</v>
       </c>
       <c r="X72" t="n">
-        <v>0.007714964968362422</v>
+        <v>0.00755224364971</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08004889403840529</v>
+        <v>0.04025276581779436</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08113991389542105</v>
+        <v>0.05536347232051227</v>
       </c>
       <c r="M73" t="n">
-        <v>4.341167164957967</v>
+        <v>4.33317781811658</v>
       </c>
       <c r="N73" t="n">
-        <v>4.328594414246572</v>
+        <v>4.324606523263236</v>
       </c>
       <c r="O73" t="n">
-        <v>0.01323244292225256</v>
+        <v>0.02659825137779304</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01256801918834716</v>
+        <v>0.01762178476435033</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.001841608910406477</v>
+        <v>0.001801163706178717</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002548885856111626</v>
+        <v>0.002341007847490206</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003786034117191857</v>
+        <v>0.0002709741151206127</v>
       </c>
       <c r="T73" t="n">
-        <v>0.03777100137267746</v>
+        <v>0.08962191717353805</v>
       </c>
       <c r="U73" t="n">
-        <v>0.0252108259623172</v>
+        <v>0.04965652585052124</v>
       </c>
       <c r="V73" t="n">
-        <v>0.003453255620810314</v>
+        <v>0.003357113370447076</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004161393983429871</v>
+        <v>0.004033240478339807</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003226953352581988</v>
+        <v>0.003165349293642675</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08447253359755409</v>
+        <v>0.04324396691802901</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1625880726057796</v>
+        <v>0.1245817905430269</v>
       </c>
       <c r="M74" t="n">
-        <v>4.398896242437559</v>
+        <v>4.406169628486518</v>
       </c>
       <c r="N74" t="n">
-        <v>4.385985339944041</v>
+        <v>4.378743273506256</v>
       </c>
       <c r="O74" t="n">
-        <v>0.006292812977601652</v>
+        <v>0.009299121360808774</v>
       </c>
       <c r="P74" t="n">
-        <v>0.008619410209494893</v>
+        <v>0.009721791622148125</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003381667276977047</v>
+        <v>0.003345567052855437</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002113418783171738</v>
+        <v>0.00196402305420914</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003726249521864578</v>
+        <v>0.00355111499063515</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01629589020276353</v>
+        <v>0.02882917148838839</v>
       </c>
       <c r="U74" t="n">
-        <v>0.0145034888740591</v>
+        <v>0.02141380503764006</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005347454516546753</v>
+        <v>0.005249609750866639</v>
       </c>
       <c r="W74" t="n">
-        <v>0.003684016781749129</v>
+        <v>0.003569501029530347</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005623921283970385</v>
+        <v>0.005457597189531748</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2074205046880389</v>
+        <v>0.148541542472987</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2623727640782005</v>
+        <v>0.236417971840428</v>
       </c>
       <c r="M75" t="n">
-        <v>4.197065933067138</v>
+        <v>4.193647807726889</v>
       </c>
       <c r="N75" t="n">
-        <v>4.282963131348233</v>
+        <v>4.271708687129742</v>
       </c>
       <c r="O75" t="n">
-        <v>0.006245120541096643</v>
+        <v>0.008065936287791063</v>
       </c>
       <c r="P75" t="n">
-        <v>0.009670164516327455</v>
+        <v>0.01016981659294952</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004021698121183217</v>
+        <v>0.00393681174460205</v>
       </c>
       <c r="R75" t="n">
-        <v>0.004762930561152022</v>
+        <v>0.004476456084793635</v>
       </c>
       <c r="S75" t="n">
-        <v>0.00717411220561622</v>
+        <v>0.006950310909617806</v>
       </c>
       <c r="T75" t="n">
-        <v>0.01211322190424821</v>
+        <v>0.0181352741380212</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01264484894402839</v>
+        <v>0.01515749254809914</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006370435967034196</v>
+        <v>0.006179064498296491</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006517516058862821</v>
+        <v>0.006389101105130059</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01087003527579221</v>
+        <v>0.01062884933147779</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053193225236777</v>
+        <v>0.006369374504835267</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02514679805700491</v>
+        <v>0.01262782327786958</v>
       </c>
       <c r="M76" t="n">
-        <v>4.359073588567345</v>
+        <v>4.367107409264443</v>
       </c>
       <c r="N76" t="n">
-        <v>4.318116560981346</v>
+        <v>4.315760700722528</v>
       </c>
       <c r="O76" t="n">
-        <v>0.04210715459668449</v>
+        <v>0.1218389233337715</v>
       </c>
       <c r="P76" t="n">
-        <v>0.02727963062340896</v>
+        <v>0.06968550537031559</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002067085639341657</v>
+        <v>0.002082841378244382</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002217603147539648</v>
+        <v>0.002115922589962488</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007945353140518981</v>
+        <v>0.0007605908591142714</v>
       </c>
       <c r="T76" t="n">
-        <v>0.1416058625041486</v>
+        <v>0.4990917226147454</v>
       </c>
       <c r="U76" t="n">
-        <v>0.08361900735273005</v>
+        <v>0.2838782989150884</v>
       </c>
       <c r="V76" t="n">
-        <v>0.003583708688033575</v>
+        <v>0.003522376589276744</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003737440631798268</v>
+        <v>0.00368021497995292</v>
       </c>
       <c r="X76" t="n">
-        <v>0.00269881302661401</v>
+        <v>0.00268477100477297</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03782537579660925</v>
+        <v>0.014699157934358</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08097815804016646</v>
+        <v>0.04735676941388613</v>
       </c>
       <c r="M77" t="n">
-        <v>4.268656568147811</v>
+        <v>4.273959898801073</v>
       </c>
       <c r="N77" t="n">
-        <v>4.245138155328809</v>
+        <v>4.239646620283942</v>
       </c>
       <c r="O77" t="n">
-        <v>0.01381894615408611</v>
+        <v>0.0282764774980253</v>
       </c>
       <c r="P77" t="n">
-        <v>0.003757490358159672</v>
+        <v>0.003658808990467539</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002032619045363282</v>
+        <v>0.001960529131459165</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003791909046618231</v>
+        <v>0.0003432916313894685</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001767978679563574</v>
+        <v>0.001684945351145738</v>
       </c>
       <c r="T77" t="n">
-        <v>0.03403154285305804</v>
+        <v>0.08653092553925498</v>
       </c>
       <c r="U77" t="n">
-        <v>0.01318563316280446</v>
+        <v>0.02143622921036587</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003054291550795958</v>
+        <v>0.002944521394992629</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002024625475944558</v>
+        <v>0.001997982272809138</v>
       </c>
       <c r="X77" t="n">
-        <v>0.00276789467274687</v>
+        <v>0.002713175557885006</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02723295651487582</v>
+        <v>0.009272849175076056</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0766008676009966</v>
+        <v>0.04495372864170763</v>
       </c>
       <c r="M78" t="n">
-        <v>4.413573948301897</v>
+        <v>4.409715680264562</v>
       </c>
       <c r="N78" t="n">
-        <v>4.37829161508492</v>
+        <v>4.36338413632331</v>
       </c>
       <c r="O78" t="n">
-        <v>0.006302566309750019</v>
+        <v>0.01123710931967161</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000071305e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.001805496917605349</v>
+        <v>0.001851853697068877</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001674553222235624</v>
+        <v>0.000128136724843387</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000000033e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.0215391969134919</v>
+        <v>0.04629003468484238</v>
       </c>
       <c r="U78" t="n">
-        <v>0.0189688646835046</v>
+        <v>0.02275019418894108</v>
       </c>
       <c r="V78" t="n">
-        <v>0.002891265875586965</v>
+        <v>0.002932172079670464</v>
       </c>
       <c r="W78" t="n">
-        <v>0.00170555842652797</v>
+        <v>0.001672825453689347</v>
       </c>
       <c r="X78" t="n">
-        <v>0.002934388439255799</v>
+        <v>0.003015327846111883</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2905655997701949</v>
+        <v>0.2305198222631793</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3193251383257389</v>
+        <v>0.2944840336380979</v>
       </c>
       <c r="M79" t="n">
-        <v>4.384688376048642</v>
+        <v>4.376078257807563</v>
       </c>
       <c r="N79" t="n">
-        <v>4.414745075458724</v>
+        <v>4.374736024285611</v>
       </c>
       <c r="O79" t="n">
-        <v>0.003147207099280328</v>
+        <v>0.003854199158449958</v>
       </c>
       <c r="P79" t="n">
-        <v>0.00181777187931982</v>
+        <v>0.001653553899850292</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001444320371422225</v>
+        <v>0.00139301954204593</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001630442173610273</v>
+        <v>0.00149653264250928</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0005977485697859727</v>
+        <v>0.4999999999998958</v>
       </c>
       <c r="T79" t="n">
-        <v>0.00607770090173849</v>
+        <v>0.00915740153640349</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002150034004461958</v>
+        <v>0.002292255310038759</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002565919663114426</v>
+        <v>0.002429698101568048</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002597945957028094</v>
+        <v>0.002361342428098995</v>
       </c>
       <c r="X79" t="n">
-        <v>0.154595460590586</v>
+        <v>11203.1950119143</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1624757209231998</v>
+        <v>0.1040560020796793</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2462244769929051</v>
+        <v>0.218476711672129</v>
       </c>
       <c r="M80" t="n">
-        <v>4.522041228329741</v>
+        <v>4.534282997629987</v>
       </c>
       <c r="N80" t="n">
-        <v>4.466768919963216</v>
+        <v>4.420265770976781</v>
       </c>
       <c r="O80" t="n">
-        <v>0.004352998420737021</v>
+        <v>0.005932839983048368</v>
       </c>
       <c r="P80" t="n">
-        <v>0.002638442960042925</v>
+        <v>0.002691147644599539</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.001807076613868658</v>
+        <v>0.001773653128436966</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001726803461836381</v>
+        <v>0.001594195191514418</v>
       </c>
       <c r="S80" t="n">
-        <v>1.000000001324653e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T80" t="n">
-        <v>0.01046157986673176</v>
+        <v>0.0176857938648153</v>
       </c>
       <c r="U80" t="n">
-        <v>0.003125894024472116</v>
+        <v>0.00431281231305578</v>
       </c>
       <c r="V80" t="n">
-        <v>0.003152564688256193</v>
+        <v>0.003063732084893318</v>
       </c>
       <c r="W80" t="n">
-        <v>0.002868581738658547</v>
+        <v>0.002588934858855894</v>
       </c>
       <c r="X80" t="n">
-        <v>0.1347039345787046</v>
+        <v>13589.83477000429</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2764885304045394</v>
+        <v>0.213446177968006</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2567972681835818</v>
+        <v>0.2374918416394046</v>
       </c>
       <c r="M81" t="n">
-        <v>4.543506980364979</v>
+        <v>4.524759522719838</v>
       </c>
       <c r="N81" t="n">
-        <v>4.588717551710889</v>
+        <v>4.590465621629452</v>
       </c>
       <c r="O81" t="n">
-        <v>0.003861634035074769</v>
+        <v>0.005221464741992496</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002251801281670118</v>
+        <v>0.00199704998973603</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001123941612958597</v>
+        <v>0.001088715129074062</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001628878612580421</v>
+        <v>0.001549017070440027</v>
       </c>
       <c r="S81" t="n">
-        <v>1.00000000000048e-05</v>
+        <v>1.000000000000034e-05</v>
       </c>
       <c r="T81" t="n">
-        <v>0.007830854480611368</v>
+        <v>0.01257767996493511</v>
       </c>
       <c r="U81" t="n">
-        <v>0.003271441487494405</v>
+        <v>0.004399579669065928</v>
       </c>
       <c r="V81" t="n">
-        <v>0.001996657285093528</v>
+        <v>0.001884380130274462</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002502731092812272</v>
+        <v>0.00231987209495698</v>
       </c>
       <c r="X81" t="n">
-        <v>0.1141189430623603</v>
+        <v>0.152436907675027</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1873857992577476</v>
+        <v>0.1218395255999014</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1461279938730407</v>
+        <v>0.152998499319656</v>
       </c>
       <c r="M82" t="n">
-        <v>4.465612453484066</v>
+        <v>4.428003213484716</v>
       </c>
       <c r="N82" t="n">
-        <v>4.5948294093929</v>
+        <v>4.609107942260349</v>
       </c>
       <c r="O82" t="n">
-        <v>0.006871720059069834</v>
+        <v>0.01086290388233511</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003131021004272071</v>
+        <v>0.002971479519978821</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.0009602008629425483</v>
+        <v>0.0009559931355004234</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001784373168837745</v>
+        <v>0.001750478629223874</v>
       </c>
       <c r="S82" t="n">
-        <v>0.2287772810153216</v>
+        <v>0.000946000408968784</v>
       </c>
       <c r="T82" t="n">
-        <v>0.02780797484512675</v>
+        <v>0.03268230711802186</v>
       </c>
       <c r="U82" t="n">
-        <v>0.006942045095459899</v>
+        <v>0.009250046975701766</v>
       </c>
       <c r="V82" t="n">
-        <v>0.001769355116460212</v>
+        <v>0.001649014405121745</v>
       </c>
       <c r="W82" t="n">
-        <v>0.003043758480154077</v>
+        <v>0.002817916242826584</v>
       </c>
       <c r="X82" t="n">
-        <v>5438.420271339656</v>
+        <v>0.4528456954412413</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1900383461359677</v>
+        <v>0.1274211052633809</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1855790480569224</v>
+        <v>0.1595764234582905</v>
       </c>
       <c r="M83" t="n">
-        <v>4.580927191812872</v>
+        <v>4.571265893551568</v>
       </c>
       <c r="N83" t="n">
-        <v>4.571329756778653</v>
+        <v>4.569304386046905</v>
       </c>
       <c r="O83" t="n">
-        <v>0.004106819793420861</v>
+        <v>0.006094554952550324</v>
       </c>
       <c r="P83" t="n">
-        <v>0.001704682090402879</v>
+        <v>0.001730887138065959</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.000998696866006887</v>
+        <v>0.0009835348495635832</v>
       </c>
       <c r="R83" t="n">
-        <v>0.00142244321359066</v>
+        <v>0.001338599811037459</v>
       </c>
       <c r="S83" t="n">
-        <v>1.000000000025039e-05</v>
+        <v>1.000000000002187e-05</v>
       </c>
       <c r="T83" t="n">
-        <v>0.009656310806411373</v>
+        <v>0.01729650461460607</v>
       </c>
       <c r="U83" t="n">
-        <v>0.004878179448193665</v>
+        <v>0.006581918783929049</v>
       </c>
       <c r="V83" t="n">
-        <v>0.001816976652035546</v>
+        <v>0.001738103584508633</v>
       </c>
       <c r="W83" t="n">
-        <v>0.002365581625461602</v>
+        <v>0.002098805333429218</v>
       </c>
       <c r="X83" t="n">
-        <v>0.130510815641632</v>
+        <v>0.165869421217256</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1700871734410854</v>
+        <v>0.1109470721818669</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2305510722140747</v>
+        <v>0.2282017934601235</v>
       </c>
       <c r="M84" t="n">
-        <v>4.554043371413063</v>
+        <v>4.586544133145753</v>
       </c>
       <c r="N84" t="n">
-        <v>4.502375865319721</v>
+        <v>4.493902833405971</v>
       </c>
       <c r="O84" t="n">
-        <v>0.004580612431084036</v>
+        <v>0.005357604577401585</v>
       </c>
       <c r="P84" t="n">
-        <v>1.000000000001186e-05</v>
+        <v>1.000000000000032e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001674498145792546</v>
+        <v>0.001972072971827946</v>
       </c>
       <c r="R84" t="n">
-        <v>0.002005585337766274</v>
+        <v>0.001931401485914033</v>
       </c>
       <c r="S84" t="n">
-        <v>1.000000000000519e-05</v>
+        <v>1.000000000000071e-05</v>
       </c>
       <c r="T84" t="n">
-        <v>0.0116420548043375</v>
+        <v>0.01667233056936858</v>
       </c>
       <c r="U84" t="n">
-        <v>0.006982834285418339</v>
+        <v>0.005083044261782481</v>
       </c>
       <c r="V84" t="n">
-        <v>0.002968594967667026</v>
+        <v>0.00361904771543812</v>
       </c>
       <c r="W84" t="n">
-        <v>0.003366699868374119</v>
+        <v>0.003196803436588013</v>
       </c>
       <c r="X84" t="n">
-        <v>0.1163796120549553</v>
+        <v>0.1401906687136986</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.234087371719241</v>
+        <v>0.2332956893959356</v>
       </c>
       <c r="L85" t="n">
-        <v>0.280140121329051</v>
+        <v>0.2566636548534066</v>
       </c>
       <c r="M85" t="n">
-        <v>4.488615918273156</v>
+        <v>4.323756426548535</v>
       </c>
       <c r="N85" t="n">
-        <v>4.486629258925698</v>
+        <v>4.387827633730484</v>
       </c>
       <c r="O85" t="n">
-        <v>0.003296136043681622</v>
+        <v>0.004609996991013587</v>
       </c>
       <c r="P85" t="n">
-        <v>1.000000000000389e-05</v>
+        <v>0.001674315511436737</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001469872716214687</v>
+        <v>0.001092119088020634</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001743971564358019</v>
+        <v>0.001439813448878605</v>
       </c>
       <c r="S85" t="n">
-        <v>1.000000000000016e-05</v>
+        <v>0.4999999999881212</v>
       </c>
       <c r="T85" t="n">
-        <v>0.007173279975091383</v>
+        <v>0.01180025961016239</v>
       </c>
       <c r="U85" t="n">
-        <v>0.008869431645645152</v>
+        <v>0.003337103167988728</v>
       </c>
       <c r="V85" t="n">
-        <v>0.002771769748580426</v>
+        <v>0.00191774101406797</v>
       </c>
       <c r="W85" t="n">
-        <v>0.00281278493756876</v>
+        <v>0.002198307044018838</v>
       </c>
       <c r="X85" t="n">
-        <v>0.1248270624367359</v>
+        <v>17798.44572577703</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1246919775437176</v>
+        <v>0.1064698714707798</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1550425121143549</v>
+        <v>0.1909897613905012</v>
       </c>
       <c r="M86" t="n">
-        <v>4.567691173450373</v>
+        <v>4.52106968442537</v>
       </c>
       <c r="N86" t="n">
-        <v>4.512548632694066</v>
+        <v>4.434172483894417</v>
       </c>
       <c r="O86" t="n">
-        <v>0.005849095074375368</v>
+        <v>0.006626556546612984</v>
       </c>
       <c r="P86" t="n">
-        <v>1.000000000000081e-05</v>
+        <v>0.0026970589683277</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001430381346093342</v>
+        <v>0.001543818943479143</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001787067398720183</v>
+        <v>0.001605790934941762</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000000000000013e-05</v>
+        <v>0.4999999999722498</v>
       </c>
       <c r="T86" t="n">
-        <v>0.01733173470967076</v>
+        <v>0.02036376328717037</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01091931350920984</v>
+        <v>0.006088301096343186</v>
       </c>
       <c r="V86" t="n">
-        <v>0.002402706329626853</v>
+        <v>0.002602085290834123</v>
       </c>
       <c r="W86" t="n">
-        <v>0.002984945666529529</v>
+        <v>0.002639614053432804</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1683221126162023</v>
+        <v>21105.47992074858</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.183694725148222</v>
+        <v>0.1378578795676572</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2687456357101996</v>
+        <v>0.1484289448198439</v>
       </c>
       <c r="M87" t="n">
-        <v>4.672692369942369</v>
+        <v>4.414858197264242</v>
       </c>
       <c r="N87" t="n">
-        <v>4.616044464788106</v>
+        <v>4.607395251395704</v>
       </c>
       <c r="O87" t="n">
-        <v>0.004964727179279235</v>
+        <v>0.01341034335547554</v>
       </c>
       <c r="P87" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>0.004076814340411841</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.002033794528026338</v>
+        <v>0.001079458167944005</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002179270426489814</v>
+        <v>0.001954331460431002</v>
       </c>
       <c r="S87" t="n">
-        <v>1e-05</v>
+        <v>0.001031324363562995</v>
       </c>
       <c r="T87" t="n">
-        <v>0.01278550199599605</v>
+        <v>0.04343008000292274</v>
       </c>
       <c r="U87" t="n">
-        <v>0.01022621818961415</v>
+        <v>0.01142884811027275</v>
       </c>
       <c r="V87" t="n">
-        <v>0.003740057321166303</v>
+        <v>0.001791853355266572</v>
       </c>
       <c r="W87" t="n">
-        <v>0.003549715269311207</v>
+        <v>0.003165718442000178</v>
       </c>
       <c r="X87" t="n">
-        <v>0.1202410704999621</v>
+        <v>0.4565565709603079</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2274032847723464</v>
+        <v>0.1889560953604737</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1673328583440921</v>
+        <v>0.2443943733861424</v>
       </c>
       <c r="M88" t="n">
-        <v>4.517087837474207</v>
+        <v>4.526684391662236</v>
       </c>
       <c r="N88" t="n">
-        <v>4.647285499139455</v>
+        <v>4.593618672831496</v>
       </c>
       <c r="O88" t="n">
-        <v>0.005266147828622851</v>
+        <v>0.005490157750864028</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0005465931621263184</v>
+        <v>0.002289825236502392</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0008493419608545413</v>
+        <v>0.001172710356653248</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001407573790231963</v>
+        <v>0.001701089432735791</v>
       </c>
       <c r="S88" t="n">
-        <v>1.00000000000075e-05</v>
+        <v>1.000000000000287e-05</v>
       </c>
       <c r="T88" t="n">
-        <v>0.01243257252173008</v>
+        <v>0.01336549654223138</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01083660223235061</v>
+        <v>0.00473844345765612</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001553682158523592</v>
+        <v>0.002005779485375153</v>
       </c>
       <c r="W88" t="n">
-        <v>0.002124945130946269</v>
+        <v>0.002527178484275516</v>
       </c>
       <c r="X88" t="n">
-        <v>0.1818832472986572</v>
+        <v>0.1421684918794727</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3272038829542777</v>
+        <v>0.2890984316053696</v>
       </c>
       <c r="L89" t="n">
-        <v>0.321952740767023</v>
+        <v>0.288660948536726</v>
       </c>
       <c r="M89" t="n">
-        <v>4.487315914632268</v>
+        <v>4.444533540889832</v>
       </c>
       <c r="N89" t="n">
-        <v>4.608693782980143</v>
+        <v>4.575225126750566</v>
       </c>
       <c r="O89" t="n">
-        <v>0.004305939976017327</v>
+        <v>0.005662439769292392</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001456081439865403</v>
+        <v>0.0004589806335395632</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001404315030037233</v>
+        <v>0.001354744439483488</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001916351078513785</v>
+        <v>0.001814220098364295</v>
       </c>
       <c r="S89" t="n">
-        <v>1.000000000000149e-05</v>
+        <v>0.4999999999999987</v>
       </c>
       <c r="T89" t="n">
-        <v>0.008668944829848734</v>
+        <v>0.01481913064843407</v>
       </c>
       <c r="U89" t="n">
-        <v>0.004370310872916383</v>
+        <v>0.003424945231461888</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002421010923300436</v>
+        <v>0.002337453544319553</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002843692963168578</v>
+        <v>0.002654808197934827</v>
       </c>
       <c r="X89" t="n">
-        <v>0.07664868788764578</v>
+        <v>12477.02435542868</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2282474838080587</v>
+        <v>0.4644377694824607</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4832343948314514</v>
+        <v>0.5375675187625859</v>
       </c>
       <c r="M90" t="n">
-        <v>4.491846084938333</v>
+        <v>4.563637114762272</v>
       </c>
       <c r="N90" t="n">
-        <v>4.280875882070323</v>
+        <v>4.297813105407688</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003757399696253097</v>
+        <v>0.003724461193466038</v>
       </c>
       <c r="P90" t="n">
-        <v>0.003634252918635858</v>
+        <v>0.004599957004401709</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.006439946019001296</v>
+        <v>0.00706977850460235</v>
       </c>
       <c r="R90" t="n">
-        <v>0.009893870077762896</v>
+        <v>0.01166389685146623</v>
       </c>
       <c r="S90" t="n">
-        <v>0.002401356286536427</v>
+        <v>0.002136615086035401</v>
       </c>
       <c r="T90" t="n">
-        <v>0.00697155200881593</v>
+        <v>0.006224583351211488</v>
       </c>
       <c r="U90" t="n">
-        <v>0.005981129556628113</v>
+        <v>0.006255939919254635</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01242154336331217</v>
+        <v>0.006729292070099131</v>
       </c>
       <c r="W90" t="n">
-        <v>0.02564634798467763</v>
+        <v>0.0270163463365355</v>
       </c>
       <c r="X90" t="n">
-        <v>0.08972936629531826</v>
+        <v>0.06027463420209723</v>
       </c>
     </row>
   </sheetData>
